--- a/Data - For Annotation/open_coding_200.xlsx
+++ b/Data - For Annotation/open_coding_200.xlsx
@@ -463,10 +463,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>🇮🇹 'Mission: Impossible – Dead Reckoning Part One' continues to lead on Friday. Indiana Jones and Elemental round up the top three.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>Top ten favorite male actors of all time? Go!</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Who are some of your favorite male actors in Hollywood? Also what are your favorite performances by them?
+I’ll start.
+1.) Daniel Day-Lewis - There Will Be Blood
+2.) Marlon Brando - A Streetcar Named Desire
+3.) Jack Nicholson - One Flew Over the Cuckoo’s Nest
+4.) Al Pacino - Dog Day Afternoon 
+5.) Robert De Niro - Raging Bull
+6.) Joaquin Phoenix - The Master 
+7.) Peter O’Toole - Lawrence of Arabia 
+8.) Leonardo DiCaprio - The Wolf of Wall Street 
+9.) Denzel Washington - Malcolm X 
+10.) Tom Hanks - Cast Away 
+There are plenty of other male actors who I think are just as amazing, but the ones at the top are simply just my personal favorites. What are yours?
+(Edit: Here are some honorable mentions, 
+Philip Seymour Hoffman - Capote 
+Gary Oldman - Sid &amp;amp; Nancy
+Orson Welles - Citizen Kane 
+John Wayne - The Searchers 
+Anthony Hopkins - The Silence of the Lambs
+Toshiro Mifune - Seven Samurai 
+Marcello Mastroianni - 8½ 
+Johnny Depp - Ed Wood 
+Sidney Poitier - A Raisin in the Sun 
+Edward Norton - American History X
+Ian McKellen - 
+The Lord of the Rings: The Fellowship of the Ring
+Geoffrey Rush - Shine 
+Alec Guinness - The Bridge on the River Kwai 
+William Holden - Sunset Boulevard 
+Gene Wilder - Willy Wonka &amp;amp; the Chocolate Factory 
+Ernest Borgnine - Marty 
+Lee J. Cobb - 12 Angry Men 
+Matt Damon - Good Will Hunting
+Colin Firth - A Single Man 
+Paul Newman - The Hustler 
+Brad Pitt - Seven 
+George C. Scott - Patton 
+Henry Fonda - The Grapes of Wrath
+Burt Lancaster - Elmer Gantry 
+Peter Sellers - Dr. Strangelove or: How I Learned to Stop Worrying and Love the Bomb
+Robert Duvall - The Apostle 
+Kevin Spacey - The Usual Suspects
+Jeff Bridges - Crazy Heart 
+Tom Cruise - Born on the Fourth of July 
+Broderick Crawford - All the King’s Men  
+Jack Lemmon - The Apartment 
+Robin Williams - Good Will Hunting 
+Laurence Olivier - Hamlet 
+Jackie Chan - Police Story
+Gene Hackman - The French Connection 
+Dustin Hoffman - The Graduate 
+Gregory Peck - To Kill a Mockingbird 
+Hugh Jackman - Logan 
+James Cagney - White Heat 
+Eddie Murphy - Beverly Hills Cop
+Peter Weller - RoboCop 
+Humphrey Bogart - The Treasure of the Sierra Madre 
+James Stewart - Mr. Smith Goes to Washington 
+Heath Ledger - Brokeback Mountain
+Clint Eastwood - Unforgiven 
+Harrison Ford - The Fugitive 
+Nick Nolte - 48 Hrs. 
+Jake Gyllenhaal - Nightcrawler 
+Steve Carell - Little Miss Sunshine 
+Javier Bardem - No Country for Old Men 
+Ed Harris - The Abyss
+Nicolas Cage - Leaving Las Vegas
+Sean Penn - Dead Man Walking
+Ray Liotta - Goodfellas 
+Paul Giamatti - Sideways 
+Tim Robbins - The Shawshank Redemption 
+Jim Carrey - Eternal Sunshine of the Spotless Mind 
+William Hurt - Kiss of the Spider Woman 
+Morgan Freeman - The Shawshank Redemption
+James Gandolfini - The Sopranos 
+Ethan Hawke - First Reformed 
+Bryan Cranston - Breaking Bad 
+Joe Pesci - Casino 
+Warren Beatty - Reds 
+Casey Affleck - Manchester by the Sea</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>mission_impossible</t>
@@ -479,17 +562,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>What are peoples opinion on Oppenheimer from 1-10?</t>
+          <t>Are we in the calmness part of the storm that's arriving in the form of Barbie on 21st July??</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Calm before the storm! Tik Tock tik tock tik tock..!</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -499,10 +582,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Barbie vs Super Mario Bros vs The Incredibles 2 - Thursday Update</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>MI7 vs Barbenheimer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>As all these 3 movies come out the same period and Oppenheimer stealing MI7’s IMAX screens and PLF theaters do you think the overall box office is hurt by all these movies playing at the same time and if yes how many millions do you think the overall box office will lose ? And who is the biggest loser out of the 3 ?</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -515,17 +602,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>There's an Oppenheimer romcom, from the creator of Monk! I.Q. (1994)</t>
+          <t>Thursday Preview Box-Office Predictions: Barbie (2023) &amp;amp; Oppenheimer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Here’s my predictions:
+- Barbie (2023) (Estimated 4,100 Theaters) - $20-$25 million ($25-$32 million if you include the Barbie Blowout Party early screening on Wednesday) (Thursday Preview Showings begins at 3:00pm)
+- Oppenheimer (Estimated 3,600 Theaters) - $6.5-$8.5 million (Thursday Preview Showings begins at 5:00pm)
+What’s yours?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -535,13 +625,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>‘Oppenheimer’ First Reactions Praise Christopher Nolan’s ‘Most Impressive Work Yet’: A ‘Spectacular Achievement’ and ‘Total Knockout’</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>When did you realize Barbillion would happen?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Barbillion believers, what convinced you that Barbie will hit the 1b club?</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -551,18 +645,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mission: Impossible – Dead Reckoning Part One Over or Under Fallout 154 Million worldwide opening weekend?</t>
+          <t>Barbie releases at the perfect moment in time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[deleted]
-[View Poll](https://www.reddit.com/poll/14vrec7)</t>
+          <t>Barbie is gonna be the no.1 or even the no.2 movie of the year and there are several reasons for it. Most people, even if big parts of Reddit try to deny it, but it is undeniable, that currently the tides are swaying and Moviegoers are tired of the typical girlboss lead character without flaws and Barbie is the perfect counterprogramming. 
+Current trends like bimboism, where women aren't afraid of just enjoying shopping, being ditzy and typical female stuff are becoming huge on social media and Barbie is that basically personified. It's gonna be a safe, nice and fun movie and that is just everything it needs to be. For that reason I do think that movie is gonna have monster legs and Captain Marvel will underperform massively. We're past the age of deconstructing our heroes and make them sad and old and suicidal and we're past the age of serious, stoic, mary sue female protagonists. The masses want human, positive, hopeful characters to follow, not robots and they don't wanna be lectured in every movie
+Sometimes I feel when estimating box office, most people on this sub forget the current mindset of the audience and think too small or too much about how they would wand the world to respond, not how it actually is</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -572,13 +667,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>#Barbie crossed the 300M mark overseas, after grossing 28.9M on THU, just -11.6% drop from WED,for a 320.3M intl. cume over 69 markets. Allied to US 258.4M, hits a 578.7M Global cume at #BoxOffice! 600M+ TONIGHT. 700M+ TOMORROW. Has a Shot at 800M on SUN 1B+ on 3rd weekend LOCKED!</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>Film trilogies that have a good first movie, an even better sequel, and then third is the weakest of the triology?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>I'm thinking 
+The Godfather
+Blade
+Sam Raimi Spider-Man trilogy
+Christopher Nolan's Batman trilogy
+The original Star Wars trilogy (A New Hope/Empire Strikes Back/Return of the Jedi)
+Alien trilogy (Alien/Aliens/Alien^3 )
+Terminator (The Terminator/Terminator 2: Judgment Day/Terminator 3: Rise of the Machines)
+X-Men (X-Men/United/Last Stand)
+X-Men (First Class/Days of Future Past/Apocalypse)
+Ant-Man (Ant-Man/Ant-Man and the Wasp/Quantumania)
+Dead Trilogy (Night of the Living Dead/Dawn of the Dead/Day of the Dead)
+Mariachi  Trilogy (El Mariachi/Desperado/Once Upon A Time In Mexico)
+Evil Dead/Evil Dead 2/Army of Darkness</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -588,10 +700,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Oppenheimer has been rated a 14A in Canada for “Infrequent portrayals of sexual activity - breast and buttock nudity”</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>IMAX 70mm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>I have a quick question about 70mm and Imax films. I want to see the new Oppenheimer in the best way possible. The AMC near me has two showings. One is "Imax Reimagined" and the other is "70mm". Which is better? Is the Imax reimagined still 70mm?
+&amp;amp;#x200B;
+Thanks!</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>oppenheimer</t>
@@ -604,10 +722,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5 Reasons TMNT: Mutant Mayhem Is A Bigger Box Office Hit Than You Realize</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>I was thinking about Sam Rockwell movies, and came up with a list of mixed up movie titles from his filmography.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hitchhiker's Guide to the Galaxy Quest 
+Clownhouse Drunks
+Jerry and Tom; Louis &amp;amp; Frank 
+13 Moons Moon
+Choke Joshua
+Frost/Nixon Gentlemen Broncos 
+Everybody's Fine Pete Smalls is Dead
+The Bad Guys Blaze
+Jack and His Friends Seven Psychopaths 
+Richard Jewell A Single Shot
+Trolls World Tour See How They Run
+Mr. Right The One and Only Ivan 
+Iron Man 2 The Sitter
+Made Snow Angels
+Last Exit To Brooklyn Happy Hell Night
+Teenage Mutant Ninja Turtles In The Soup 
+Basquiat Somebody To Love
+Charlie's Angels Arresting Gena
+Pretzel Heist
+The Green Mile Seeking For Justice Children
+G-Force Digging For Fire
+JoJo Rabbit Poltergeist 
+A Single Shot Better Living Through Chemistry 
+Lawn Dogs Safe Men
+Celebrity Mercy
+Stella Light Sleeper
+Strictly Business Confessions of a Dangerous Mind</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>tmnt</t>
@@ -620,13 +768,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>New Posters for 'Teenage Mutant Ninja Turtles: Mutant Mayhem'</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>Memento is one of Nolan's best</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rewatching Memento made me realize how much I missed the first time. Not gonna talk about any spoilers here but damn Guy Pearce is such an underrated actor &amp;amp; the twist still gets me. If you still haven't watched the movie add it to your watchlist RIGHT NOW!!! Such an incredible movie.
+Btw your favorite Christopher Nolan movie? Mine's Inception, Memento is a close second.</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tmnt</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -636,17 +789,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oppenheimer is fantastic. A masterpiece, but...</t>
+          <t>Who was the best female lead from the Mission Impossible movies (and the worst)?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>I will always say Rebecca Ferguson because she wasn't just a incredible fighter, she was a master spy and I still believe she revitalized the series with her introduction in ROGUE NATION. I remember how hyped the fans were by her character and how good a chemistry she and Tom Cruise had when they worked together. She was strong but also sexy and feminine as well as flawed. 
+Worst is probably Thandie Newton in MI 2. I just find her to be useless and only exists merely as a love interest. Emmanuelle Beart might have been underwritten but I did enjoy her spying scenes, which were subtle but spry, and  Michelle Monaghan started out as a generic girlfriend to someone fighting for her survival in a powerful way in MIII. Paula Patton had that cool fight scene where she beats up Lea Seydoux and actually had a strong arc of her own.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -656,13 +810,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Christopher Nolan says the cast of #Oppenheimer left the premiere to ‘go and write their pickets’ and join the strike</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>With "Barbie" and "Oppenheimer" being noteworthy for how tonally opposite they are, what are other examples of "tonal whiplash" in movies that released next to each other?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>I'm sure this has happened many times in cinema but there is definitely more buzz around Barbie/Oppenheimer particularly due to how different they are. I can't tell if all the memes and discourse are organic or maybe a bit manufactured by marketing teams. Though I've heard people say they'll be seeing them as a double feature just for the novelty of it, which is hilarious. The only other notable example of this that I remember is when Doom Eternal and Animal Crossing released on the same day.</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -672,10 +830,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>In #China’s #BoxOffice, benefited by strong WOM + momentum, #Barbie has her own comeback story, grossing 4.3M on SUN over 27k screenings (+10k), up +53.5% from SAT, more than FRI Op Day + SAT combined,for a 8.2M 3-day opening $920k pre-sales for MON, increased to 29k screenings.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>Snow White 2023 remake info</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Here's everything you should know about the new Disney Live Action remake of their classic Snow White for the next generation of youth and fans:
+Rachel Ziegler is portraying the titular character. 
+Marc Webb is directing the film. 
+Greta Gerwig wrote the screenplay. 
+After Peter Dinklages comments about how he was offended by the portrayal of the dwarves, Disney has gone ahead and changed them in the story to make it more modern by removing the mine working and them being actual dwarves as well. 
+The "Dwarves" are said to be her friends now instead of what they were originally and diverse so they can avoid stereotypes in our climate now. 
+Prince Charming is no longer a character in the story, and instead replaced by a character named Johnathon who will serve the same purpose in it.
+The kiss to awaken Snow White is being replaced for the movie, because it's been deemed offensive. 
+Gal Gadot will be playing the Evil Queen who's jealous of Snow Whites beauty and her own vanity. 
+The movie is being described as a "modern" take on the story.</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -688,12 +859,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>‘Oppenheimer’ First Reactions Praise Christopher Nolan’s ‘Most Impressive Work Yet’: A ‘Spectacular Achievement’ and ‘Total Knockout’</t>
+          <t>Nolan Should Direct the War of the Worlds Musical film</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[deleted]</t>
+          <t>Does it even class as a proper musical ? I'm watching clips of the show on youtube now and like does it not just feel right to say ? I can just see him pulling it off .
+Adding more words here, but i feel like he'd ace the setting and tone i don't think hed go too musical in tone but far enough for it to work, and the worlds been begging for a victorian era War of the Worlds after BBC failed.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -708,19 +880,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Is watching a movie on its opening day much special than watching it on a later date?</t>
+          <t>Is Oppenheimer worth it in a non-IMAX screen?</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>I know, I know it's a silly question but I'm just curious... 
-With the release of the Barbie and Oppenheimer, two of the most anticipated films this year, I've been seeing tons of posts online of people going to see it on its opening day.. but considering that these films are coming to be the biggest films of this year, would it be more special if I watch it on its opening day or is it any different if I watch it on a later date?
-Thank you :))))</t>
+          <t>I was planning to watch Oppenheimer this weekend but I read that the best way to see it is in 70mm since that's how it was shot but there is one (1) singular IMAX screen in my country and I don't even know if it's 70mm so now I'm struggling if I should bother to go see it in IMAX or just go to my regular theater Lol.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -730,13 +900,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mark my words, MI7 will be the best movie of the year and… quite possibly the best action thriller of all time.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>Will Barbie’s marketing budget rival its production budget?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Seeing that the budget for this film is reportedly $100 mil and so some of are thinking it can make it’s money back fairly quickly. But between the traditional press tour (international and domestic), print and social media press runs could that *balloon* the market budget to considerable amount? An amount that could make it’s total budget even upwards of $150 or even much more?</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -746,13 +920,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>The 11-mile long IMAX print of Oppenheimer. It weighs ~600 pounds.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>Can anoy one beat four movies in nine days!</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Like most of you I assume I am an avid cinema goer, it\`s one of my pleasures amd have recently been on a run of going four times in nine days, which for me is a record, can anyone here beat that?
+To make it even better,  all were, in different ways enjoyable, they were
+Barbie with the kids, funny, Ken stole the show!
+Oppenheimer alone, really good, but a bit long, were all the courtroom scenes entirely necessary?
+Talk to me with the wife, Ozzie horror, loved the ending!
+TMNT with the kids, = great animation and funny parts.
+Can anyone beat that for cinema going?</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -762,17 +946,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Giving Tom Cruise his flowers</t>
+          <t>Barbie 2023 is unironically my most anticipated movie of the year, and here's why.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>A question that is asked by many every year, and that question is "What is Your Most Anticipated Movie of this Year?" Which in reality, is a hard question many people have many different taste, and the outcome of the movie is always unknown. Sometimes you lucky and it ends up being good, if not great, others....well, not so much. 
+And this year is no exception, if you were to ask anyone last December or the beginning of 2023 what there most anticipated movies of 2023 was, they probably give an answer like Oppenheimer, or Dune Part 2, or David Finchers The Killer, or that Creator movie with John David Washington, or even something more fanboyish like Mission Impossible: Dead Reckoning Part One, or John Wick Chapter 4, or Guardians of the Galaxy Vol. 3, or Across the Spider-verse, or Indiana Jones and the Dial of Destiny.
+All reasonable answers, at least for the time in Indy 5's case. But for me, it may sound weird. But I have had the exact same answer, ever since I saw the teaser trailer for Greta Gerwigs, Barbie, Starring Margot Robbie and Ryan Gosling. This is my most anticipated movie of 2023. But why? Why is this seemingly run of the mill by the numbers summer blockbuster, based on a property i was honestly never the biggest fan of to begin with? Why this movie? Well....for a few reasons.
+The first reason is, well, obviously, the teaser trailer. Which is literally just a parody of 2001: A Space Oddesy, with footage from the film only being shown in short snippets at the end. It does everything a teaser trailer, not give away the movies plot, if not show little to nothing from the actual film, while still giving an idea of what the tone, feel, and style is going for, in this case, a zanny, colorful, upbeat, and over the top yet still very much lighthearted and in some ways feel good comedy, and while I've been trying to avoid later advertisements to keep myself as surprised as humanly possible going in, from what I've heard, the later ads only confirm what I thought from the first teaser trailer.
+The set photos and official stills prior to the first teaser trailer, also helped alot. I mean, going back at looking at them, they were just so colorful and yet gave very little away. They peaked my interests, especially the ones with Barbie and Ken on the Rollerblades wearing that technicolor jump suits. The other reason I am hyped is just how colorful it looks, and do I even need to explain why, just look at it. Everything about not only screams Barbie, but the colors pop, and you can tell they put a lot of effort in the set design, especially for Barbieland.
+Another thing, is that the premise sounds like the crazy and over the top type of films I like, and let me just say...I love me some over the top concepts, it's the same reason why Barb &amp;amp; Starr is in my top ten favorite movies of 2021, same with The Unbearable Weight of Massive Talent for 2022, and the same reasons why films like The Big Lebowski and Fear and Loathing in Las Vegas are some of my favorite movies of all time. I appreciate films that just have really weird concepts and ideas, and are able to turn them into something truly special, as well something that still resembles a cohesive film, as well as a great film, and Barbie from the looks of it is not different.
+The idea of Barbie leaving to the human learn the truth of her existence and the real world as well as possibly save Barbieland if the Cinemacon description is to be believed sounds so crazy it just make work. Yeah it also seems like a fish out of water, but honestly I'm okay with that, most of of the film from the small glimpses I've seen on the commercials for it on TV seem to still be mostly set in Barbieland anyways, and even if it isn't, just because it's a fish out of water story, doesn't automatically mean it'll be bad or generic or run of the mill/by the numbers. For example, Elf and Enchanted are fish out of water stories, and there still great films in there own right. Barbie looks like it'll be up the same alley as that, and I have faith that it will be good, and the reason is my next point...
+Greta Gerwig. Greta Gerwig, for a premise like this, is the perfect director. Gerwigs films like Lady Bird and Little Women were stories about women. Not just that, but the relationships between women and the struggles they face of trying to adapt to our world and she brings depth to her roles in front of the camera, always finding a balance between dramatic and comedic. This already makes her the perfect director for this type of films premise, a story about Barbie and by extension Ken leaving Barbieland and discovering the real world, only to discover its not as glamorous as she once thought, and the ideas of women now being very different to what it was when Mattel first introduced Barbie, which I think could make an interesting character study.
+Now yes, it will obviously still be played up for laughs, but I imagine it could be a lot like Elf, where it is a family comedy, yes, but it can still be seen as a character study about a person thrown from a almost dream like fantasy land, into our real world and seeing what they get up too. Ironically, Will Ferrell, buddy the Elf himself, will be in this as the CEO of Mattel which I honestly think is pretty funny. Not to mention Gerwig character writing a directing could work wonders for this film. Plus, after Lego Movie proved that you can a movie about almost anything and everything as long as you have passion, love, heart, effort, and care put into it, there's no reason why this movie can't be great, and knowing She directing it, I think it will be.
+Overall, for these reasons, on top of the stellar cast, the fact that we really need happy movies again in times like these, the colorful visuals and set design and wardrobe, and Ryan Gosling playing a character who isn't a sad and depressing loner male. Barbie is my number 1 most anticipated movie of 2023. An unorthodox choice, yes, but for an unorthodox movie that looks so damn good. I say, come on Barbie let's go party.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -782,12 +975,13 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Oppenheimer Format Question</t>
+          <t>BFI IMAX - here are the available seats for Blue Beetle's opening Saturday Vs Oppenheimer. Can you guess which is which?</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>I realise this is maybe pushing it for this sub but I thought this was quite funny. To focus it back on the box office, this is not boding well for BB's opening weekend numbers. 
+To be clear the sold out screening is Oppenheimer and the mostly empty one is BB.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -802,12 +996,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Box Office Fusion: ‘Barbie’ Heads for Staggering $155M-Plus Opening, ‘Oppenheimer’ Eyes $77M - IMDb</t>
+          <t>Is this the year of Hollywood Imploding?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>It's concerning just how many movies are flopping this year. 
+* Flash
+* Antman 3
+* Renfeld
+* 65
+* Dungeons &amp;amp; Dragons
+* Beau Is Afraid
+* Shazam 2
+* Elemental
+* Indiana Jones 5 (yeah, it just came out... but look at the weekend projections, it's not going to cover the budget, much less the marketing costs)
+All of these movies have failed to make their budgets back in theaters. Rumors have it Little Mermaid, Transformers and Fast X *barely* made a profit. 
+Yeah, Spider Verse and Super Mario were hits, Barbie, Mission Impossible and Oppenheimer will likely do quite well. But that's a handful of movies in what looks like a sea of flops. Aquaman 2, Blue Beetle, Marvels, Kraven, Gran Turismo, I think these will all fair poorly.  
+What do you guys think the end result of all this will be? Tighter budgets? Less confidence in pre-existing IPs?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -822,10 +1028,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Greta Gerwig’s BARBIE has just a $100M price tag—finally WB is in the money-well-spent category. Barbie—one of the biggest toy brands ever and at 60+ years still going strong—is gonna have a hot girl summer at the box office, it seems.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>‘Barbie’ Banned In Vietnam Over Map Showing China’s Claims In South China Sea</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Vietnam has banned commercial screenings of Warner Bros’ Barbie due to a scene that depicts a map of the South China Sea with the “nine-dash line” that is contested by the Vietnamese government.</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -838,17 +1048,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Could Barbie be front loaded?</t>
+          <t>The pre-sale of Barbie in Brazil is crazy. That's 16 times more than Fast &amp;amp; Furious 10 pre-orders (biggest domestic debut of the year), The Flash, The Little Mermaid and Spider-Man at the same point.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Barbie is doing like a predicted when the first main trailer came out. It's appealing to all women in a way TLM was supposed to. Great marketing campaign, lots of social media hype, no real backlash from any audiences towards the actual movie. 
-But these big films that appeal to women have been really front loaded in the past like the Twilight saga or 50 Shades Of Grey trilogy.
-Unless there's a lot of memorable quote worthy moments, I don't know about it's legs. It's the kind of thing that will produce a lot of girls nights or curiosity but I'm interested to see how it does after opening weekend. 
-Mission Impossible and Oppenheimer is likely to be more legs oriented but Sound Of Freedom feels like it's getting the most attention out of all of them. WOM has spread past the internet now and that's likely why it's having good holds.
-These three films all appeal to the same audience. Barbie feels like there's more of a rush to see it to feel part of the cultural moment than Mission Impossible or Oppenheimer.
-[View Poll](https://www.reddit.com/poll/14ybot9)</t>
+          <t>Via- BOT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -863,31 +1068,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>'Mission: Impossible - Dead Reckoning Part 1' About to Take the Franchise Off Cruise Control and Into High Gear - (Ticket Sales Tracking 7/9-7/11 )</t>
+          <t>Why is Disney releasing Haunted Mansion in July and not October?</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hi,
-I've been tracking ticket sales for movies recently at my two local NJ AMCs that do fairly well.
-Last week, my **Insidious: the Red Door** tracking got me to a Thurs total of **$3.29M** and Fri total of **$5.74M** for a Thurs+Fri total of **$9.03M.  E**verything here was vastly underestimated compared to the surprisingly high actuals.  For **Joy Ride**, my predictions were also underestimated with a Thurs total of **$.69M** and Fri total of **$1.33M** for a Pre+Thurs+Fri total of **$2.27M.**  While actuals did come over these estimates, this is still a far cry from recouping its budget and the heyday of Summer comedies.
-Don't be confused if you're seeing this post earlier than usual this week.  You can thank Paramount Pictures for moving up **Mission: Impossible - Dead Reckoning Part 1** (jeez, that's a mouthful) to a Wednesday release with Tuesday previews, as well as Monday Early Access screenings, in addition to Sunday Walmart+ sneak previews.  Coming off a box office run for the ages last summer with **Top Gun: Maverick**, Tom Cruise is back with his long Covid-delayed sequel.  After a franchise high, this 27 year-old film series seems to be going strong into its seventh entry.  Since MIDRP1 is releasing on a Wednesday, there are not many identical comps, but given the adult-driven blockbuster nature with strong walk-up potential, we will use **John Wick: Chapter 4**.  I have recorded ticket sales for this Tuesday and Wednesday for 2 Days. The green bars are how much ticket sales increased from day to day.
-https://preview.redd.it/qeomv0zmdgbb1.png?width=2336&amp;amp;format=png&amp;amp;auto=webp&amp;amp;s=452a5cdaa3edf80a96892c334f495032cf871f11
-For its brief, midweek of ticket sales, MIDRP1 showed healthy signs of growth in the days leading up to release with a great surge day of.  Also in the film's benefit is that Tuesday is discount day so more people might have turned out last minute.  With these numbers, raw Tuesday is looking at a preview of **$12.69M** compared to JW:C4.  **Things to note:** MIDRP1 had around **$2M** of earlier previews which JW:C4 did not have and will be added into the eventual total.  For a 20+ year old franchise, this is a phenomenal start and growth from previous entries.  The only concern here is that since it is discount Tuesdays, these numbers could be severely inflated from a normal previews night.  Big surprise, people love a good deal.  What is expected is a strong demand and that can be seen in the theater capacities.  With capacities at M: **10.18%** and EH: **31.78%**, MIDRP1 is showing a healthy turnout, especially against JW:C4, which had capacities of M: **9.96%** and EH: **15.61%.**  While the demand is fairly even at Theater 1, Ethan Hunt and crew show a much stronger outing at Theater 2, indicating a strong older audience turnout given that theater's core demo.  With an older audience, you can expect longevity on the title this weekend and weeks to come.  Still, I just have the feeling Discount Tuesday might be skewing these numbers high.
-https://preview.redd.it/bfhgjylndgbb1.png?width=1918&amp;amp;format=png&amp;amp;auto=webp&amp;amp;s=99ed7eb8c3a51b7ff5514098f171153c93c1323d
-With our limited Wednesday tracking, it is still apparent that this title is starting to surge with a lot more room to grow.  Yet, possibly due to Discount Tuesday, ticket sales for Wednesday are extremely deflated compared to previews.  Currently, MIDRP1 is looking at a raw Wednesday of **$9.72M** compared to JW:C4.  That's right, the opening day gross is less than the previews.  Once again, I think the discount day has a play in here, especially since JW:C4 did not have this advantage, therefore skewing the results.  Nevertheless, we must prevail with the numbers we have.  Even if there might be a Tuesday frontloaded-ness by these numbers, this is still a decent opening with a 5-day weekend ahead of itself to only grow.  Most adults, a prime demo for this title, are still at work on a Wednesday despite the summer season.  The only concerning element is the theater capacity as MIDRP1 is currently at M: **3.13%** and EH: **14.08%.**  At this same period, JW:C4 was at M: **8.89%** and EH: **14.23%.**  While Theater 2 had pretty much the same capacity, Theater 1 for MIDRP1 was significantly lower, potentially showing less demand for action audiences.  Due to its mid-week release, I still feel like a title with this runway has more room for greater walk-ups.
-Overall, this will bring Mission: Impossible - Dead Reckoning Part 1 to an Pre+Tue+Wed opening of **$26.18M**. Hopefully, these numbers are not as preview heavy, but they had to get the mid-week jump for those PLFs.  With Discount Tuesday potentially throwing a wrench in this data, I do advise to treat these numbers with caution.  If these number holds though, we could be looking at a 3-day weekend of **$54M** and a 5-day **$87M** weekend.  Against a **$291M** budget, that certainly isn't the highest mark, but given the power of Tom Cruise, I believe these numbers can go up and could leg out through the rest of the summer.
-I have taken some suggestions to help make this post better. Please comment if you have anymore!
-TL;DR:
-Previews: **$2M**
-Tuesday: **$12.69M -** expect lower
-Wednesday: **$9.72M**
-Opening Day: **$24.41M**</t>
+          <t>I’m sorry, this makes absolutely no sense to me.
+In July, Haunted Mansion will be trampled by Barbie and then have to compete with Teenage Mutant Ninja Turtles five days later. It’s completely sandwiched in.
+But in October, not only would the movie be a much better fit for the Halloween season, but there would be little to no competition for the movie’s demographic. The only family friendly film in that timespan is Paw Patrol, and that’s for far younger kids. Kraven the Hunter is going to be rated R, and families will be looking for an alternative. Disney themselves will have nothing until November with The Marvels and Wish, so there’s zero conflict.
+Am I not seeing something important? Because I just don’t see the logic. I honestly believe this is a $50m+ opening in October, conservatively.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -897,17 +1091,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bill Maher’s Take on ‘Barbie’ Is One of the Lamest Movie Reviews Ever</t>
+          <t>Oppenheimer is Nolan’s worst film.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>**Why Oppenheimer Is a Bad Movie**
+I'm a big fan of Christopher Nolan's films. I love long-form movies, I'm deeply interested in science, and I love film.This is a personal review, I'm not trying to be unbiased - just raw and authentic with my feelings towards the movie. Enjoy or hate as you will:
+Here are my reasons why I think Oppenheimer is a bad movie:
+* **Insane amounts of dry exposition:** Some of it was creatively weaved in, but the majority felt very pace-breaking and unnatural. This is a common trope in Nolan movies, but this is by far the worst hyperbolic version of it. It completely breaks the characters, pacing, and immersion of the reality he is trying to establish. It felt quite lazy and uncreative a lot of the time.
+* **Terrible pacing:** Besides the main hooks in the movie, Ludwig and the editing team made some amazing sequences, but for the most part, it's largely quite boring. However, the hooks of the movie keep you grounded in your seat long enough not to fall asleep when trying to trench through the shallow characters and exposition avalanche, until you come to another hook in the movie which tie you back down in your seat for another avalanche of uncreative exposition.
+* **A lot of the dramatization of the characters and perspective felt very pretentious at times:** Yes, it is profound to harness the strong force, and make a film about it - but there is a subtle self-importance to the film. It's the feeling of an artist knowing they create profound art, and the self awareness seeps into the art and you can feel it. It's hard to explain, but I feel it's tangible in this film. I do enjoy that it teaches newer generations about history and the dangers of humanity with such technology - but it felt self indulgent at times and it's hard to explain; for that I apologize -- I wish I was better with my words. I'm sure someone out there feels what I feel.
+* **CGI dust on the screen completely ruining the continuity of the film and image:** This is obviously something only some people will notice, but it's just absolutely wild that post production thought it was a good idea to have floating particles cover up the beautiful scape of Los Alamos. Cheap, uncreative, and unnecessary CGI atmosphere. Usually these visual effects can blend quite well in majority CGI films, but something so grounded with such high dynamic range, shot on film with this ridiculous atmospheric effect added just breaks the aesthetic of film entirely.
+* **Florence Pugh's character was very shallow and was used uncreatively as an narrative tool:** Yes, we're used to this with many Nolan films, shallow characters used to drive the main characters motivations in an obvious way. You can use your characters more creatively and mask the plot tools that they truly are; have them feel more authentic as characters and not just shallow story telling tools.
+* **Jack Quaid's cameo was an awkward choice of casting:** He says a few lines and plays bongos in the background of a few scenes and whenever I saw him on screen, it felt so wrong. Maybe there was potential to have him fit in another way, but there's something about his acting and presence that is super unconvincing and unfitting. This is likely just a bias that I cannot explain due to association of him in outside media - but there's something tangibly wrong with him being in this film lmao.
+**Some innovations that were great in the movie:**
+* **The way Nolan portrays psychological distress:** Nolan did a great job portraying psychological distress. He used creative editing and physical shaking of the environment abd avoids those typical cheesy visual effects representing trauma in your average movie or Tv drama. It was very creative and arguably innovative.
+* **The hooks in the movie had incredible pacing in synchronicity to Ludwig's score AND ironically great exposition:** In one example: Nolan literally tells the audience when the climax is coming and subverts your expectations of the climax with creative cinematography, editing and sound. (if you've seen the movie, you'll likely understand what I'm talking about)
+* **The acting:** The acting was excellent. Cillian Murphy was particularly good as J. Robert Oppenheimer. And of course the rest of the cast excluding Jack Quaid chameo.
+Overall, I think Oppenheimer is effective in the hooks and even innovative with it's stylistic mechanics in film making, but a terrible movie inbetween. The movie is boring for the most part, and the exposition is lazy and uncreative.
+THE MAIN SUMMARY OF WHY ITS BAD:
+* Lazy plot devicing of characters, exposition overload and bad pacing.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -917,17 +1126,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Oppenheimer also having explosive this week internationally, added another 16M overseas on WED (just a -0.6% drop from TUE) for a 147.2M cume over 78 markets. Added US 117.9M, #ChristopherNolan hits 265.1M Global cume at #BoxOffice. 300M+ on FRI. 400M+ on SUN. 500M+ on 3rd weekend.</t>
+          <t>Jack Reacher, Shooter 2.0?</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>I just watched Jack Reacher for the first time, and it didn't occur to me whilst watching, but afterwards I instantly realised that I watched what was probably the most similar film out there to Shooter.
+Both are based on novels and have a 5 ft 7 1980s/1990s heartthrob in the lead role. The stories are centred on a disgruntled Iraq War veteran who dropped out of society (Swagger with his dog and his guns lives in the middle of the  Alaska wilderness reading about conspiracy theories, Reacher is a drifter who moves from town to town on a minimalist budget and lives as if he's on the run because he is equally paranoid in his own way) that has been contacted by government officials to use their expertise in long range ballistics help figure out how an experienced sniper would commit a crime (Reacher was called to figure out how a recent mass shooting was carried out, Swagger was brought in to predict a potential assassination of the POTUS), during their investigation, both get framed and have to run from the police, being in part set up by the same law enforcement officer who was assisting them earlier (Swagger had the chubby middle aged cop, Reacher had the black detective) and have to take off on a car chase and balance being out of sight whilst being everywhere they need to be.
+Two scenes that really struck me as unusually similar was how there are scenes in both stories where the hero visits a gun shop to help with their investigation and become friends with the owner who's a fellow veteran, and there is a scene where Swagger/Reacher have go to a place where their female friend who's covered for them is being held, and get to talk with the main villain.
+I can't be the only one who thinks that Tom Cruise loved Mark Wahlberg's movie so much that he couldn't resist the opportunity to do something similar.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -937,17 +1149,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>I didn't understand the ending of Oppenheimer (SPOILERS!)</t>
+          <t>Being Remembered As Barbie Is The Biggest Compliment Ever. Margot Robbie As Barbie!</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>An article i wrote about how Margot Robbie being remembered as Barbie is one of the biggest compliments ever.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -957,12 +1169,13 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Are Christopher Nolan's films really "emotionally cold"?</t>
+          <t>Oppenheimer Release Date: Why is it a day early at my local theatre?</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>I'm fairly new to the world of film, and I'm really excited to watch Oppenheimer. I've been eagerly waiting for its release, and I just found out that my local theatre will be screening it on the 20th, a day before the official release date, which is on the 21st. I'm a bit confused about why this is happening and wanted to get some insights from you all.
+Is it common for movies to have early screenings before the official release date? I've noticed that some films are occasionally released early in certain locations or theaters. Is there a particular reason behind this practice?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -977,12 +1190,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Barbie Has Most Ticket Pre-Sales Since Avatar: The Way Of Water</t>
+          <t>Has the summer box office changed your thoughts on what films could do well at the end of the year?</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[deleted]</t>
+          <t>I've been keeping track of what has performed differently to what everyone on the sub predicted. Basically, "What movies was r/boxoffice wrong about?" These are the most obvious ones.So far we've got,
+\- Mario
+\- The Little Mermaid
+\- Across the Spiderverse
+\- The Flash
+\- Indiana Jones and The Dial of Destiny
+\- Mission Impossible
+\- Barbie
+\- Oppenheimer
+What future movies will perform better or worse in comparison to what most are thinking?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -997,17 +1219,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>What are your thoughts About The New TMNT Animated movie.</t>
+          <t>Which movies deserved a sequel we never got?</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Which movies do you think deserved a sequel we never got? I'll go first: "Ferris Bueller: Another Day Off" There was so much potential for a Ferris Bueller franchise. I wonder why they never made another one.
+I also hope they make a third part to The Hustler/The Color of Money movies with Tom Cruise in a role similar to Paul Newman in the sequel.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>tmnt</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1017,17 +1240,18 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Oppenheimer sex scene accused of ‘waging war’ on Hinduism</t>
+          <t>Favourite Ryan Gosling Performance</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Just saw Barbie last night. Ryan Gosling stole the movie. 
+He’s one of my favourite actors. He’s willing to make himself look ridiculous for the sake of the movie (Barbie, The Nice Guys). He can play quiet and brooding (Drive, The Place Beyond The Pines, First Man). He can be a romantic lead (The Notebook, Crazy Stupid Love). He can learn to sing, dance, and play the piano (La La Land). And I’m sure I’ve forgotten a few.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1037,12 +1261,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>If the Barbie movie would have had a black lead as Barbie, like The Little Mermaid has, how do you think it would have done at the global box office compared to the actual movie?</t>
+          <t>Yzma and Kronk from the Emperor’s New Groove (200) have real oppenheimer gf/barbie bf energy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[View Poll](https://www.reddit.com/poll/15madr9)</t>
+          <t>Yzma would love to see a three-hour machination on the nature of nuclear power, and she alone has the cheekbones to match Cillian Murphy. She probably has seen all the other Chris Nolan movies.
+Kronk, on the other hand, would love Barbie. He likes to think critically about the patriarchy and has real “Kenergy.” I
+Emperor’s new groove really predicted barbenheimer. I wish I had the photoshop skills to produce an image of Kronk in a little pink tutu and Yzma in an Oppenheimer suit, but, alas, I cannot.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1057,12 +1283,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Greta Gerwig Said ‘Oh, God No!’ When Asked If ‘Barbie’ Should Use CGI for Actors’ Arched Feet: ‘That’s Terrifying'</t>
+          <t>How much will the month of July 2023 do at the domestic Box Office? An estimate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>**Holdovers**
+Spider-Verse is at 331, I think it can get to 380m in total or so, so 50m for July
+Mermaid is at 277m, I think it can get to over 300m in total, so 20m
+Rise of the Beasts is at 130m, I think it can do 155m, so 25m
+Flash is at 95m, I think it can do 110m, so 15m roughly
+Elemental is at 81m, I think it can do 135m, so 55m seems good
+GOTGV3 has another 5m in the tank, but maybe closer to 10m
+Boogeyman also 5-10m left
+Fast X and Mario are done domestically
+Past Lives is A24 so it's been expanding nicely, could do more but I'll say another 5-10 million as well
+Indy 5 had a 24m OD, and around 58m OW. B+ CS and Holiday weekend so probably 160m finish, so let's say 130m for July.
+Ruby Gillman had a 2.3m OD and probably 7m OW. Could have decent legs as it's a low opening family animation but will get booted off theaters quickly so let's say 22-24m, so 15m for July.
+Asteroid City has made 16m so far, let's say it finishes under 40m so 20m for July
+No Hard Feelings has made 24m, let's say it legs out to 50m so 25m for July
+Adding all these holdovers up gets holdovers to 370-390m total
+**New Releases**
+Insidious: Red Door will have 25 days of release during July (July 7 to 31). Insidious: The Last Key made 64m during it's first 25 days. Insidious chapter 3 made 50m. Insidious chapter 2 made 75m. Insidious 1 made 45m. Averaging it all up gets us to about 60m.
+Joy Ride I have no clue, let's say 30m for June, could be wildly off.
+Dead Reackoning: Part 1 will have 23 days in July (July 9 to 31). Fallout made 178m, Ghost Protocol 175m and Rogue Nation 154m. That averages to 170m. Let's just say 200m to account for a possible small Top Gun boost.
+Oppenheimer will have 11 days in July. 11-day totals for Nolan movies include Interstellar (99m) Inception (149m) and Dunkirk (105m). That averages out to 120m.
+Barbie also has 11 days in June. It has clear breakout movie ingredients. It has 11 days in July. Other female skewing titled include TLM (192m) Beauty and the Beast (326m) Captain Marvel (270m) and Wonder Woman (213m). Average is 250m.
+Haunted Mansion let's say 20m, only 4 days in July.
+Adding all these major releases up gets us to roughly 680m. All the other July movies not listed above could do a combined 30-70m. So 710-750m for new releases. Adding that to the 370-390 for the holdovers gets us to 1.08-1.14b in domestic gross, which is on par with previous July months.
+&amp;amp;#x200B;</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1077,21 +1326,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mission Impossible: Dead Reckoning Part One, ugh</t>
+          <t>My takeaways from this year's box office so far: A hook and WOM are necessary</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Just got done watching on IMAX. 
-The stunts were amazing, cinematography on point, lighting was decent depending on the scene.
-But overall, as a movie, as a story... it was completely underwhelming to me. The whole plot thing is sort of confusing in a mildly interesting enough, but this was ultimately just another overly serious, monotonous cliche. Stringing together action set pieces with boring dialogue delivered in everyone's best Christian Bale batman voice. And ah yes, the entire world at stake again.
-Music too was a major let down, seeing how they advertised 14 hours of music was recorded. It sounded like the same 2 tracks the entire time. Both variations on the original theme but slowed down with braaaaam. 
-This might be my least favorite one. Seeing high 90s on rotten tomatoes, Am I the only one who didn't like it?</t>
+          <t>In 2018-2019 any remote blockbuster could make 500 mil pretty easy. Didn't matter how good you were or what kind of hook you had. 
+Now in the post Covis era that is not enough. Here are box office flops/bombs this year off the top of my head:
+The Flash
+Ant Man 3
+The Haunted Mansion
+Indiana Jones 5
+Movies that will or have struggled to break even:
+Fast X
+Mission Impossible
+Elemental
+Movies that have exceeded Box office expectations
+Mario
+Barbie
+Oppenheimer
+Sound of Freedom
+Guardians 3
+What does the first group have in common:
+No real good hook other than "here is known product please come see." Not good word of mouth
+The second group is interesting. 2/3 are existing IPs with large fanbases. And neither were complete failures but far from box office smashes. Elemental is also not a smash but word of mouth saved it. 
+The last group the successes all have: a good hook (extremely popular character in a film made for fans of that character, excellent marketing campaign, highly popular and prolific director, end of the trilogy) except for Sound of Freedom whcih has excellent word of mouth mixed with controversy (which tends to help). They also all had good word of mouth and Guardians 3 desperately needed it  for a mediocre opening. And all are generally considered very good movies except for Mario which is one of the single most popular brands in the planet. And it wasn't terrible either. 
+So what do you need to be a box office success? A hook, a reason to get people in the seats and/or very good word of mouth. You also need to be at least somewhat good. And the hook can't be "hey we are Disney here is a movie about a ride" or "here is 80 year old Harrison Ford, you like Harrison Ford".</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1101,10 +1366,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nolan, Scorsese and Tarantino are all-time-great directors, but Nolan enjoyed the most box office success between the three of them. What do you think is it that seems to give Nolan even more Box-Office mass appeal compared to Scorsese and Tarantino, who surely are similar good filmmakers?</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>How to get better seats.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>I don't really ever go to the movies so I didn't know how quickly seats can sell out. I'd been looking forward to Oppenheimer for sol long but didn't realize I'd need to buy tickets in advance. I really want to watch the movie in AMC Lincoln square IMAX, so I just bought some tickets for Wednesday Aug 16, but got crap seats. Third row, almost all the way at the side. 
+Is there any way to somehow get better seats like pay extra to people who may have bought multiple to sell? Or should I keep calling the theater to see if anyone has cancelled their seat?</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
           <t>oppenheimer</t>
@@ -1117,13 +1387,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jatinder (charlie): $25M+ THU OS for #Barbie. $35M+ total. Weekend $160M+ likely. I don't have good sources for LATAM and this is doing best there so est. be delayed. FR - $5.3M MEX ~ $4.5M+ AUS - $3.3M BR ~ $3M GER - $2.8M IT - $2.4M ESP - $2M ARG - $1.4M</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>The original MISSION: IMPOSSIBLE is still a good movie but they should have given Kristin Scott Thomas the female lead role. Emmanuelle Beart is, by far, the weakest link in the movie.</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>It's disappointing because Emmanuelle Beart is a good actress and she had the look but in this movie, I found her wooden and forgettable. Kristin Scott Thomas is only in the first act but she made a much stronger impression and her kiss scene with Tom Cruise showed greater chemistry than Beart in her wah wah role.
+I love Mission: Impossible but if there is a big flaw, aside from Vanessa Redgrave not getting to truly sink her teeth as the main villain, it is Beart. Scott Thomasd would have done the most if she had got to play that part. Beart just looked lost and I never even believed she was a two-faced baddie. I could definitely buy that Scott Thomas could go from loving and loyal to glam bitch killer. Missed opportunity.</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1133,12 +1408,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Updated domestic opening weekend totals for Barbenheimer: • BARBIE - $164M • OPPENHEIMER - $82M</t>
+          <t>Can someone please explain the obsession and fan base around “sound of freedom?”</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>I’m really not getting it. In the last week any movie related article I see on Facebook, especially any about Barbie or Oppenheimer the comment section is flooded with people commenting all about sound of freedom and how it’s the superior film in box office and the most important film in history blah blah blah. I’ve never seen such a belligerent die hard fan base for a movie especially one about child sex trafficking, I got called a legit pedophile and attacked online for calling the movie overhyped. I’m just really confused why so many people are massively fan boying over this movie to the point of labelling any non fans pedos?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1153,12 +1428,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>So which movie will win ? Opperheimer or Barbie .I think craze for Opperheimer is going to rise more after the release</t>
+          <t>What's your guys' favorite comedic performance?</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>I believe it was Michael Caine or Jack Lemmon who stated that comedy's harder to execute than drama. And it makes sense, seeing how there's so much to add into it. The script matters, but so does timing and delivery, and if you mess those up then the joke falls flat. Recently, I think Ryan Gosling's performance as Ken in Barbie is a masterpiece of a comedic performance, he just does a great job on the delivery and giving the blank-eyed stare of Ken and perfectly illustrating his dimwitted yet kind-hearted and charming personality. I'd say his performance is only second to my personal favorite, which is Kevin Klein as Otto in A Fish Called Wanda. He's putting his 100% into the role, with every facial expression and line delivery, and it's truly glorious. So what's your personal favorite comedic performance?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1173,10 +1448,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mission: Impossible – Dead Reckoning Part One | mission impossible 7 WATCH AND DOWNLOAD</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>When do you think Paramount is gonna send Dead Reckoning Part 1 to digital PVOD?</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>They’re definitely not waiting as long as they did with Top Gun Maverick. 
+I think very early September if the movie doesn’t cross the 600 mark by mid August</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>mission_impossible</t>
@@ -1189,17 +1469,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>One of only 30 existing 15/70mm IMAX reels of Oppenheimer (and Interstellar below it) in Prague</t>
+          <t>I could really use a collectors help</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>I want all the mission impossible in steelbooks to give to my girlfriend after all we been through. I don’t know movies, but it seems a lot are advertised as a ripoff as a one set. Could you direct me as to what would be the best price for everything and authentic? I will but just the newest one to go along with</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1209,13 +1489,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Asian Barbie - what’s missing in the new movie</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>I think Tom cruise should be considered on the same level as dicaprio and pitt.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cruise is a phenomenal performer. Some of his best films Magnolia, Eyes wide shut, Top Gun, Risky Business, Collateral, Mission impossible. The dude never turns out a bad performance. his dedication to the craft of acting learning how to fly jets, ride helicopters,sky diving etc. the dude is just phenomenal. I think he absolutely should be in the conversations with dicaprio and pitt</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1225,26 +1509,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>I don't think studios will try to set up Barbenheimer 2.0. Here's why:</t>
+          <t>anyone else find oppennheimer's music and editing distracting?</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1
-There are tons of examples of two big films coming out the same day yet there wasn't any viral marketing or increased awareness.  Killers of the Flower Moon and Kraven the Hunter are set to come out on October 6th while Wish and Napoleon are set to come out on November 22 yet basically no one has called attention to this.  
-2 
-Capacity can be a big problem unless the films aren't that big at the box office and the overall weekend gross is low.  Barbie and Oppenheimer may be very limited by screen capacity this weekend so this is an actual issue.  This is especially true for the biggest and most expensive seats (PLF, premium format, bigger auditoriums, etc.).  
-3
-Competition is a problem if the films are too similar but if they are too different then there is no audience crossover.  No crossover in interest will prevent there from being any box office boost at all.  
-4
-Barbenheimer was viral *because* it wasn't created consciously by corporations, it just happened on its own.  Corporate attempt to drive awareness  (corporate memes, social media posts, PR events, etc.) will inevitably fall flat and murder online interest.
-5
-It is a difficult sell to movie studio executives even if Barbenheimer gives a tiny boost to Barbie and Oppenheimer.  Executives don't want to schedule their own films to release on the same day so they would have to find another movie studio and release both of their films together on the same day.  Unless Barbenheimer actually leads to a bunch of ticket sales, I don't see how executives could be convinced to work with another company to cross promote very different films considering that any pre-release problems or delays with one film would negatively affect the other.</t>
+          <t>im a big nolan fan but his style which is loud music playing throughout the film works in action films like interstellar and inception but imo didnt work in this film at all. Being almost purely a dialog based film the loud music made it extremely hard to focus on what they were saying. Also extremely distracting was the editing with the constant scene cuts. Its like it was made for tik tok generation rather than hearing a complete conversation to be able to tune in to what they were saying it would always be a few words than boom scene cut. What the heck kinna shody editing is this, like a 3 hour trailer or fan made film. The editing coupled with the loud constant music and fx made it hard for me to keep engaged and became extremely bored and left 2.5 hours into the film, feeling relieved to get out.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1254,18 +1529,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Oppenheimer nudity</t>
+          <t>I think TMNT Mutant Mayhem has potential to be one of Seth Rogen’s best films in a long time</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Oppenheimer may face plot losses in India due to censorship, impacting its storytelling and creative vision. 
-Does it feel weird to watch a movie with cuts</t>
+          <t>I can see a solid coming of age story in the same vein as Superbad, just told through the Ninja Turtles story… also not as raunchy or adult.
+I feel like having Seth Rogen make a story like this was smart just seeing his history into films about teens and just the youth in general. Even Good Boys was solid imo.
+I think we may have something special, if the early reviews from the Film Festival screening (don’t remember which one) are anything to go by I think we have a solid and entertaining film to look forward to. Think this is his first “kids film” he and Evan Goldberg have produced so I’m interested to see how this goes.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>tmnt</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1275,13 +1551,18 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Oppenheimer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>What’s the next untapped IP?</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>After the massive success of Barbie and Super Mario, Hollywood will surely look to more longstanding beloved pieces of IP that have yet to be fully mined on the big screen.
+What else is out there? If you were running a studio and looking for untapped IP with the potential to really catch on at a massive scale - where would you look?</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1291,10 +1572,30 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>If Asia is not that excited for #Barbie , #Europe’ll eat it up it seems! In #France’s #BoxOffice for instance, the film starring #MargotRobbie grossed spectacular est. 3.2M on 2023’s best WED Opening Day incl previews. Impressive 360k admissions (incl. 90k from TUE previews) 1/2</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>Cue the Outrage: 'Barbie' is the Gayest Film of the Year</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>And I thought Nimona was going to be the gayest film I saw this year...
+I saw Barbie earlier today in a theater packed with every single white woman and gay man that live in my city. I haven't seen a crowd this hyped up for a movie since Endgame. The audience fucking loved this movie and I was right there with them. Barbie as a film is doing so much that it's hard to really take it in. The film is clunky at times especially towards the middle of the film but this actually works to it's benefit in a weird way. Barbie is so flamboyant and over the top that it instantly falls into camp. So the awkward delivery of its central films works because everything else is so direct and in your face, why not this? I have so many thoughts on the film so I'll try to organize them as best as possible here:
+-The Kens collective journey in the film feels like a coming out story. In the beginning, they distilled their identities into obtaining affection from women and then being noticed by other men for having the women. There is this undercurrent of sexual angst and confusion the Kens seem to collectively have that results in them constantly competing for each other or meekly craving for another Ken's approval in the background. Ken bringing patriarchy to Barbieland is the campiest most over the top portrayal of masculinity. It very much feels like what a closeted gay man trying to fit into heterosexual society thinks straight men are like.  Kingsley Ben-Adir's shy twink character always holding sports balls but having zero idea what they're for heightens this affect. Finally the Kens give into their feelings for other Kens, demonstrated by rage that turns into the erotic. Kens are now doing ballet with each other and embracing one other. Stereotypical Ken finally stops tying his worth to possessing women and resolves to discover who he really is. He bequeaths the symbol of the patriarchy to another man, the Ken not so secretly obsessed with him. This is not the only reading of the film and I'm quite sure other people will have less queercentric takes on this, those are valid too. But damn this movie was really gay. 
+-The homoeroticism was inherent to the Kens, both in the movie and the actual doll, from the start and honestly has always been a part of Ken's public image so it would seem strange not to include it. The Kens make threats to 'beach' each other off. One Ken is constantly cowering behind and silently adoring Stereotypical Ken. The Kens seem to care more about showing off for each other and winning the approval and attention of other Kens at times than Barbies. It very much reminded me of the boys in high school who weren't quite sure who they were and couldn't explain why they were inexplicably drawn to other men. The most self-aware Barbie that isn't played by Margot Robbie is played by comedic genius and noted lesbian Kate  McKinnon. She doesn't shy away from not so subtly flirting with Stereotypical Barbie and shows her the path to happiness outside of trying to live up to an unattainable level of perfection. She's the only Barbie who embraces living outside of traditional femininity and she offers up her home as a play for other Barbies off the beaten path and those incredibly gay discontinued Kens. She literally creates a safe space for queerness. 
+-This film feels like 'But I'm a Cheerleader' on steroids. When the Kens were doing their dream ballet on a glowing surface of baby blue and carnation pink, I couldn't help but think of how stereotypical and distilled gender roles were portrayed in the former film. In fact, this film owes a lot to New Queer Cinema in it's exploration of gender roles and male socialization. When the Kens are fully liberated they dress in a way that wouldn't be too off from fashions I've seen at Pride weekends. Their short shorts and crop tops that adorn all of their perfectly sculpted bodies coupled with their outlandish portrayal of masculinity felt like something John Waters would do. The three Kens looking like they just came from a really fun circuit party discussing what they should against the other Kens felt like me and my gay friends deciding what we're doing for the weekend. The queer energy was so strong and it makes entire sense why it's that way. There has always been this undercurrent of homoeroticism that belies ideals about masculinity and the praising of said masculinity. I kept waiting for one Ken to declare his love to the other Ken. Maybe in the sequel. 
+-For as much as the film dissected the male gaze in the real world, I thought it was very interesting how a lot of the sexualized comments delivered to Barbie weren't actually just delivered to her. If you pay attention the lecherous men are absolutely looking at Ken too. He didn't notice it for what it was because of course he wouldn't but I do like how ambiguous it was. You could and I did read it as showing how the male gaze can objectify men too. I've long said if you wanna observe masculinity and men in a vacuum just go to any gayborhood and grab some popcorn. After all, Ken is perfect. He's a chiseled blonde, blue eyed Adonis that many men wish they could be and many men want to be with. There is a lot to say about how our society also promotes unrealistic beauty standards for men as well. Every superhero film actor gently skirts around the topic of PEDs and steroids when asked about their transformations and proport to be completely natural. This film doesn't delve too deeply into that but it would've been interesting to see Ken meet men in the real world who had a negative view of what he represented. Ken has a great arc as it is but I think there was a scene missing where Ken sees that a male dominated world means a lot more is expected of men too. Also I bet the Asian and Black Kens would have had WILDLY different experiences than Stereotypical Ken and I would've been very interested in seeing how they reacted to that. Imagine going from a world where you don't even know what race is to 'put your hands behind your back, you fit a description'. You could've played it for camp but it would've been interesting commentary. The film largely sidesteps race as it relates to gender and I get it. It was written by two white people who probably felt like it wasn't their place to speak for non white men and women. I was definitely satisfied with what we got. 
+-America Ferrera is going to be nominated for Best Supporting Actress at the Oscars which I am not upset by and I'll be glad if she wins. I was not expecting her to be the heart of the film nor to be the one who consistently brought the house down with her speeches. My audience literally burst into applause near the end of her first monologue. Was it about as subtle as a kick to the balls? Yes. Was it preachy? Also yes. Did it fit the tone of the film? Absolutely! Like I said earlier, almost nothing else in this film is shy nor subtle. It is screeching everything at you at all times. Everything presented is its most heightened, exaggerated and distilled version of itself. So why wouldn't the way it communicates its main thesis be this way? I can absolutely understand if you didn't vibe with the way her character was handled. It was very on the nose and in your face, but I thought having Gloria be the one to deprogram the Barbies was a great twist. Her presence in the film helped anchor it emotionally because I really do think that Barbieland is something to be digested in bites. If the third act was Stereotypical Barbie and the other Rogue Barbies doing this alone, it may have gotten very old very fast. Ferrera brought a humanity to the last third of the film that it desperately needed. 
+-Speaking of maximalism, this film wouldn't work at all if the production design, costume design and hairstyling and makeup weren't on point. The first fifteen minutes of the movie where it's just pure 100% cheese was perfection and the look of Barbieland has everything to do with that. They made you want to live in Barbieland which made it all the more disturbing when Ken brings all of that to its knees. The costuming was god-tier. Many of the outfits Barbie wears in the film are inspired by actual outfits the doll has debuted. The costumes also tell a story though. In the beginning, the Barbies are dressed modestly yet still as traditionally feminine as possible. Every Barbie is hyper competent but also still hyperfeminine and none of them stray from that. Kendom sees them lose the modesty but keep the exaggeration of womanhood. After the Barbies are deprogrammed, their costumes are much more casual. We see more Barbies in jeans and sensible shoes. The actual presentation of Barbieland is a neon washed dreamland that has a hint of darkness to it. Parts of it felt like a flash game from the early 2000s. The cartoonish sparkles and dust that appeared whenever the characters did anything, the way they flung through the air like a child playing with dolls, the way Barbie falls over when she's absolutely at her lowest and Weird Barbie's entire existence was a marvel of great effects and editing. The editing in this film did wonders for selling the concept of Barbieland but also Barbie herself. In particular, I'm thinking of the moment where Barbie finally finds Sasha and introduces herself. Barbie is highly saturated and brightly colored yet the real world around her is shades of brown, grey and black. Her hyper realized form of womanhood visually clashes with the down to earth vibe of women in the real world. We see plenty of attractive women in the real world, but none of them are presented as overly glamorous. Only Barbie struts around as a manifestation of unrealistic beauty standards. The film itself pokes fun at this with Helen Mirren's narrator pointing out the folly of casting Margot Robbie as a woman who doesn't represent idealized perfection.
+-The music for this movie was top notch in every respect. The actual score bounced between campy and cartoonish with accented 'aah's' and 'la's'  in the score and the eerie and reflective. Ken had a musical motif that was very unsettling but felt appropriately childish at the same time. As his character began to become distorted by the real world, so did his motif until it exploded into his own rock ballad. The music actually written for this film was equally fantastic. The Lizzo song that goes from fun dance party to existentialist nightmare was glorious. I've heard Dance the Night a lot this summer but seeing it in context was something else to behold. This film did the impossible by getting me to like a Billie Eilish song. And of course, I'm Just Ken is a fun glossy emotional bop that I'm sure will get nominated for an Oscar. 
+-Will Ferrell is perfectly serviceable in this movie. I know that reaction to his inclusion has been mixed but I personally enjoyed his role in the film. I liked the twist that he wasn't just a soulless CEO but he did genuinely care about empowering women, albeit in the most misguided way possible. Him being in the film very much helped amplify the strong mid 2000's vibe this film had going for it. I will admit that the Mattel executives don't add a ton to the plot but they do build upon the themes in that it is possible for men to still uplift and support women, even at their own cost. Ferrell is adamant about returning order to the way things are even thought Ken's Major Domo Gloryhole Bathhouse Whatever is selling like hotcakes. I thought that was a very nice touch. 
+-Ryan Gosling has deservedly gotten much praise for playing Stereotypical Ken but the other actors playing Ken deserve equal praise. Simu Liu plays an excellent jockish bro who has an obsession with another Ken for reasons he can't quite explain. Seeing Kingsley Ben-Adir go from playing the very ruthless and coldblooded Gravik in Secret Invasion to a super bottomy Ken doll hopelessly in love with another Ken doll was a wild ride. Michael Cera was the perfect accent to the sickening sweet performance of traditional gender roles. Also I cannot believe they got Sugar Daddy Ken and Magic Earring Ken into the movie. It was interesting how the Kens that were queer coded the most were the ones to instantly side with the Barbies. It makes sense because the patriarchy doesn't really serve them much if they want to be themselves.  Alan is the only one of him because he knows who he is and thus doesn't want to be a part of Kendom. Alan is essentially what it felt like to be the only openly gay guy in high school in 2005. He even wears a mesh top to the dance party. The Kens fighting on the beach had so many lustful shots of men's perfect muscular bodies heaving against one another and committing acts of athletic prowess. It was so sanitized and childlike yet so inherently horny that it brought me back to being that confused gay boy in the locker rooms back in '04.
+-I appreciated how diverse the Barbies themselves were but they did something interesting with the idea. There's Barbies of every race and ethnicity but this is never brought up nor is race much of a focus at all in this film. There's a trans Barbie but she's treated no differently than any other Barbie. There's a fat Barbie who is treated as if she's just as perfect and beautiful as the other Barbies. There's a wheelchair bound Barbie but she's not relegated to being in the background or on the margins of society. Her disability will never actually be an issue in Barbieland. Each woman while representing a different type of woman is still the most perfect version of that woman. I was expecting us to be in for a real bad time when Ken took over but to my surprise the Barbies of different races, gender identities and disabilities were not treated any different from the white able bodied Barbies in that they were all treated like mindless objects. Kendom was actually quite progressive in that regard although had the Kens continued to rule who knows how that would've eventually shook out. It also underscored how Stereotypical Ken was less malicious but was moreso acting out due to not really knowing his place in the world and still craving Barbie's attention. 
+-Margot Robbie and Ryan Gosling were perfect castings for this film and so much of it works largely due to how invested in it they were. Margot Robbie gets to show off every tool in her acting toolbox for the first time since I, Tonya. It's hilarious that a Barbie film is probably her best and most fleshed out role to date. Ryan Gosling as adorable himbo Ken was one of the many highlights of the movie. They knew exactly what they were doing getting this very masculine and muscular man to act like an immature closeted frat boy while his body was on display for two hours. Ken making me feel all the feels while a bunch of Kens campishly shout 'Boy's Night' was quite an experience. Margot Robbie has been called a human Barbie doll before in her career so casting her as  'the Barbie you think of when you think Barbie' was sublime. She gives a performance that bounces back between pure camp to existentialist horror to straight dramatic on the dime and sometimes within the same scene. 
+-The film's tone was incredibly disjointed and this actually worked for me but I can see how it wouldn't for others. Some people feel as if the story itself was disjointed and I'm gonna pushback on them there. If you view the story in vacuum, all of the beats make absolute sense. How these beats are executed is where things get a little dodgy. The campiness of the first fifteen to twenty minutes juxtaposed with the emotional rollercoaster of the last third of the film was brilliant. It unpacked everything that was set up in the first part of the film and the ending felt satisfying. The middle portion is where it dragged a bit. My personal head cannon is that the board of executives is all Kens that escaped into the real world. These portions in a vacuum work fine but the problem is they're sandwiched between touching moments of Barbie discovering the beauty of life and the symbol of Barbie defending herself from the criticism the brand has received for years. That last portion also feels very much like Mattel slipping the screenwriters some notes because it reads exactly how I'd expect a multinational corporation to defend itself. It's poking fun at consumerism and unrealistic standards for women, both of which it aides and abets, but it's also going to make money hand over fist by selling Kenough sweaters. It's the classic game of playing both sides against the middle to ensure they win no matter what. The intense presentation of the film helps me ignore this problem but I never truly forgot it. There is a lot to be said about how capitalism creates unhealthy beauty standards and portrayals of gender roles. This film respectfully tips its hat to that school of thought but never applies it in earnestness. But why would it? It's still a film about Barbie after all.
+-I did find it somewhat disappointing that the film dropped the plot point about Barbie distraught that she actually hasn't done as much for women as she thought. She never brings this up to the other Barbies nor do they interact with the real world. This was actually disappointing to me. I feel like the various Black Barbies would've definitely had a much different experience than Stereotypical Barbie. President and Writer Barbie might find the Real World to be a much harsher place on multiple levels than Stereotypical Barbie. Doctor Barbie is also an interesting case because the actress is trans but no one addresses that in-universe. Were they a Ken that decided to become a Barbie? Does this imply the existence of transmasc Ken? I wonder how she or Lawyer Barbie would view the real world. That's something worth exploring and showing how while sexism affects all women, there are definitely curves and bends to this. These are all hooks for the sequel I'm quite sure we'll be getting in about four years or whenever the strike ends. 
+-The segments with Ruth Handler's ghost were a great idea that had even better execution. The harsh cut from this girl power theme blaring over Barbie outwitting a small army of businessmen was very well done. The genuine touching moment of Barbie meeting what is essentially God to her kept the film from feeling too cartoonish. It reminded you that this film is still about something at the end of the day. Barbie choosing to be a real woman with all that entails instead of just being an idea was incredibly moving and I did not expect to cry at a Barbie movie. Rhea Pearlman gives probably the best performance of her entire career, again in a fucking Barbie movie. This film surprisingly had a lot to say about humanity and self worth and what it means to be alive. It's hard to believe that touching scenes like this are preceded by Will Ferrell giving us exactly what he's been giving for twenty years and succeeded by Barbie proudly going to a gynecologist. Again that tonal shift will not be everyone's cup of tea, but it was very much mine. 
+Overall, I found Barbie to be a film that was much better than it honestly had any right to be. The performances were top notch. The production value was INSANE, the music was distinct and fun, the messages were timely and also very direct. It has flaws like some unneeded padding and tonally it could've been a lot smoother. But those issues didn't really bring down my experience as a whole. I do wonder about the scores of parents who brought their kids to this only for Barbie to have an existential crisis and loudly declare she doesn't have a vagina. There's gonna be a lot of kids asking their parents about 'what happens when we die?' and 'why are we born?' Good luck y'all. I give it a 9/10. Instant classic.</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -1307,23 +1608,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Could the SAG-AFTRA strike affect new movies for mid-late 2023 releases ahead of premieres?</t>
+          <t>Ranking the films of Christopher Nolan</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>With the Actors are now on strike along with the writers, there are many movies scheduled for mid to late 2023 release could be affected by the strike. Studios are making sure that they have marketing and new trailers and promiding the upcoming movies ahead of its premiere. However, the actors are currently on strike right now as well as the writers. It includes new 2023 movies scheduled for a theatrical release date that could be affected by the ongoing strike. Here’s what could affect the upcoming movies of 2023 ahead of its premiere that could cost them tons of money:
-July: Haunted Mansion
-August: TMNT: Mutant Mayhem, Meg 2: The Trench, Gran Turismo, The Last Voyage of the Demeter, Blue Beetle, Strays.
-September: The Equalizer 3, The Nun 2, My Big Fat Greek Wedding 3, A Haunting in Venice, Expendables 4, Dumb Money, The Creator, Paw Patrol: The Mighty Movie.
-October: Kraven The Hunter, Killers of the Flower Moon, The Exorcist: Believer, Saw X, Five Nights at Freddy’s.
-November: Dune Part Two, The Marvels, The Hunger Games: The Ballad of Songbirds and Snakes, Trolls Band Together, Wish, Napoleon.
-December: Wonka, Aquaman and the Lost Kingdom, Ghostbusters: Afterlife Sequel, Migration, The Color Purple.</t>
+          <t>1. The Dark Knight
+2. Dunkirk
+3. The Prestige
+4. Inception
+5. Memento
+6. Oppenheimer
+7. Batman Begins
+8. Interstellar
+9. The Dark Knight Rises
+10. Tenet
+11. Insomnia
+The first five films are among the 25 best films of this century imo. I liked Oppenheimer but personally found it a little frustrating with how some of the historical characters were handled (namely Harry Truman and Edward Teller, whose portrayals weren't all that fair imo).</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>tmnt</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1333,17 +1639,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>My Barbie Review</t>
+          <t>Name a terribly reviewed or generally poorly received film that is a prime example of being successful simply due to the star of the film</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>I pick Cocktail, a 1988 film about Tom Cruise being a hotshot bartender. It's at a measly 9% on RT. It grossed 170 million worldwide vs a budget of 20 million.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1353,18 +1659,21 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>So, after doing Barbenheimer, were you happy with the order you watched it in?</t>
+          <t>Oppenheimer Format Question</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Just a fun question with no right or wrong answer. I know many people planned on watching the movies back to back. Most (in my feeling) watched Oppenheimer first and then watched Barbie. Some did it the other way around.
-Since I have yet to watch them, which did you pick first and did you enjoy it? Or did you now wish you had done it the other way around?</t>
+          <t>I've been reading a lot about the various formats Oppenheimer will be available in. Unfortunately I don't live very close to a theater showing the 70mm IMAX, but I have the option between IMAX Xenon (or Liemax as some call it) or theatrical 70mm film (5/70).
+Which would you choose and why?
+I'm interested in seeing the film closest to the way Nolan intended it to be seen but not sure which of these formats that would be.
+Obviously 70mm IMAX is the best of both worlds but choosing between the two I'm just not sure.
+TLDR: IMAX Xenon (Liemax) vs Theatrical 70mm film</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1374,15 +1683,51 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>John Cusack has had a pretty solid career and given some great performances. Almost a travesty that he's only been doing schlock B-movies for nearly a decade now</t>
+          <t>Tom Sizemore might be the ultimate 6 degrees connection</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sure he wasn't a Tom Cruise when it came to the box office or a Sean Penn when it came to critical acclaim but he's a young actor who survived the 80s to become a far better actor and work with some well regarded directors in the 90s. I quite respect that he tended to go more for the work than simply do popcorn films. 
- I'm watching The Jack Bull which is nearly 25 years old. Pretty neat seeing him in a Western. I'm sure most folks know him from Say Anything or Better Off Dead but combing through his filmography you see neat films like Being John Malkovich and Grosse Pointe Blank and of course he would do bigger studio films from time to time like Con Air or 2012 but it's performances in films like say an Identity or Runaway Jury or The Grifters or True Colors that make me wonder what exactly happened to him to be doing VOD films now? He clearly showed range over the years of his career. I mean he was never an A-list star but it seemed more like he chose that himself.
-Did he lose roles to Ed Norton/Mark Ruffalo? I know he's quite political but so are a ton of actors. Was he a Val Kilmer type of star that made it difficult to work with?
-&amp;amp;#x200B;</t>
+          <t>He links directly with 
+Al Pacino
+Robert De Niro
+Tom Hanks
+Matt Damon
+Wesley Snipes
+Denzel Washington
+Brad Pitt
+James Gandolfini
+Christopher Walken
+Don Cheadle
+Eric Bana 
+Ewan McGregor 
+Natalie Portman
+Woody Harrelson
+Juliette Lewis
+Don Johnson
+Mickey Rourke
+Keanu Reeves
+Gary Busey 
+Patrick Swayze
+Christian Slater
+Kevin Costner
+Danny Trejo
+Will Smith
+Jon Voight
+Tom Cruise
+Gene Hackman
+Nic Cage
+Sylvester Stallone
+Orlando Bloom
+Jason Lee
+Morgan Freeman
+Barry Pepper
+Thomas Jane
+Donnie Wahlberg
+Antonio Banderas
+Lucy Liu
+…
+I mean, if you never want to get stumped at 6 Degrees ever again, just memorize all the ensemble casts Tom Sizemore has been a part of.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1397,10 +1742,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>According to ThatWalugiDude, some Brazilian theaters are running Barbenheimer double features. Could Oppenheimer experience a significant boost from this since Barbie has huge presales?</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>What are some films that helped you grieve?</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>My husband and I lost our cat yesterday morning after a years long struggle with various health conditions; and while our proclivity for media consumption is at an all time low during this period, eventually we’re going to be diving into movies again (in fact, we bought tickets to “Barbenheimer” weeks ago and are reluctantly going tomorrow), so now we are looking for some recommendations to help us during our grieving process when we eventually can find the focus at home to consume new content again.</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -1413,15 +1762,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>'Oppenheimer' (2023) Review Thread</t>
+          <t>Now that Oppenheimer has an A Cinemascore, what are your domestic total predictions?</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[Rotten Tomatoes](https://www.rottentomatoes.com/m/oppenheimer_2023) \-
-**TOP CRITICS:**
-[Metacritic](https://www.metacritic.com/movie/oppenheimer) \-
-I will update this post as reviews continue to come in.</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1436,17 +1782,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Barbie Double Feature with Shoot the Piano Player (1960)</t>
+          <t>What are the differences to look out for in a 70mm showing compared to digital?</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>About to see my first 70mm (IMAX) showing at Oppenheimer.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1456,17 +1802,18 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mission Impossible 7 box-office collection day 1: Tom Cruise delivers biggest Hollywood opening of the year, actioner rakes in Rs 12 crore in India</t>
+          <t>What’s the difference between IMAX, IMAX with Laser and standard?</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mission Impossible 7 box-office collection day 1: The film is poised to become the first installment of the franchise to make more than Rs 100 crore in India.</t>
+          <t>Went to see the Oppenheimer movie at a standard theater and was really disappointed with the sound.  The sound special effects were way too loud as was the music.  The dialog was muted and at times the music drown out the dialog.  I thought I would see it at an IMAX theater.  The theater I chose in Emeryville, California is an AMC theater which claims to have IMAX with Laser.  The movie visually looked the same as at the standard theater and the sound still sucked.  The dialog was muted, music way too loud and special effects sounds deafening.  Was not enjoyable.  But when I look at the list of IMAX theaters in Wikipedia I find the AMC theater in Emeryville is NOT an IMAX theater.  So now I’m confused.  Is IMAX with Laser some gimmick to fool people into thinking it’s true IMAX? 
+What’s going on?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1476,10 +1823,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Box Office: ‘Barbie’ Dances to $775M Globally, Days Away from Joining Billion-Dollar Club</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>Mission Impossible 7 is the first well received blockbuster I've seen that practically disappeared from the zeitgeist only a week after its release.</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Normally, if a movie is good but doesnt have a strong opening weekend, it can leg out in the following weeks and still do well through word of mouth and positive scores. However with Barbenheimer and Sound of Freedom, it feels like Mission Impossible went away as quickly as it came. Barely anyone seems to be talking about it, no premium screens are showing it and it's box office is steeply declining.
+ All of this would have been expected if it was a bad movie from a dying franchise, but the last three MIs have been increasingly successful and Cruise got a major publicity bump from Top Gun. Its just really really bad timing. Considering how tough it was to get this movie in the first place with the constant shutdowns (and meltdowns) it just seems like a really unlucky movie. Either way this has to be one of the most fascinating moviegoing months in movie history.
+&amp;amp;#x200B;</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -1492,12 +1845,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Critic said Barbie is evil and malicious!</t>
+          <t>Rest of Summer predictions</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Mission Impossible Dead Reckoning-$95 Million 5-day
+$280 Million domestic 
+$910 Million WW
+Should have good WOM and play throughout the summer but losing premium screens after one week probably keeps it from A Billion 
+Barbie 
+$105 Million 3-day
+$275 Million Domestic 
+$675 Million WW
+Could go higher if it also does Great internationally as domestically it will be big
+Oppenheimer 
+$50 Million 3-day
+$175 Domestic
+$410 Million WW
+I don’t feel that Oppenheimer will have wide appeal but Nolan’s fan base and Having IMAX screens for 3 Weeks will help it perform solidly 
+Haunted Mansion 
+$40 Million 3-day
+$150 Million domestic 
+$350 Million WW
+Horror movies have been doing Great recently and The Haunted Mansion ride is well known so it do better then predicted or it could flop opening after Barbie and Oppenheimer I’m leaning towards it doing decently.
+Tmnt Mutant Mayhem 
+$70 Million 5-day
+ $225 Domestic
+  $475 WW
+Feel like this will be the breakout of the August movies as It’s the first Big Animated movie to release since June and TMNT is pretty popular and could have Great legs with no competition for the rest of the summer 
+The Meg 2: The Trench
+$30 Million 3-day
+$120 Domestic
+$400 WW
+Feel like it will do slightly worse Domestically than the 1st one opening against TMNT but it could breakout overseas and preform on par with the first Meg.
+Gran Turismo 
+$12 Million 3-Day
+$45 Million Domestic
+$120 WW
+I don’t think the game is popular enough for it to draw an audience and it doesn’t stand out against the competition.
+The Last Voyage of the Demeter
+ $10 Million 3-day
+  $32 Million Domestic
+  $75 Million WW
+Probably performs similarly to Renfield don’t think audiences are into Dracula films right now.
+Blue Beetle
+$15 Million 3-day
+$65 Million domestic
+$145 Million WW
+Some DC fans might go and watch it but it looks too generic and it’s based off an unknown character so I don’t see a lot of people going to see it</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1512,10 +1908,15 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Barbie is all set to crush that $300M mark at domestic box office tomorrow SAT (day 9) and then break $350M by MON, day 11. It may even do that SUN! AvatarTheWayOfWater needed 14 days to hit $350M while TopGunMaverick needed 15 days.</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>It's Been Great Seeing So Many People At The Cinema This Weekend</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>I work right next to a cinema and there were people going all day out on Friday from the first screenings onwards and even more so when I finished work in the evening. I don't usually go and watch big movies on opening weekend, but my screening of Oppenheimer was the busiest screening I have been to since I saw Parasite a few days after it won the oscar which was a full four years ago now. , and the amount of people who had seen were leaving at the same time after seeing Barbie is something I really have not seen since before the pandemic.   
+Obviously it's an exceptional circumstance, but still great to see that the appetite for going to the cinema is still there after all the uncertainty of the last few years.</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -1528,21 +1929,21 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Bait-&amp;amp;-switch: Movies that are secretly courtrooms dramas</t>
+          <t>2023 Paramount Pictures</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Watching Oppenheimer I was faced with something that has repeatedly annoyed me in other movies: when I see a movie that has at least 1/3 of the film (usually the last 1/3) take place in a courtroom or something like a courtroom. When that’s gonna happen, I want full disclosure beforehand. When it happens I pretty much always feel tricked. 
-Don’t get me wrong, I love a good courtroom drama: A Few Good Men, The Verdict, 12 Angry Men, and so on. But don’t sell me one thing and then give me another. 
-As I mentioned, I was dismayed to find that this was true of Oppenheimer. And it was an even bigger insult because the last 1/3 of the movie, the courtroom stuff, felt utterly superfluous to the story I came to see. 
-I can think of another couple off the top of my head, like Quiz Show, or the most surprising and confusing of all, Bee Movie. Who thought that would be a good idea? “You know what kids like? Courtroom drama!”
-What other movies are secretly courtroom dramas? And did anyone do it well?</t>
+          <t>I’m thinking back to Avatar 2 and 3 before release when many people were thinking it was going to bomb, and a lot of people were saying that the box office of Avatar 3 is really what matters because the two movies were (financially) a package deal (there was a lot of thinking that the 13 year gap would cause Avatar 2 to underperform, but word of mouth of a good Avatar 2 would carry Avatar 3). Now obviously, Avatar 2 made so much money that the box office of Avatar 3 doesn’t really matter as all box office of Avatar 3 will be profit.
+With all that said, MI7 and MI8 are a similar package deal with a 2 film budget of around $500 million. Assuming the profitability number for the combined films is $1.35 billion, and MI7 ends its run with about $550 million (there are some hopes from Tom Cruise that a second wind of IMAX showings will happen in August to increase overall returns to closer to $650 million or more), that would mean MI8 would need to gross $800 million, which isn’t outside the realm of possibility.
+Something that is somewhat related is the box office of Dungeons &amp;amp; Dragons: Honor Among Thieves. With hindsight, that movie did much better than it appears back during release. Very few movies have been runaway successes this year, and the timing of that film could not have been worse (the Open Games License controversy was turning off the hype of the film). I think it would be wise for Paramount to give that film series a second chance as either a sequel film or a TV Show (like a reverse Star Trek TOS, where it started as a TV show and became a movie series). It would be a pity if a great movie was abandoned because of bad circumstances.
+Regarding Transformers/GI Joe, I think that concept is full steam ahead even the Transformers films have been on a downward trend since Transformers: The Last Knight. 
+I believe the $70 million budgeted Teenage Mutant Ninja Turtles: Mutant Mayhem will be profitable for the studio, so maybe it’s time to make an animated Star Trek film with the same feel as The Next Generation/Deep Space Nine era of shows for around the same amount? I mean Star Trek has never been a huge money maker, but if you make it for the right amount, you could squeeze out a nice profit. It could be worth a shot.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1552,17 +1953,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Christopher Nolan tells the story of J. Robert Oppenheimer in a Genuine Way - Write-Up</t>
+          <t>Do you think Wonder Woman (2017) would have been a billion-dollar movie had Batman v Superman not been so poorly received?</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>I feel like it should have done Barbie or Captain Marvel numbers or at least close to them. Wonder Woman is the most iconic female superhero by far and they made a movie that was very well received overall. I remember really enjoying myself when I saw it in theaters and I think most people felt the same way. 
+Barbie had a great marketing campaign that built up a lot of hype and Captain Marvel was aided by the Marvel branding and a cliffhanger from Infinity War that teased the character. But Wonder Woman had to fight a huge uphill battle in the sense that the character was recently introduced in a movie that scored less than 30% on Rotten Tomatoes (which was followed by Suicide Squad that was also very poorly received). 
+Part of me wonders if Wonder Woman would have made more money had it not been connected to any other DC movies at all and had just been released as a standalone thing.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1572,10 +1975,222 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>Oppenheimer Alternative Poster</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Apologies if someone’s already done this better!</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>oppenheimer</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Who feels movie boycotts?</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Hi folks. Sorry if this isn’t the correct community for this question, but I wasn’t really sure where else to ask.
+Between the Writers and SAG strikes I’ve considered ways that I as a person who likes movies but doesn’t actually work in the film industry can show support for the labor.
+My question is for movies that have already been made (e.g. Barbie or Oppenheimer) who feels the pain if I don’t get a ticket and see it in theaters where I otherwise would have?
+Is there a more effective way to communicate to Studios that I as a consumer am unhappy with the way that they are behaving? I know that I am just a small voice, but I’d like to do my part while also hurting the people who need the resources the most the least (other film labor and possibly theater owners).</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>What happened to Mission Impossible Dead reckoning Part 1? Sound of Freedom is Going to Beat It With Literally 1/20th the Budget?</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>How didn MI7 bomb this bad when MI6 Fallout was supposed to be the best in the series? Honestly, I saw MI6 Fallout and wasn't impressed, so could it be that people who saw Fallout thinking that it was the best in the series and heard that Dead reckoning Part I wasn't as good decided to not show up because they knew that Fallout wasn't that good overall?
+Fallout had a solid first half, but it was almost 3 hours long, and the second half of it was pretty lousy and cliched. Maybe moviegoers caught onto this nuance and waited it out for Oppenheimer, Barbie, and Sound of Freedom instead.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Twenty Stand-Out Directors from 2000-2019</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>If you had to pick 20  (American, mainstream) directors who defined 2000-2019 in film, who would they be? I'd honestly want to include TV directors/writers/producers, but to make this not complicated, I'll exclude them from here. David Chase, Alan Taylor, Tim Van Patten, and Vince Gilligan would be on that list, for what it's worth.   
+Peter Jackson, Gore Verbinski , Russo Brothers, Joss Whedon, JJ Abrams , Guillermo Del Toro, Alfonso Cuaron, Christopher Nolan, Alejandro Inarritu, Paul Thomas Anderson, The Coen Brothers, Ridley Scott, Ron Howard, Lord and Miller, Barry Jenkins, Damian Chazelle, Tarantino, Scorcese, Fincher, and Ang Lee.   
+Clearly a lot of franchise directors, but that's just what the industry has mostly been making on the mainstream side of things! Scorcese, Innaritu, and Anderson seem to be able to get stuff made and seen in spite of that, however.   
+Who would you include? Anyone missing? Seems like I missed Soderbergh!   
+&amp;amp;#x200B;</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>oppenheimer</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Can Oppenheimer be the start of a great relationship between Universal and Christopher Nolan?</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>With Oppenheimer earning the best review in Nolan’s career and having a solid box office, should Universal become Nolan’s new studio?
+I hope this happens because given Universal’s the only major willing to take risks with filmmakers these days, I would love to see Nolan at Universal.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>oppenheimer</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Record breaking Weekend for Barbie/Oppenheimer at my AMC.</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>At AMC Disney Springs in Orlando the multiplex has broken the lifetime admittance record that Spider-Man NWH set and passed 10,000 admits with a couple hours left in the night. By the looks of it they weren’t expecting it either as they are understaffed for the crowds. Still incredible to see what a phenomenon this double future is turning into.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Anyone else think Nolan is pissed off will all this Barbieheimer stuff?</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Potentially the most significant film of his career - about the heaviest and most sensitive of subjects, and due to social media, all the marketing has it now associated with a fluffy, throwaway comedy flick literally at the opposite end of the spectrum. Just because they are released on the same day. I would be!</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Barbenheimer resparked my love of going to the theater again!</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>I'll keep things simple. I adore that our Barbie screening wasn't just packed, everybody was also either in pink or wearing wartime era clothing. Kids or adults, it didn't matter, they were leaning on the bit. This was second weekend too, so the hype is strong. This is in the Philippines too, midn you, so the passion for these kinds of movies are really returning worldwide.
+It's just great to see people having fun. Our theater was loud, but in that fun friendly way. Laughing at jokes but staying silent for dramatic scenes.  There's just an ostensibly good vibe about being in a theater again where it doesn't feel like a chore. 
+Maybe it's a one-off, I really don't know. But this was the most fun time going to the theater I've had in a long time, and I hope more movies in the future capture that sort of passion among people again.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>How much do drive-ins contribute to the overall box office?</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>From a cursory glance, there's ~300 drive-ins still operating in the United States. From the ones I've been to, they seem to do pretty decent business.
+But the big question here is: how much do they actually contribute? Are there any white papers about this? Due to the "carload" rates some places do, and the double feature format for value (which...one nearest me has the weirdest double feature of *Sound of Freedom* followed by *Barbie*)... It seems like even a fully loaded venue would bring in lower than average numbers.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>July 21-23 will be the highest grossing weekend of the year.</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Barbie has the potential to open to 100m, and Oppenheimer could open to 50m. With holdovers like Mission Impossible and Insidious, it could easily be the highest grossing weekend. The current highest grossing weekend is April 7-9, with $205 million. If Barbie and Oppenheimer open on the high end of projections, then that is already 150 million, with MI adding atleast 35 million onto that.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>Screen Counts &amp;amp; Holdover Weeks</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Since we have some surprising movies this summer that are over-performing, along with some that are under-performing.  Wanted to provide some insider info about how long these movies will have screens.  
 Most movies are booked with a minimum guarantee on the number of weeks.   Typically 2-3 weeks guaranteed.    This means that a movie booked at 3570 screens.   Will keep all those at least through week 2, and usually through week 3.   
@@ -1585,217 +2200,610 @@
 I would expect this with Barbie too.  It’ll keep screens for a long time.</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>“Teenage Mutant Ninja Turtles: Mutant Mayhem” Brings Fresh Energy, but the Excitement is Short-Lived</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Would Blue Beetle do better if WB tapped into the #BlueBeetleBattalion memes?</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>I think most people are agreed that *Blue Beetle* is heading for a disastrous box office run due to a combination of lack of interest, DC fatigue and poor marketing. However, right now, there is a social media trend of the #BlueBeetleBattalion showing up in droves on opening weekend to launch the movie to a huge opening.
+My question is this: Whilst this trend is obviously meant to be ironic, would the movie perform better if WB embraced the memes in their marketing, especially given that the strikes mean that the actors can't help promote the film? We've seen with the #Gentleminions trend, as well as with *Cocaine Bear*, *M3GAN* and *Barbie*, that social media hype *can* in fact translate to the box office.
+On the other hand, the most obvious recent example of a superhero film that experienced numerous ironic memes about how successful it was is *Morbius*, and Sony embarrassed themselves trying to tap into the ironic hype with the infamous re-release. Perhaps the same fate befalls *Blue Beetle* if WB tries to use the memes to its advantage?</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Will Mario’s current international gross ($773m) be over/under MI7 total?</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MI7 has amazing reviews but with China not being as big as it was pre-covid, im suspecting this film to do around the same as Fallout. Domestic and other countries will probably make up for the loss of China.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>mission_impossible</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Closed caption question</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>So after decades of rock concerts, riding motorcycles and years working in IndyCar my husband is going deaf. My hearing is better but if dialog isn’t clear I don’t always get it all either. Now anytime we watch anything at home we have the closed caption turned on so we can enjoy. We used to go to the movies all the time but after the world wide event we haven’t really been back much. We did see Indiana Jones and both of us struggled with the dialog. We want to see Oppenheimer on the big screen but I’ve seen more than one review mention that the dialog can be very muddy at times, thank you Christopher Nolan. Has anyone had any experience with the CC system in the movie theaters? If so, how does it work there and was it worth using it? We’ll probably go either way but I’d really like to be able to enjoy it as well…thanks for any comments or thoughts!</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>oppenheimer</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Is the WGA strike indirectly affecting box office numbers since no talk show rounds/segments?</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Curious to hear people’s thoughts on how, if at all, the WGA strike may be affecting the box office numbers of the recent movies? Talk shows provide a lot of eyeballs on clips of upcoming release plus there’s often some lazily written free press after the fact if something noteworthy came out of the talk show plug or if some segment went viral (like some of Tom Cruise’s on Fallon have).  
+With no talk shows, that’s presumably extra marketing money that has be spent on publicity and it’s possibly harder to spread the word about new releases. Just wondering what others think about this!</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>mission_impossible</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>I'm bummed Barbenheimer weekend is over.</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Like many of you, I've been anticipating this weekend for over a year, and it was worth the hype surrounding both films. I live in LA and I've never seen such enthusiasm from my non-cinephile friends and strangers over movie-going. Now that they've released and the weekend comes closer to the end I began to think about what's the next thing in the movie world to get excited about, and I'm having a hard time finding that.
+IMO the rest of the year doesn't have too many films that I'm going gaga over like I was with Barbie and Oppenheimer. With the strikes going on, some of these movies could see delays in their releases (per Variety). Not to mention how much of a bummer the situation is with seemingly no end in sight. Even if these films release as scheduled, I don't know if they can match the excitement/vibe that Barbenheimer has brought to theaters.
+Is anyone else thinking the same? Or am I alone here?</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>which movies that’s come out from the past 2 decades (2000-2023) would you consider as classics that define the 21st century</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>I think Inception, The Incredibles, The Wolf of Wall Street, Her, and (possibly) Oppenheimer. The last one because I watched this really great video essay about it.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>oppenheimer</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Can a Barbie like G.I Joe movie work?</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Imagine a radical, paradigm-shifting film where the quintessential G.I. Joe - the symbol of heroism and duty, shaped and polished by the Military-Industrial Complex (MIC) - faces a profound moral crisis. He begins to question the morality of war, the concept of 'justified violence', and the overarching authority of the MIC. This is a G.I. Joe movie that dares to tread the untread path, challenging the norms and conventions of its predecessors.
+The film could open with the protagonist enmeshed in the fabric of the MIC, unquestioningly executing orders. However, a series of unanticipated events shatter his belief system, forcing him to question his lifelong devotion to the military. As he uncovers the manipulative power structures and uncalled-for violence perpetuated by the MIC, his faith in his superiors crumbles, his image of the 'enemy' blurs, and he finds himself alienated in his own world.
+The audience would be taken along the protagonist's journey of questioning, realization, and rebellion. The narrative would delve into his struggle as he attempts to reconcile his love for his country with his growing disdain for the system that controls it. It would showcase his transition from a puppet in the hands of the MIC to an enlightened being who dares to voice his dissent against the systemic exploitation.
+Yet, can such a movie work? The G.I. Joe franchise is deeply rooted in the ethos of patriotic heroism, and a drastic departure from this theme may risk alienating its traditional fan base. On the other hand, it could also open up new avenues for a more mature audience who are willing to engage in discussions about the role of the military, the morality of war, and the MIC's influence.
+However, the challenge lies not just in acceptance, but also in execution. The film needs to balance its critical stance with an engaging narrative that does not compromise on the action and adventure that G.I. Joe is known for. The protagonist's transformation should be gradual and believable, with ample room for character development. The action sequences should not just be gratuitous violence, but rather serve to drive the narrative and underline the movie's central theme.
+In a world increasingly conscious of the horrors of war and the exploitation by power structures, such a G.I. Joe movie could indeed work. It has the potential to inspire dialogue and provoke thought, while keeping viewers engaged with its compelling storyline and thrilling action sequences.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Why are people writing off Killers of the Flower Moon?</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Everywhere I look recently there’s been constant doom and gloom about KotFM. I’m not saying it’s gonna make like 600m worldwide and become a cultural phenomenon, but some of the predictions I’ve seen from it are absurdly low.
+I feel like if Oppenheimer taught us anything about box office, besides the power of internet hype, is that nontraditional movies in this age can still do great, especially considering how strong of a comparison those two films are.
+While Nolan is a bigger box office draw by name alone, Scorsese’s name still holds a ton of prestige, so there’s a similar draw from the directors talent. And unlike Oppenheimer, DiCaprio is a much stronger box office draw by that name alone. I know this is definitely going to be hampered by the SAGAFTRA strike with DiCaprio and De Niro not being able to do press, but the names are still a strong draw and will be even more if the studios come to a resolutions like they are allegedly seeming.
+Both of them are 3 hour historical stories, which is traditionally not a blockbuster genre. Yet Oppenheimer is doing phenomenal.
+If you want another comparison, look at Once Upon a Time in Hollywood. A 3 hour movie that is a genre that traditionally doesn’t appeal to people (a movie about “making movies”) by an acclaimed director staring DiCaprio. That film made almost $400m. Now replace Brad Pitt and Margot Robbie star power with De Niro and Brendan Fraser star power, and give it an even higher critic score. 
+Again, I’m not saying it’s gonna have a Barbie level run. I just strongly disagree with the Babylon level bomb some have been pushing, especially if the Actor’s Strike is resolved.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>The dark knight seems to heavily inspired by monster (anime)?</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Christopher nolan is a great director, i am in no way saying getting inspired for something from something is bad, after watching monster i thought this johan liebert guy kind of resembles the ideologies of joker from the dark knight. But monster came before the dark knight.
+Even some scenes resemble each other from monster and the dark knight, the money burning scene and the library burning scene, the come kill me scene from the dark knight and johan pointing at his head, the protagonist and antagonist dynamics, the ideologies, the ending of the dark knight is the monster's could be ending. The nameless monster story that anna reads is what happens at the end of the dark knight. Batman takes all the blame on him and people turn against him, in the nameless monster tale, the monster finally had a name but no one to call him by that name is a relation to this ending. The excellent planning of both the characters, the way they both manipulate people into completely become evil.
+What do you think?</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>oppenheimer</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>What are some predictions which you got absolutely right this year?</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>This year has been a clusterf*ck of shocks, flops, surprises, and what not....and most of us made so many Ls with our predictions including Me but what is the one which u got the most right? 
+For me I got Fast X and TLM right , and Spiderverse as well..almost everything else, especially MI and Barbenheimer, got wrong...l</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>What makes the difference between great eye acting and simply opening your eyes really wide?</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Hi. I was watching Oppenheimer in cinemas a few days ago, and I was struck by just how good Cillian’s performance was, particularly how much contemplation and struggle he was able to convey with his eyes through an endless, wide eyed stare. However, whenever I try to replicate it by simply opening up my eyes wide, I just end up looking like a deranged try-hard. Yet with one wide eyed stare, Murphy is able to project so much emotions. Which got me wondering: what makes the wide eyed stare that Cillian does so effective, and what makes it convey much more than someone simply opening their eyes really wide and staring without blinking? Somehow, he manages to convey so much with just that one look - what are the nuances behind that?</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>oppenheimer</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Mission Impossible Underperformance</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>It’s looking like Mission Impossible might underperform, but should this be judged this way. I just checked Fallout and the budget was 175 million as opposed to 290 million for the newest one, Covid clearly effected the budget for the newest one. Should the movies performance be judged as an outlier in that case?</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>mission_impossible</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Mario and Barbie are the highlight success stories of 2023. What lessons should studios take away from this?</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Imo it shows that they don't have to constantly mine the same IPs over and over. There are other brands that haven't been in movies as much that are just as big as the likes of Marvel and Star Wars, but their potential on the big screen has not yet been realized.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Call me Crazy but $260M+ for a global debut for Barbie and Oppenheimer doesn’t seem all that impressive to me.</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Dead Reckoning Part 1 did $235M that’s 90% of these two films combined Worldwide opening.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>What is your favourite movie with the word "American" in the title?</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>I recently came to know that there is a new movie coming out by the name of American Fiction, a film adaptation based upon the novel Erasure with the movie being directed by first-time director Cord Jefferson starring actor Jeffrey Wright as the lead.
+The movie premieres at the Toronto International Film Festival in September 2023 and is scheduled to release in theatres this year on 3rd Nov, 2023.
+This apparently got me thinking on how there how many movies we have got over the years which have had included the word 'American' in their titles.
+Infact Mena Suvari the American actress has got not one nor two but a whole informal trilogy of movies with the word 'American' in their titles.
+With the exception of American Pie and American Beauty both in 1999, her third movie was  initially titled as 'Live Virgin' before being retitled to as American Virgin to capitalise on her previous 'American' successes.
+And co-incidentally a Tom Cruise flick from 2017 was formerly known as 'Mena', Suvari's first name before being retitled before release as American Made.
+So which are some of your favourite movies you have watched which accidentally also happened to include the word 'American' in their names?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>mission_impossible</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Halo effect, Nolan and Oppenheimer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Peaking early in one's career can be a challenge for a director. Christopher Nolan is a prime example of this phenomenon, having produced an array of masterpieces early on that set the bar exceedingly high for both himself and others. Movies like "The Prestige," the Batman trilogy, and "Inception" built an unparalleled aura around Nolan, contributing to what is known as the halo effect. However, some of his later movies have been commendable, but they struggled to reach the high standards he had established for himself. 
+Take, for instance, today released "Oppenheimer," a good movie without a doubt, but it doesn't quite achieve the same level of excellence as Nolan's earlier works. The halo effect surrounding the director can sometimes deceive us into perceiving any new release as an instant masterpiece.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>oppenheimer</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Best opening day of 2023 for Barbie in Italy!</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>It beats Mario which opened with opened with 1.256.759 €</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>How much will Barbie do in overseas markets combined? Is 800-million internationally possible?</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>I believe it will get to 600+ this weekend but is 800-million possible?</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>It's no wonder Mission: Impossible (1996) kicked off a mega-franchise</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>I’m watching all the M:I movies in preparation for Dead Reckoning. The first one I haven’t seen in a while, maybe not since it came out (when I was 11). So I’m going to make some scattered observations (spoilers).
+1. Brian De Palma is in blockbuster mode here, but he still finds time for this almost-oedipal psychosexual drama between Ethan Hunt, his mentor Jim Phelps, and Phelps’ wife Claire. It really ups the stakes because Ethan isn’t just trying to find the mole, he’s trying to prove the woman he loves is innocent. And Phelps shoots her just for having feelings for Ethan! That’s some true crime business to have in the middle of a blockbuster spy movie finale!
+2. Ethan Hunt gets dinged for not having much of a personality—something I’d argue is truer for Daniel Craig’s Bond, whose brooding metastasized to overtake all of Bond’s other personality traits—but in this movie, I think there’s an intriguing fission between Tom Cruise’s boy scout persona and the character/world’s dry martini cynicism. He’s noble enough to form a bond with Luther over not allowing collateral damage to the spies on the NOC list, but also enough of a game-player to laugh and joke around with Max, the arms dealer ready and willing to profit off that damage. 
+3. Danny Elfman’s soundtrack can be as samey as ever, with some bits that sound more appropriate to Batman than a spy thriller, but those precision strikes of the Lalo theme still hit HARD.
+4. Casual POV shots here and there. When was the last time you saw those in a blockbuster, not even as a ‘the monster watching someone’ thing?
+5. I love that ‘the killer impossibly manages to vanish’ trope in Phelps’ death is actually a plot point that he faked his death. If he hadn’t, Ethan would’ve run into whoever killed him.
+6. I know we’re used to the ‘rogue agent’ trope now and, if anything, it’s overused—Vin Diesel’s doing it in XXX—but how goddamn cool is the premise that Ethan Hunt is framed for treason, goes on the run, and recruits untrustworthy, disavowed IMF agents to back him up? They wrap it all up in one movie, but you could make an entire Netflix series out of that elevator pitch.
+7. It’s kinda funny to look back on Casino Royale and see that it’s also about a spy with a love interest that turns out to be a traitor but her death still greatly wounds him. Of course, Ethan Hunt actually got over it in the next twenty years.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>mission_impossible</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Hi guys. Is there any reason as to why Paramount did not postpone Mission Impossible Dead Reckoning Part:1 when they knew that Oppenheimer and Barbie are going to release on 21st July and Oppenheimer will take most of the IMAX screens ? Mission Impossible Dead Reckoning Part 1 hardly had 9 days befo</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Re Oppenheimer and Barbie hit the theatres.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Indian Box Office - Week 1 NBOC (GBOC) Oppenheimer - ₹56.75 Cr (₹66.97 Cr) | Barbie - ₹23.76 Cr (₹28.04 Cr)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>EDIT: Oppy crossed ₹100cr in India. ₹101cr Gross  as of y’day 29/07</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TMNT Amimator Conditions</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>This post raises a good question about if TMNT’s low budget meant that the animators were mistreated and underpaid…</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
         <is>
           <t>tmnt</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Barbie over/under $300M opening</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>I feel like it got potential to opening up that big worldwide considering all the decent to great WOM
-so far and all the factors are going for the film too
-[View Poll](https://www.reddit.com/poll/154bwr1)</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Mutant Mayhem Animators…</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>tmnt</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Tom Cruise’s ‘Mission: Impossible — Dead Reckoning Part One’ Delivers $7M in Box Office Previews</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>[deleted]</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>As a former entertainment journalist and PR person I feel like this sub misses one key elements of success?</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>I’ve noticed this around the Barbie movie, but it seems to be a theme in a lot of analysis - there’s this idea that audience are themselves the primary driver of what they go on watch, in way that really undermines ‘influence’.
+Take Barbie for example - I’ve seen people say repeatedly that Greta Gerwig as a name is not the reason for the box office success, because the general audience don’t know she is. While it’s true they don’t know who she is, journalists,  industry peers and influencers certainly know who she is - and these are the sources that trickle down to the public to gain information to a film.
+It’s a bit like hits on the radio - they don’t just happen ‘organically’, there are many gatekeepers who put forward music to the general public, with all sorts of complex industry reasons influencing their decisions.
+Another oft repeated myth is that Twitter has ‘no impact’, because the vast majority of the general audience are not on Twitter. But who is on Twitter? Journalists, influencers and industry movers and shakers - and Twitter discussion among these elite groups has all kinds of effects in the way info is communicated to the public - and in turn, the public often trusts these elite groups/individuals.
+Now don’t get me wrong I’m not saying journalists and influencers are the only or even the main reason films make money - we can clearly see that’s not the case. But PR, and the influence of those seen to have cultural authority does have meaning, and helps to influence buzz, and support momentum.
+ The idea that box office smashes just happen organically like some kind of revolution is a seductive idea, but I don’t think it’s accurate.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>This might be the first year Disney won't have a top 3 DOM film since 2011</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Not counting 2020 obviously. But with Mario, Barbie, and Spider-Verse looking to be the top 3 movies domestically for the rest of the year it seems like it's happening. Unless Marvels really breaks out and outgrosses Spider-Verse, which I don't think anyone expects to happen.
+The top 3 in 2011 were:
+1. ***Harry Potter and the Deathly Hallows Part II*** (381M) 
+2. ***Transformers: Dark of the Moon*** (352M) 
+3. ***The Twilight Saga: Breaking Dawn Part 1*** (281M). 
+The highest grossing Disney film that year was ***Pirates of the Caribbean: On Stranger Tides*** (241M) which was actually number three worldwide that year, but fifth domestically behind ***The Hangover Part II*** (254M).</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>barbie</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Mission: Impossible – Dead Reckoning Part One Question</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>I am going to see it tomorrow and I have one question.
+Before the movie starts and right after the previews are we subjected to a short video with Tom Cruise explaining some stunts and telling us to enjoy the movie? Or a spoiler-filled behind the scenes thing showing all the stunts including the train?
+I really, really hate this stuff. I love Cruise films, and Mission Impossible films too, just not this stuff, its eye rolling..</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
         <is>
           <t>mission_impossible</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Im stuck on the bus and I’m missing the first 30 minutes of Oppenheimer. Fill me in quickly??</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>oppenheimer</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Dead Reckoning at 100% fresh with (currently) 54 reviews in</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr">
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>“Oppenheimer” Is Ultimately a History Channel Movie with Fancy Editing</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Richard Brody is kind of a critic who is very hard to agree with. But he is very compelling in his arguments.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>oppenheimer</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Is Mission Impossible the strongest current franchise?</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Just looking at what’s happened the last year or so, we’ve seen the MCU really stall. Antman and Thor really underperformed and lacked the excitement of previous installments. Not to mention the mixed at best reaction of the Disney Plus slate of programs. 
+The DCU is a mess. The Flash probably was destined to fail but still, I’m not sure anyone could have expected this kind of disaster. 
+Then look at Fast and the diminishing returns, Star Wars burnout and now Indians Jones really falling well below expectations. 
+The hype for Dead Reckoning appears real with 99% on Rotten. I’m hard pressed to think of another IP that has this kind of consistency and reliance at the box office. 
+Curious to see what everyone thinks and what may be the ultimate reason for it. Tia!</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
         <is>
           <t>mission_impossible</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>'Mission: Impossible - Dead Reckoning - Part One' Rotten Tomatoes Verified Audience Score Thread</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>I will continue to update this page as the score changes.
-||**Score**|**Number of Reviews**|**Average Rating**|
-|:-|:-|:-|:-|
-|**Verified Audience**|94%|500+|4.6/5|
-|**All Audience**|93%|1,000+|4.6/5|
-**Verified Audience Score History:**
-* 96% (4.7/5) at 100+
-* 95% (4.7/5) at 250+
-* 94% (4.6/5) at 500+
-[**Rotten Tomatoes**](https://www.rottentomatoes.com/m/mission_impossible_dead_reckoning_part_one): Certified Fresh
-**Critics Consensus:** With world-threatening stakes and epic set pieces to match that massive title, *Mission: Impossible - Dead Reckoning Part One* proves this is still a franchise you should choose to accept.
-||**Score**|**Number of Reviews**|**Average Rating**|
-|:-|:-|:-|:-|
-|**All Critics**|96%|261|8.00/10|
-|**Top Critics**|95%|61|7.90/10|
-[**Metacritic:**](https://www.metacritic.com/movie/mission-impossible-dead-reckoning-part-one) 81 (61 Reviews)
-**SYNOPSIS:**
-In *Mission: Impossible – Dead Reckoning Part One*, Ethan Hunt (Tom Cruise) and his IMF team embark on their most dangerous mission yet: To track down a terrifying new weapon that threatens all of humanity before it falls into the wrong hands. With control of the future and the fate of the world at stake, and dark forces from Ethan's past closing in, a deadly race around the globe begins. Confronted by a mysterious, all-powerful enemy, Ethan is forced to consider that nothing can matter more than his mission – not even the lives of those he cares about most.
-**CAST:**
-* Tom Cruise as Ethan Hunt
-* Hayley Atwell as Grace
-* Ving Rhames as Luther Stickell
-* Simon Pegg as Benji Dunn
-* Rebecca Ferguson as Ilsa Faust
-* Vanessa Kirby as Alanna Mitsopolis
-* Esai Morales as Gabriel
-* Pom Klementieff as Paris
-* Mariela Garriga as Marie
-* Henry Czerny as Eugene Kittridge
-**DIRECTED BY:** Christopher McQuarrie
-**WRITTEN BY:** Christopher McQuarrie &amp;amp; Erik Jendresen
-**BASED ON THE TELEVISION SERIES CREATED BY:** Bruce Geller
-**PRODUCED BY:** Tom Cruise, Christopher McQuarrie
-**EXECUTIVE PRODUCERS:** David Ellison, Dana Goldberg, Don Granger, Tommy Gormley, Chris Brock, Susan E. Novick
-**DIRECTOR OF PHOTOGRAPHY:** Fraser Taggart
-**PRODUCTION DESIGNER:** Gary Freeman
-**EDITED BY:** Eddie Hamilton
-**COSTUME DESIGNER:** Jill Taylor
-**MUSIC BY:** Lorne Balfe
-**CASTING BY:** Mindy Marin
-**RUNTIME:** 163 Minutes
-**RELEASE DATE:** July 12, 2023</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>mission_impossible</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Dead Reckoning fights</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>mission_impossible</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>2023 Oscar Nomination Predictions</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>I know it's a little early but below are my nomination predictions. I'm took *Dune* and *The Color Purple* out because of their likely push to 2024.
 **Best Picture:**
@@ -1843,613 +2851,9 @@
 &amp;amp;#x200B;</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Barbie vs Oppenheimer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>This sub is more r/movies than r/boxoffice and it has hindered the authentic, analytical conversations once seen in this sub.</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Where to begin??
-This sub is flooded with people who are unable to distinguish between what they like and what general audiences like. Yes, you don't like Captain Marvel but you sure as hell love Oppenheimer. Okay, good for you, but it doesn't mean that when you don't look forward to a movie, it means that it'll flop. No, far from that, and that's totally the worst way to 'predict' a box office performance of a movie.
-Also, this sub is a cesspool of negativity that idolises and celebrates box office bombs just because they have a preconceived notion that a movie is terrible based on whatever they've read.
-I mean, just look at what is posted here everyday. Countless articles everyday about The Flash bombing or Indy projects to bomb or Elemental bombs. And even if they are indeed terrible movies (which again many here would not have even watched the movie beforehand before starting their opinions), there is literally no need to repost the same thing over and over again everyday. I mean just take a look at Indy, I guarantee you that everyday, there will be a post about Indy bombing and someone in the comments would say something along the lines of, 'When will Kathleen Kennedy be fired?'
-To bring home by point, this sub should stop hoping or celebrating for movies to bomb just because they 'think' it'll suck rather than actually watching the movie and forming their opinions. And anyway, time and time again has proven that good quality movies does not guarantee high box office numbers. 
-I know this isn't related to the box office but it sure as hell is related to r/boxoffice but the mods can decide whether to take down or lock this thread anyway.
-TLDR; If you're analysing the potential of a movie's box office performance based on feelings, go back to r/movies. Bad movies sometime make bang and good movies sometime flop and that's just the harsh truth, and r/boxoffice isn't mean to be an outlet for you to degrade the movies you hope will flop, but rather an outlet for like-minded people to discuss about the box office seriously.</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>oppenheimer</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>What Barbenheimer Reviving Big-Budget Double Bills Means for Hollywood</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Both movies will be successful, but which of these will be bigger: Oppenheimer’s worldwide total or Barbie’s domestic total?</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>[View Poll](https://www.reddit.com/poll/154huay)</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>#MissionImpossibleDeadReckoning crossed 100M mark at US #BoxOffice after a 5.6M 2nd FRI. Legs hit hard by #Barbenheimer, and the loss of IMAX dropping -61.6% from last pure FRI #TomCruise’s #MI7 hits a 104.8M cume in the US! Eyeing a 20M-23M 2nd 3-day weekend and 63%-58% drop.</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>mission_impossible</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Apparently Fifty Shades of Grey broke the opening weekend record (in admissions) in Poland that used to be held by Shrek the Third. Fifty Shades of Grey's 834k is still a record for Hollywood films. For context, Barbie and Oppenheimer just had big openings but only managed 716k admissions combined</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>June 2023 Recap: 'Spider-Verse' Massive, But Newcomers Disappoint</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>&amp;amp;#x200B;
-https://preview.redd.it/fxvjnpiase9b1.jpg?width=1920&amp;amp;format=pjpg&amp;amp;auto=webp&amp;amp;v=enabled&amp;amp;s=4b9296f92f795f1deeaa45ec4f8b19aa13a8403a
-***Spider-Man: Across the Spider-Verse*** was the champion of June 2023. It will go down as one of the biggest increases for a sequel.
-&amp;amp;#x200B;
-And that's basically where the good news end for the month. The rest of the line-up was a mixed bag; if some didn't break even, others massively flopped.
-&amp;amp;#x200B;
-June 2023 earned a combined $1.003 billion. While that's a 3.6% improvement over the previous June ($968 million), most of the releases here really struggled.
-&amp;amp;#x200B;
-As mentioned, ***Spider-Verse*** led the month with a fantastic $331.8 million. It took it just 9 days to outgross the entire run of the original ***Spider-Verse***. With its holds, it will eventually pass ***Guardians of the Galaxy Vol. 3*** to become the summer's highest grossing film domestically. Worldwide, it has made $575 million, making it Sony Pictures Animations' highest grossing film and almost doubling the original's gross.
-&amp;amp;#x200B;
-In second place, ***The Little Mermaid*** added $138.8 million this month, which takes its domestic total to $277.3 million. Worldwide, it wasn't as strong as domestically, where it has made $507 million. That would be respectable figure... if it wasn't for the $250 million budget. 
-&amp;amp;#x200B;
-In third place, ***Transformers: Rise of the Beasts*** made $131 million. That's already above ***The Last Knight*** and ***Bumblebee***, but that's not saying much. If Paramount was hoping that it would reignite interest in the franchise, it appears that it still has a long way to go, because it's still almost $100 million below the reviled ***Age of Extinction***. Worldwide, it has made $349 million on a $200 million budget, which is even below ***Bumblebee*** ($467 million). It's unclear what Paramount plans going forward, but the future is not looking bright for the franchise.
-&amp;amp;#x200B;
-In fourth place, we find ***The Flash*** with a paltry $95.6 million. Warner Bros. was confident that they had a hit in their hands, and the movie has managed to surprise in all the wrong ways. [It had the fourth worst second weekend drop for a comic book movie (72.5%)](https://redd.it/14jvqqg), and it's heading for another steep drop this weekend. It's behind ***Green Lantern*** by this point and it will keep falling behind it and miss the 2x multiplier. WB may have thought they had the best DC movie since ***The Dark Knight*** so here's another stat: its domestic total will be below what ***The Dark Knight*** did in its first two days ($114 million) in 2008. Worldwide, the movie has made just $218 million, just slightly below its massive $220 million budget. WB may have wished for records, but the monkey's paw made sure it had infamous records.
-&amp;amp;#x200B;
-In fifth place, Pixar's ***Elemental*** has made $80.8 million. That includes its poor $29.6 million opening weekend, which was the second worst in Pixar's history (but worst in sold tickets). With that said, the movie has had great holds throughout the month, managing to even get to #1 on multiple days, thanks to strong word of mouth. With no new animated competition until ***TMNT*** in August, it should continue holding well. Worldwide, it has made $137 million, with South Korea in particular showing strong power. The disadvatange, however, is that the movie will not break even given its $200 million budget.
-&amp;amp;#x200B;
-In sixth place, we find the oldest movie in the top 10, ***Guardians of the Galaxy Vol. 3***, which added $42.7 million to its gross. Adding its May gross, it has made $353.6 million, passing the original movie. The movie has enjoyed strong word of mouth and despite the amount of big movies opening after its debut, it still has yet to drop higher than 48.7% on any weekend. It will hit a 3x multiplier this weekend, making it one of the MCU's leggiest movies. Worldwide, the movie has made a fantastic $833.6 million. 
-&amp;amp;#x200B;
-In seventh place, ***The Boogeyman*** made $39.8 million this month. Surprisingly, the movie has the best legs (3.22x) in the top ten so far, which is impressive considering reviews and word of mouth aren't glowing. Worldwide, it has made $60.6 million. That would be very solid for a horror movie, except for the fact that it cost $35 million. If Disney/20th Century were hoping for something around ***The Black Phone*** or ***Smile***, it appears that it wasn't the case here.
-&amp;amp;#x200B;
-In eighth place, ***Fast X*** added $27.3 million this month. Coupled with the May gross, it has earned $145.1 million. That's not a good figure, especially for a movie that cost a colossal $340 million. Unless it gets to $146.7 million, it will finish with the worst legs in the franchise. In fact, it will finish as the fourth lowest grossing movie in the franchise domestically (second lowest in ticket sales). Luckily, overseas was much more favorable, where it has made $712 million worldwide. But once again, when that figure includes a declining domestic market and $138 million in China, it looks bad with its massive budget. Universal will have to be more careful with the next installment.
-&amp;amp;#x200B;
-In ninth place, ***No Hard Feelings*** made $24 million. It's difficult to really find a comparison with other comedies in the post-pandemic era, as comedies have been declining in theaters for years. Worldwide, it has made $33.5 million. We'll see how much it changes in a month.
-&amp;amp;#x200B;
-***Indiana Jones and the Dial of Destiny*** and ***Ruby Gillman, Teenage Kraken*** released on the very last day, so there's no complete analysis on their runs. Nevertheless, judging by their early debuts, the month ended in more disaster as neither will have a promising or even acceptable run. On their first day, the former earned $24 million, while the latter earned a $2.3 million. Both will rank among their respective studios' biggest bombs.
-&amp;amp;#x200B;
-Now, there were a few bright spots. One of these included Wes Anderson's ***Asteroid City***. On limited release, the movie achieved an extraordinary $142K per-theater average, which is the biggest since 2016. On its wide release, the movie opened with a great $9 million, which is easily Wes Anderson's biggest weekend ever. Through the month, it has made $15.5 million. In not-so-great news, the movie's recent Friday-to-Friday drop (69.2%) is quite steep, which indicates the movie will be more front-loaded than anticipated.
-&amp;amp;#x200B;
-Other newcomers in the month included ***The Blackening*** and ***Past Lives***. ***The Blackening*** has made $13.9 million, against its $5 million budget. ***Past Lives*** made $4.8 million, with almost 90% of that gross coming from limited release. That's already above A24's previous movie, ***You Hurt My Feelings*** ($4.6 million).
-&amp;amp;#x200B;
-All in all, we'll see if July can turn things around.
-#**Other recaps**
-**2023:** **June** | [July](https://redd.it/15ft6mo)</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>tmnt</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Barbie is rated 8.89 out of 10 on the Korean naver website,with female users rating it 9.64 out of 10 and male users rating it 5.55 out of 10 ! ! !</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Oppenheimer was boring and stupid</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>oppenheimer</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Paramount's Mission: Impossible - Dead Reckoning Part One grossed $54.69M this weekend (from 4,327 locations). Total domestic gross stands at $78.49M.</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>mission_impossible</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>The National Association of Theatre Owners is projecting that more than 200,000 moviegoers will attend same-day viewings of "Barbie" and "Oppenheimer."</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Will M:I7 still be profitable? With a $290M budget, it needs $725M worldwide.</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>I think Barbenheimer next weekend, and Sound Of Freedom are hurting it.
-[View Poll](https://www.reddit.com/poll/150ene7)</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>mission impossible 2</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>mission_impossible</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>"Barbie" raised R$ 22,9 million at the box office in Brazil in its debut in theaters, which took place this Thursday. The film has already been watched by 1,18 million Brazilians. It is the highest-grossing opening for a film in Brazil since "Avengers: Endgame", in 2019.</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>‘Oppenheimer’ includes “prolonged full nudity” between Cillian Murphy and Florence Pugh. The love story aspect “is as strong as I’ve ever done,” says Christopher Nolan.</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>oppenheimer</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Barbie product placement is hilarious and terrible</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Am I the only one who thought The Barbie movie was satire?</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>When things were about to improve for #MissionImpossibleDeadReckoning at US #BoxOffice… #TomCruise grossed 2.1M on 3rd THU, just -38.3%, best hold yet. But too late, exhibitors took -1.130 theatres away from #MI7 , what may affect legs. 128.5M US cume! Eyeing a 165M-185M US run.</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>mission_impossible</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Greta Gerwig’s #Barbie has officially hit 1 BILLION at the global box office.</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>'Oppenheimer': No CGI For Explosion Shots, But at What Cost to The Environment?</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>[deleted]</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>oppenheimer</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>GF Booked Oppenheimer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>My partner has just given me surprise tickets to see Oppenheimer on opening night at an Odeon Luxe iSense screening in the UK and, in the most self centred way possible, I'm a bit mortified that we wont be seeing it in iMax. 
-How has everyone's experience been with Odeon iSense? Does the non-iMax aspect ratio really affect the screening? How is the audio? Would your recommend seeing such a huge release in IMax? 
-I'm so excited for this film and just worried I need to rebook the screening! 
-Cheers!</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>oppenheimer</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Revisiting Heath Ledger + Christopher Nolan</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Saw Oppenheimer in 70mm yesterday and I’m still reeling from how good it is. Personally, I think Christopher Nolan has cemented himself as all-time great director, overtaking folks like Tarantino (and I was a huge QT fan) - especially if he sweeps awards season this year. 
-Seeing how Nolan has his roster of actors to help him tell his stories, I can’t help but think of how Ledger would fit in his films if he were alive today. What roles could you see Ledger in post-TDK?
-In Oppenheimer, maybe he could have done well as Groves (Damon) or Pash (Affleck). In Dunkirk probably could have been a solid pilot opposite Hardy. I haven’t seen Tenet yet so couldn’t say anything there.
-Thoughts?</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>oppenheimer</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Very belated question about the logic of Tenet</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>So with Oppenheimer out I was thinking back to Nolan movies and I can't remember how Tenet worked, and it is really bugging me. 
-So my recollection is that at the beginning of the film, the protag is moving forward in time, and as viewers we are watching that a fairly standard flow as well.
-In the lab scene where the main mechanic is explained, they do some examples with bullets. 
-When protag "fires" at the wall, he's dealing with inverted bullets, so from his and the viewers perspective, the bullets move "backwards" in time and return to the gun. 
-But then what? Shouldn't those bullets *keep* moving "backwards" relative to the protag? Do they explain that at all? I can't remember for the life of me. 
-My vague recollection is that the mechanic kind of worked but came apart if you picked at it too hard, but maybe I'm just forgetting key rules.</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>oppenheimer</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>After Mario and Barbie, what big IPs mostly unexplored in theatrical movies could go big if they did?</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Barbenheimer review.</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Well, guys, I did it. I saw both Barbie and Oppenheimer in the movie theatre back-to-back. (Barbie first, if you ask.) In the same hall, no less.
-Here's how I'll do the review: For each movie, first I will review it on its own, and then I'll review it in the context of the Barbenheimer double feature.
-So, here we go.
-**Barbie.**
-**Review on its own:** It turned out to be somewhat more meaningful than I had expected it to be. The plot is of the same kind as that of the Lego movie. Although, some parts I found a little cringe, especially the beginning. I reckon that might have been the whole point, but still.
-**Review in the context of** ***Barbenheimer:*** We were all anticipating this movie to be completely goofy and over-the-top, just to contrast Oppenheimer in every way. And, well, in that part, it was successful.
-**Oppenheimer.**
-**Review on its own:** Brilliant. Although, the pacing might have been a little bit too fast, which is not something I would do in a movie set in the 1940s. (But that's just me.) The moment the bomb went off was epic. (Wait...)
-**Review in the context of** ***Barbenheimer:*** On the subject of Oppenheimer, from Nolan, we were expecting nothing more than a completely serious film, especially in the contrast of what we expected from Barbie. And in that compartment, Oppenheimer delivered.</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>barbie</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>What part of Oppenheimer are you most excited about?</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>oppenheimer</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Simple "Movie Format" guide for Oppenheimer movie goers:</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>oppenheimer</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Does Warren Theater still do the pre-movie light shows? Do they have one for Oppenheimer?</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>oppenheimer</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Am I the only one that though Oppenheimer was complete trash</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>[removed]</t>
-        </is>
-      </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2459,10 +2863,14 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Will #Barbie cross 1B? Still early for that, and as always I’ll put my first projections out on its 2nd weekend this SUN But ok, *IF* current trend holds, #Barbie would hit 700M at Global #BoxOffice this SUN. *IF* so, then the 1B mark would be locked &amp;amp; crossed by its 3rd week!</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>Barbie vs Mario - Weekend 2 Int’I Markets Comparison</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Sources: twitter.com/BORReport, twitter.com/TaiwanBoxOffice</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -2475,10 +2883,14 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>$21m+ for Barbie and $10m+ for Oppenheimer on Thursday.</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>Oppenheimer: Nuclear Destruction</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>So I had the privilege of watching this three hour nuclear odyssey, on opening day &amp;amp; chose it over Barbie. Because history will always triumph, over fiction. I was speechless, after it ended. Because this is cinema done right. The storytelling, regarding the Manhattan Project &amp;amp; the three years, of construction. 4,000 personnel working tirelessly, in a race against the Russians &amp;amp; the Nazi's. All overseen, by the genius &amp;amp; the sorrow of one J Robert Oppenheimer. Who after his creation, truly became known by his moniker. Destroyer Of Worlds. The acting was tremendous, Cillian Murphy &amp;amp; Robert Downey Jr were truly unreal &amp;amp; the screenplay, is one of my favourites ever. What did everyone else think &amp;amp; like, about the film &amp;amp; did you see it first, or Barbie first?</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -2491,13 +2903,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Oppenheimer Director Christopher Nolan Draws Parallels to AI Danger</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>I’m going to Cinema on Barbenheimer day ALONE</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>this is my first time going to the cinema alone and i really want to know is it something wonderful or just mehh experience.
+Normally i would go out with my friends but something’s telling me that going there alone will cure my loneliness (paradox, lol) I’ve heard before that watching the silver screen alone is pretty satisfying and now i want to experience it myself.
+are there any cool things i can do alone there?</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -2507,17 +2925,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Oppenheimer</t>
+          <t>Which actor and actress do you think is having a great year so far in 2023?</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>I have two options for seeing Oppenheimer while I'm back home. Crap seats in a 70mm IMAX screening or good seats in a pretty decently sized, normal screen at my local multiplex. Which would you go for? I kind of feel like the 70mm is an exceptionally rare opportunity, but I don't know if the viewing experience would actually end up being better if I'm staring directly upwards or to the side for three hours.</t>
+          <t>For me, Pedro Pascal even though he's been industry for a quite a while but the last of us hbo series which came out back in January 2023 has pretty much made him a household name. Now he's getting even more roles for movies and shows. Even Ayo Edebiri who has five films that is being released in one year 2023 like Theater Camp, Across the Spider Verse, Bottoms, Teenage Mutant Ninja Turtles Mutant Mayhem, and The Sweet East. I know we are are halfway throughout the year right now and it got me thinking which actor and actress do you think is having the best year in 2023 so far?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>tmnt</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -2527,12 +2945,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Barbie gratuitement</t>
+          <t>Does Barbie’s success mean that right’s attacks for being “woke” is not a significant factor for box office?</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Multiple movies have been attacked by  the right as being woke. Many of these movies also did not have any significant box office success. Since these movies had other problems such as quality or Disney’s idiotic early dump to streaming strategy, the impact of attacks was not certain. Now that Barbie has been attacked as well and is breaking box office records, can we conclude that these attacks do not have significant impact on box office?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2547,10 +2965,14 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>‘Barbie’ Oscar Dilemma: Warner Bros. Weighs Original or Adapted Screenplay Consideration</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>Barbenheimer proves the internet matters</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>This sub has the tendency to write off internet trends and buzz as not being real life but the Barbenheimer meme which was born from Twitter and TikTok actually posted substantial results. We have already seen internet buzz translate to real money with Mario, M3GAN, and Minions as well.</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -2563,18 +2985,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>The 11-mile long IMAX print of Christopher Nolan’s ‘OPPENHEIMER’.</t>
+          <t>My theaters numbers for today. BARBIE is our biggest opening day ever (theater has been open since 2002). Oppenheimer has a pretty good start and very strong hold for Sound of Freedom. Everything else are second choices for sell out from Barbie. [see comparison in comments]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Source:
-https://twitter.com/DiscussingFilm/status/1677074487261511680?t=_2AJr_FZQ0e9DRxBz_ANQA&amp;amp;s=19</t>
+          <t>I wanted to share this because BARBIE is the #1 opening day EVER for my theater by quite the margin. Listed below are recent blockbuster opening days. I haven’t posted in recent weeks because I discourage any political commentary for Sound of Freedom. It’s all about the numbers, not about the movies or actors involved themselves. Everything else did respectable numbers because people got sold out of Barbie.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -2584,14 +3005,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Barbie Is Legit Great Loved It</t>
+          <t>Wild Predictions for 2024 and beyond I’m posting to look back on in the future</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Just got out of the theatre in New Zealand. 
- 44 yo male nt in expected audience. 
- Throughly enjoyed it. Very clever, brilliant  execution. Can see what the hype is about.</t>
+          <t>This year’s been weird and next year will be even weirder as the fallout of the WGA and SAGAFTRA strike occurs. I just wanna make some predictions, some off the wall and some less so, and come back to them in the future.
+-Inside Out 2 and Kung Fu Panda 4 make more than Beyond the Spiderverse (in the scenario they come out in the same year)
+-Sony will announce The Amazing Spider-Man 3 sometime soon after Madame Web flops financially
+-Mickey 17 makes more than Snow White
+-Warner Brothers will release an extended cut version of Barbie after its nominations from The Academy come out
+-Garfield does suspiciously well internationally
+-Deadpool 3 will be insanely front loaded
+-Ballerina makes between John Wick 3 and 4’s gross
+-Despicable Me 4 is the highest grossing film of the year
+-There will be an ironic internet craze similar to Morbius about Mufasa: The Lion King (which will also get a rotten tomatometer score)
+-Beetlejuice 2 doesn’t do great in the box office but becomes a massive streaming hit
+-Foile à Deux isn’t nominated nearly as much as the first for Academy awards, but becomes the highest grossing R rated film of all time</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2606,12 +3036,13 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Have people experienced problems at Oppenheimer IMAX screenings?</t>
+          <t>Oppenheimer nudity</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Oppenheimer may face plot losses in India due to censorship, impacting its storytelling and creative vision. 
+Does it feel weird to watch a movie with cuts</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2626,18 +3057,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Oppenheimer R Rating</t>
+          <t>Tom Cruise and Scientology. Thoughts?</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>So I’m wondering if i can take my 12 year old son to see this. We were very excited about it but I’ve heard there were some “graphic” sex scenes that lasted a long time. I’m fine with some nudity and sex  but i don’t want to sit through Monsters Ball with my kid. Can someone who has seen it give me a realistic sense of how much sex and nudity, hire graphic it is and more importantly for how long it lasts?
-Thanks in advance.</t>
+          <t>To get this out of the way- if this topic is out of bounds for this subreddit, I can delete it, no biggie. I find it kinda interesting personally though.
+For starters- I think Tom Cruise is one of the best action film stars at this point in time. How many actors actually do their own crazy stunts at this level now?
+My one gripe with Tom though- like many have as well is his contributions to Scientology- as possibly the highest profile figure there. I don't care what people do in their private lives but like it's been documented in many places- Scientology actively ruins people's lives, especially anyone that dares speak out on them.
+So with all that preamble- I wonder if some point maybe when Tom is too old to keep doing movies like he does today- that reporters should start calling him put and asking about it interviews?  (Not sure what else you can do)
+It might seem silly but I remember one of the Smallville actresses ended up getting into trouble for being involved in a sex cult. Not saying this is as bad- but it's certainly a cult to say the least.
+Anyway, what do you think- none of our business, Tom should face some sort of public backlash at some point for his pro option of the cult group, think this topic is stupid, etc?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -2647,23 +3082,18 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>This year will likely be the first time in years that a non-franchise, non-animated movie will be in the year-end Top-10 at the worldwide Box Office</t>
+          <t>Barbie in the Middle East ?</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>With a strong 170-180M weekend opening and likely good legs ahead, Oppenheimer is on course to smash into the Top-10 of the 2023 worldwide Box Office.
-So what do I mean with „non-franchise“ movies? Obviously all sequels, prequels, remakes, comic book adaptions are franchises. In terms of book to movie adaptions, those can be franchises, but don’t have to be. If the book has a big cult following, or many book-sequels etc, it would be a franchise (for example a lot of fantasy stuff, like Harry Potter etc), but other book adaptions (for example Killers of the Flower Moon) are not „franchises“. Also I don’t consider movies like Bohemian Rapsody „non-franchise“, because famous bands and famous singers like Queen, Freddie Mercury, ABBA („Mamma Mia“) etc are kind of franchises in itself. That’s not „non-franchise“.
-Also, I don’t take chinese movies into account, who sometimes break into the top-10 worldwide Box Office, and who are for the chinese market only. Also excluding 2020, because in that Covid year studios didn’t release their franchise blockbusters.
-That being said, Oppenheimer will likely be the first time since 2015 that a non-franchise movie will finish in the year-end Top-10 (2015 „The Martian“ was #10 at the global box office). So the first time in 8 years!
-But it would be if Oppenheimer breaks into the top-5 at the global Box Office (which isn’t out of reach) that Nolan would enter legendary territory. After the mid-2000s, non-franchise movies in the Top-5 at the global Box Office died out, with 2012 (2009) and Inception (2010) being the last two movies to achieve that feat. Oppenheimer now could finally break that 13-year barrier.
-To put that into perspective: The last time Spielberg reached the Top-5 with a non-franchise movie was in 1998 („Saving Private Ryan“), while Tarantino and Scorsese never achieved that feat. Nolan did it once until now („Inception“, 2010, the last time anyone did it).
-Nolan turning the clocks back in Hollywood, in bringing non-franchise movies back into the list of highest grossing movies of the year!</t>
+          <t>I'm curious to know how the Barbie movie is being received in the Middle East considering women's rights in some regions. It's possible the movie is undergoing an edit and later release for some countries like Saudi Arabia, United Arab Emirates, Kuwait and Egypt. Is that true ?
+Any boxoffice followers from those regions with any information?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -2673,17 +3103,141 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Don't understand why everyone says Cruise is the last movie star/box office draw</t>
+          <t>In China Barbie in 5th grossed $7.23M(-11%)/$25M its 2nd weekend. Creation Of The Gods repeats 1st with $57.12M(+35%)/$154M. One and Only opens in 2nd with $35.51/$53.34M ahead of 30,000 Miles From Chang’an $22.51M(-43%)/208M and NSN $11.8M(-41%)/$281M. Meg 2 passes $2.5M in opening day pre-sales</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>I'm not being a hater, I think he kinda has maybe the most impressive resume for an actor maybe ever? he kinda hads the Tom Brady thing going where even his haters just have to respect his longevity. But besides a sequel to his first hit, and a bunch of Mission Impossible movies, his career over the last two decades isn't really crazy impressive. I don't understand how people could think its more impressive than what leo dicaprio has done, having so much success with mostly R-rated dramas. And even though they aren't actors, I'd say Nolan and Cameron are both bigger draws than Cruise as well at this point.</t>
+          <t>***
+#Weekend Box Office (July 28-30th 2023)
+Creation of the Gods Part 1 continues its impressive run increasing a nice +35% of its opening FRI-SUN gross. Even if we account the full 4 day opening + early previews gross of $53M it still managed to beat it this weekend. One and Only after a good Sunday pulls a respectable opening weekend. Both NSN and 30,000 Miles From Chang’an continue to hold well as does Barbie. 
+|# | Movie                 |Gross| %LW|Total Gross| Weekends
+:----------- |:-----------|:-----------:|:-----------:|:-----------:|:-----------:|:-----------:|:-----------:|:-----------:|:-----------:|:-----------:
+1| Creation Of The Gods Part I    |$57.12M          |+35%   |$154.01M  |2
+2| One and Only(release)   |$35.51M           |/      |$53.34M   |1
+3| 30,000 Miles From Chang’an|$22.51M        |-43%   |$208.22M  |4
+4| Never Say Never         |$11.86M          |-41%   |$280.77M  |6
+5| Barbie                  |$7.23M            |-10%   |$24.94M   |4
+6| Oh My School            |$3.63M           |-42%   |$41.38M   |4
+7| MI7:Dead Reckoning      |$2.22M           |-56%   |$45.83M   |3 
+8| Wonder Family           |$2.07M           |-93%   |$39.85M   |2
+9| Lost In The Stars       |$1.64M           |-58%   |$483.76M  |6 
+---
+#Daily Box Office (30th of July 2023)
+Creation Of The Gods Part I continues to dominate on Sunday. Nothing even close to it. One and Only does better than expected as many movies benefit from getting some screenings back and increase nicely from yesterday.
+|# | Movie                 |Gross|%YD| %LW|Screenings|Admisions(Today)|Total Gross|Projected Total Gross|
+:----------- |:-----------|:-----------:|:-----------:|:-----------:|:-----------:|:-----------:|:-----------:|:-----------:|
+1| Creation Of The Gods       |$21.67M |-3%   |+20% |98977 |3.6M  |$154.01M |$334M
+2| One And Only               |$12.46M |-2%   |/    |82104 |2.1M  |$53.34M  |$165M
+3| 30,000 Miles From Chang’an |$8.66M  |-4%   |-51% |58000 |1.4M  |$208.22M |$256M
+4| Never Say Never            |$5.07M  |+21%  |-41% |39797 |0.89M |$280.77M |$314M
+5| Barbie                     |$2.56M  |-9%   |-39% |26893 |0.50M |$24.94M  |$36M
+6| Oh my School               |$1.57M  |+25%  |-46% |17982 |0.28M |$41.38M  |$49M
+7| MI7:Dead Reckoning         |$0.94M  |+11%  |-55% |6017  |0.16M |$45.83M  |$50M
+8| Wonder Family              |$0.74M  |-3%   |-90% |11775 |0.13M |$39.85M  |$43M
+9| Lost In The Stars          |$0.71M  |+30%  |-58% |10159 |0.12M |$483.76M |$493M 
+*YD=Yesterday, LW=Last Week
+---
+###**Barbie**
+A very solid 2nd weekend of $7.23M sees barbie continue its run towards the high $30's. Even so total projections decrease to $36M of what is expected to be more normal drops going forward into the week and Meg 2's release next weekend.
+It has passed Mario's total gross today and will pass Flash tomorrow.
+|#|FRI|SAT |SUN |MON|TUE|WED|THU|Total
+:-----------:|:-----------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|
+First Week|$1.16M|$2.73M|$4.18M|$2.90M|$2.68M|$2.41M|$2.05M|$18.11M
+Second Week|$1.84M|$2.83M|$2.56M|/|/|/|/|$24.94M
+|%± LW|+60%|+4%|-39%|/|/|/|/|/|
+**Scheduled showings update for Barbie for the next few days:**
+|Day |  Number of Showings |Presales|Projection
+:----------- |:-----------:|:-----------:|:-----------:|
+Today|26837|$856k|$2.56M 
+Monday|26080|$316k|$1.21M 
+Tuesday|15637|$40k|$1.09M 
+---
+###**Creation Of The Gods**
+Creation caps of an excelent weekend with another great day. It has now passed $150M and looks on course for $300M 
+Reception remains very strong as it holds the 9.4 Maoyan and 7.7 Douban score it got right on release. Most movies tend to slip a bit as the first weekends pass.
+|#|THU|FRI |SAT |SUN|MON|TUE|WED|Total
+:-----------:|:-----------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|
+First Week|$6.84M/$11.11M|$8.15M|$15.77M|$18.14M|$10.95M|$11.12M|$10.99M|$86.23M
+Second Week|$10.66M|$13.02M|$22.43M|$21.67M|/|/|/|$154.01M
+|%± LW|+60%|+60%|+41%|+20%|/|/|/|/|
+**Scheduled showings update for Creation Of The Gods for the next few days:**
+|Day |  Number of Showings |Presales|Projection
+:----------- |:-----------:|:-----------:|:-----------:|  
+Today|98440|$2.67M|$21.12M  
+Monday|96527|$884k|$11.29M 
+Tuesday|56486|$93k|$10.62M 
+---
+###**One and Only**
+One and Only shows some staying power on Sunday defying its sub $10M projections and staying almost flat from yesterday. Bodes well going forward.
+Reception to the surprise of noone considering its a Wang Yibo movie is positive with a 9.7 on Maoyan and 7.5 on Douban
+|#|FRI|SAT |SUN |MON|TUE|WED|THU|Total
+:-----------:|:-----------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|
+First Week|$10.43M|$12.62M|$12.46M|/|/|/|/|$53.34M
+**Scheduled showings update for One and Only for the next few days:**
+|Day |  Number of Showings |Presales|Projection
+:----------- |:-----------:|:-----------:|:-----------:|  
+Today|82726|$1.79M|$9.31M   
+Monday|77310|$708k|$5.94M 
+Tuesday|44763|$96k|$5.64M 
+###**Wonder Family**
+Wonder Family caps of the dissastrous weekend with another -90% drop and barrely shy of $40M. Its only projected to earn another $3M after opening to 30M+ just 7 days ago.
+|#|FRI|SAT |SUN |MON|TUE|WED|THU|Total
+:-----------:|:-----------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|
+First Week|$12.15M|$11.10M|$7.51M|$2.47M|$1.86M|$1.52M|/|$37.78M
+Second Week|$0.56M|$0.77M|$0.74M|/|/|/|/|$39.85M
+|%± LW|-95%|-93%|-90%|/|/|/|/|/|
+**Scheduled showings update for Wonder Family for the next few days:**
+|Day |  Number of Showings |Presales|Projection
+:----------- |:-----------:|:-----------:|:-----------:|    
+Today|11907|$102k|$0.51M   
+Monday|11925|$36k|$0.32M 
+Tuesday|6594|$3k|$0.29M 
+---
+###**Mission Impossible Dead Reckoning**
+A better? if you can call it that weekend for MI7. Passes 45M and looks like it will just about get there to $50M
+|#|FRI|SAT |SUN |MON|TUE|WED|THU|Total
+:-----------:|:-----------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|:------------:|
+Second Week|$1.03M|$1.93M|$2.10M|$0.83M|$0.72M|$0.66M|$0.59M|$43.61M
+Third Week|$0.43M|$0.85M|$0.94M|/|/|/|/|$45.83M
+|%± LW|-65%|-56%|-55%|/|/|/|/|/|
+**Scheduled showings update for Dead Reckoning for the next few days:**
+|Day |  Number of Showings |Presales|Projection
+:----------- |:-----------:|:-----------:|:-----------:|
+Today|5921|$222k|$0.93M 
+Monday|6445|$52k|$0.37M 
+Tuesday|4046|$7k|$0.34M 
+---
+###**Other stuff:**
+Next big few holywood releases are MEG2 on the 4th August and Oppenheimer which does not have a date yet. Some WTS(Want To See Numbers) for those movies as well as some comparisons to how other revelant movies in a comparable number of days till release. Note these are not pre-sales. This is just a checkbox on Maoyan saying that your interested in the movie. The pre-sales are only ever in tables.
+**MEG2** 638k(+8k)
+MEG 2 breezes past $2.5M for its opening day pre-sales. It will surpass Transformers ROTB total opening day pre-sales tomorrow.
+Opening day pre-sales comparison:
+|Days till release | Creation Of The Gods Part 1 | Wonder Family |Lost In The Stars |Transformers ROTB|Fast X|The Meg 2  |The Meg 
+:----------- |:-----------:|:-----------:|:-----------:|:-----------:|:-----------:|:-----------:|:-----------:|:-----------:|:-----------:|
+12|$203k/18616|          |$93k/22228    |       |                     |$497k/34372|$339k/18679
+11|$221k/19085|          |$162k/25858   |       |                     |$640k/38455|$435k/19840
+10|$240k/19478|$68k/32748|$233k/28535   |       |                     |$789k/42955|$556k/22182
+9|$353k/21633|$290k/44426|$302k/31672    |       |                    |$951k/46289|$763k/25264
+8|$498k/22873|$497k/49041|$397k/34388    |       |                    |$1.15M/50034|$945k/27463
+7|$616k/24049|$642k/52977|$571k/39422    |       |                   |$1.48M/53656|$1.19M/29629
+6|$699k/25284|$793k/56363|$705k/44992    |             |$196k/69382  |$1.87M/58794|$1.62M/32376
+5|$785k/26673|$925k/59299|$802k/50423   |$121k/71289  |$471k/82292   |$2.22M/63516|$1.93M/34145	
+4|$861k/28606|$1.07M/62121|$902k/55347  |$312k/83324  |$728k/92034   |$2.53M/67717|$2.30M/35854
+3|$961k/30621|$1.28M/68808|$1.05M/61048 |$592k/94438  |$988k/103517  |            |$2.75M/40533		
+2|$1.11M/35990|$1.56M/80988|$1.29M/76567|$946k/106022 |$1.35M/114980 |            |$3.22M/48395
+1|$1.36M/46824|$2.03M/114817|$1.68M/119658|$1.45M/136762|$2.08M/140431|           |$3.93M/59242	
+0|$2.08M/60004|$3.31M/142828|$3.54M/149993|$2.78M/162406|$3.97M/168748|           |$5.66M/70354	
+*Gross/Screenings
+***
+**Gran Turismo** 27k(+1k)
+**Oppenheimer** $131k(+7k)
+Officialy confirmed to relese on the 30th August</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -2693,17 +3247,20 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Barbie's $29M in its second Friday is on par with: The Avengers $29.2M, $103M 2nd fin, $623M final. Jurassic World $29.1M, $106M 2nd fin., $652M final. Black Panther $28.8M, $111M in 2nd fin, $700M final. Two of those 3 exceeded $1.5B overall.</t>
+          <t>Do you think we are overestimating the marketing budget of COVID affected films?</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[deleted]</t>
+          <t>Obviously with most big blockbusters the 2.5x rule is fairly solid although I’m sure there are exceptions. Generally people have been assuming that a movie’s marketing budget is around about equal to its production budget.
+With these inflated budget movies that were shooting during COVID though like Fast X, The Little Mermaid, Mission Impossible 7 etc the production budget is being inflated because of COVID measures. That would not lead to a similar proportional inflation in marketing budget though. Mission Impossible 7 ended up with a $300 million production budget so using the 2.5x that gives us a break even if $750 million but that assumes that Paramount would increase the marketing budget to $300 million what just to match the production budget? That doesn’t really make sense to me.
+Avengers Endgame had an estimated marketing budget of $200 million+ (which was an increase over their normal $150 million) and I really don’t think Paramount spent $100 million more marketing Mission Impossible than Disney spent on Endgame. So I feel like with movies like Fast X and Mission Impossible we can’t just assume the 2.5x rule is 100% correct. Because the studios aren’t gonna be doing these all time massive marketing budgets just for the sake of matching an inflated production budget.
+This is just guess work but do you think Universal spent $340 million marketing Fast X or Disney spent $250 million marketing The Little Mermaid just to match it with a production budget? They might spend a little more but giving them among the highest marketing budgets *ever* even bigger than some of the biggest movies of all time seems unlikely.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -2713,18 +3270,25 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Is the WGA strike indirectly affecting box office numbers since no talk show rounds/segments?</t>
+          <t>After actuals this July is the fourth highest grossing July ever</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Curious to hear people’s thoughts on how, if at all, the WGA strike may be affecting the box office numbers of the recent movies? Talk shows provide a lot of eyeballs on clips of upcoming release plus there’s often some lazily written free press after the fact if something noteworthy came out of the talk show plug or if some segment went viral (like some of Tom Cruise’s on Fallon have).  
-With no talk shows, that’s presumably extra marketing money that has be spent on publicity and it’s possibly harder to spread the word about new releases. Just wondering what others think about this!</t>
+          <t>Will it beat 2013,2016 and even 2011?
+Monday 
+The average week to week drops on Barbie on its second weekend are 39.7% meaning that it’s Monday will likely be 15.678mil however that can be higher or lower so the likely gross is 14mil-16mil
+The average week to week drops on Oppenheimer are 41.6% meaning that it’s Monday will be 7.008mil but that can be higher or lower so the range is 7mil-8mil
+If everything else drops by 50% then holdovers can make 5mil 
+Talk to me has good WOM and a good start and will likely make 1-2mil
+Haunted Mansion will make 3-4mil 
+This’ll all add up to 1.361bil-1.363bil 
+What do you guys think?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -2734,12 +3298,19 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>I just found out that Nolan is not very good at portraying women in his film</t>
+          <t>A Review of Oppenheimer by a Woman Who Just Left the Theater</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>I'm not sure if I should post this here or in unpopularopinion, but after watching Oppenheimer, my biggest thought was: Nolan isn't very good at portraying women... too much unnecessary nudity and presence of two female characters in the movie are essentially just decorative, with no substantial roles. This also made me think of Nolan's past films I've watched, except the daughter role in "Interstellar," there's hardly any female lead that left a strong impression on me – bar waitress in memento? The deceased wife in "Inception"? Rachel in "The Dark Knight"? Come on, I feel like they're there just to complement the male protagonist's presence... don't get me wrong I'm big fan of Norlan I think he's a great director but it's a disadvantage of him…</t>
+          <t>This is Christopher Nolan's best film.
+It's not even *close.* 
+*Oppenheimer* uses the life of it's titular subject to examine the defining issues of the 20th century. It follows one of the few men who could definitively be called one of the most important men to ever live, and how his actions changed the trajectory of humanity's future. But despite it's scope, tackling everything from scientific progress (and it's consequences), the Red Scare, anti-intellectualism, the reason we go to war, the morality of developing a weapon as terrible as the atomic bomb, and more, this is probably Nolan's most character driven film. 
+Many have said that Nolan is a cold filmmaker, more focused on the big ideas behinds his plots than the characters who exist within those plots. But here he has managed to truly delve into Oppenheimer's psychology in a way that he never has with any of his characters. There is also the incredible supporting cast of people who come in and out of Oppenheimer's life, and despite how quickly so people come and go, they all leave an impact, on Oppenheimer, on the audience, on the world.
+These characters are portrayed by an incredible suite of actors. Cillian Murphy is absolutely haunting; his Oppenheimer is a man plagued by visions, to see the world in a way that no one else can, and it nearly ruins him. When he looks into the camera, one gets the impression that he is not looking at *you,* but at the particles and atoms you are made of, and the awful power that is locked inside of each of them. Robert Downey Jr. does the best acting he's done in years as Lewis Strauss, a man who's loyalties seem ever shifting, though I will not say more for fear of spoiling the events of the movie. Matt Damon, Emily Blunt, and Florence Pugh all turn in fantastic performances as well. I cannot recall the last time I have seen a cast of actors firing on all cylinders like this.
+Speaking of firing, let's talk about Trinity. The big question going into this movie was 'How is Nolan going to recreate a nuke?' The answer is spectacularly. The Trinity scene must be seen to be believed, and it demonstrates exactly why the title of the biography this movie is based on was called *American Prometheus.* The sound design and visual effects of this film sell every moment, whether it be Oppenheimer contemplating what a fission reaction would look like to a Nazi V2 rocket screaming across the sky. Nolan has taken the VFX prowess of his blockbuster filmmaking and applied to an intense character study.
+This movie is a masterpiece, and I hold no reservations about using that word. Go see this movie. It's one for the history books.
+&amp;amp;#x200B;</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2754,12 +3325,13 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Box Office: ‘Haunted Mansion’ Spooked With $23-27M; ‘Barbie’ Heads for Record $95M Second Weekend (-41%); ‘Oppenheimer’ Eyes $46M (-44%)</t>
+          <t>Barbie will be a blockbuster, judging from open caption presales.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[deleted]</t>
+          <t>The open caption presales for Barbie just rose to a 5.06 ticket to screentime ratio.  So far, 1,507 tickets sold for 298 open caption screentimes. So it has already hit the 5.0 ticket to screentime threshold to qualify as a blockbuster. 
+What is it about the Barbie movie that makes people want to see it? Speaking for myself only, I see the picture used to promote the movie on theater sites and it just looks like a fun movie. That's what it looks like based on the picture alone without regard for the trailers. Who doesn't want to see a fun movie?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2774,13 +3346,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>[Brazil] Oppenheimer grosses ~$480k USD on opening day in Brazil. Tracking for the biggest non-Batman Nolan opening.</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>Isnt it crazy how well theatrical movies are doing compared to the past years?</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>I dont remember the last time we had so many movies being talked about in one year. We had mario, barbie, the little mermaid, etc. its crazy! And what's even crazier is these movies are theatrical releases. The past few years popular movies were straight to streaming only but now? It looks like theaters are doing so well again. Is it just some coincidence or did everyone change their minds about streaming? Cause I clearly remember people avoiding theatrical releases and waited for movies to stream.</t>
+        </is>
+      </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -2790,17 +3366,20 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Oppenheimer watching screen inquiry.</t>
+          <t>Lady Bird (2015)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>One of my favorite films I've ever seen was Greta Gerwig's 2019 adaptation of Little Women, which featured a wonderfully touching story, a fabulous cast and some scenes that I keep coming back to (especially the heartwrenching scene on the hill between Laurie and Jo).
+It was while I was reading some reviews on the film, people kept referring to Gerwig's 2017 Lady Bird, which garnered many Oscar nominations in the year it came out, 2017, and I decided I needed to watch that movie.
+While watching the movie, which like Little Women also stars the immensly talented Saoirse Ronan and a brooding Timothee Chalamet, I was struck by the poignant and turbelent teenage years and the conflict in the family, acted with matter of fact honesty by Laurie Metcalf. I was reminded a lot of Mary Taylor Moore's character from Ordinary People, which also centers on a mother and troubled teenage child relationship. I really admired the themes of shame about family and wealth and the outstanding acting in this film, and was pleasently surprised to find Lucas Hedges has a small role in the film, after connecting to his performance in the bleak but mesmirising Manchester by the Sea. Overall, I found this movie outstanding, and I think I prefer it to Little Women, on the grounds that it's an original screenplay.
+Edit- Lady Bird came out in 2017 and not as written in title. Also, the best thing about 2002 is it's a palindrome.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -2810,13 +3389,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Barbie JUGGERNAUT at US #BoxOffice, grossing another 15M BIGGEST non-holiday nor-Christmas-corridor 2nd MON of all time! (Top5 below) #11 BIGGEST 2nd MON of all time! (Top10 below) Fantastic hold, -42.7% drop from last MON 366.4M cume. 400M+ on THU</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>Tom Cruise has worked with just about every high profile and well regarded director in Hollywood minus Quentin Tarantino, Christopher Nolan, Steven Soderbergh, David Fincher, Spike Lee and Clint Eastwood. Why is that?</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>He worked with Francis Ford Coppola before he was 21. He's worked with Steven Spielberg on two occasions. He's starred in a Paul Thomas Anderson film. He's also worked twice for the following directors Spielberg, Edward Zwick and Tony Scott. He's even worked with Stanley Kubrick. John Woo, Barry Levinson, Ron Howard, Michael Mann, Robert Redford are other filmmakers who Cruise has worked with.</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -2826,13 +3409,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>🇯🇵 INSIDIOUS THE RED DOOR is almost passing MISSION IMPOSSIBLE DEAD RECKONING despite being released a few days later and no IMAX.</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>Christopher Nolan Says ‘No’ to Directing Another Superhero Movie</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Christopher Nolan Says ‘No’ to Directing Another Superhero Movie, Criticizes Studios for Viewing Films as Plot and Not an ‘Audiovisual Experience’</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -2842,17 +3429,20 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Rank the following directors: Denis Villeneuve, Christopher Nolan, David Fincher</t>
+          <t>Just when you think Mission Impossible movies cannot get any better, Tom Cruise outdoes himself with Dead Reckoning Pt. 1. GO! SEE! IT! ASAP!</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Seems like these 3 are the next generation goats, akin to the previous generation in Spielberg, Scorsese and Coppola (not saying that their styles match). In my opinion, they are the most consistent big-budget directors in Hollywood. But how would you rank them? Personally, I’d go Fincher, Villeneuve, then Nolan.</t>
+          <t>Just came back from the movies and I need to rave about this masterpiece.
+I have so much respect for Tom Cruise’s dedication to his movies, specifically this franchise. (He is one of the producers BTW)
+Dead Reckoning is incredible; it keeps you on the edge of your seat from beginning to end. I expected nothing less from Cruise.
+Hands down this is movie of the year!</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -2862,17 +3452,18 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Barbie is my new favorite movie, Greta has blown me away</t>
+          <t>Movies about a technical subject should not gloss over the technical aspects of it!</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>I've been thinking about this after watching The Big Short. I'm not a financial wizard after having watched it but the cutaways made the dialogue easier to understand and they were done in a very entertaining way. 
+I didn't feel that way when watching Jobs, Social Network or most recently, Oppenheimer. Give the audience a sense of what the most difficult technical problems and how they overcame it. It's okay to dumb it down, just don't show an image of sparks or a character typing away furiously. None of that means anything to me.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -2882,18 +3473,18 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Will Barbie beat out Avatar 2?</t>
+          <t>How come I can't hear movies in theaters very well, but I can hear the opening trailers clear as crystal?</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Its already at 800 mill ww after like 12 days?
-I feel that this will have legs. Could even top 2 billion</t>
+          <t>Saw Mutant Mayhem the other day and could only make out every other word. That's how it usually is with me and movies and I used to worry if I was losing my hearing. 
+But this time I noticed: Even though I couldn't hear the movie itself, I  heard every miserable word of that "Trolls Band Together" trailer. So is it just AMC, or are movies deliberately played quieter than the trailers?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>tmnt</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -2903,12 +3494,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>After recent events, I'm wondering what was the REAL reason as to why Top Gun Maverick was such a hit?</t>
+          <t>Mission Impossible WEIRD watch order</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>I don't think it was because of nostalgia because we literally saw The Flash and Indiana Jones bomb, it's probably not because of Tom Cruise either because Mission Impossible Dead Reckoning is looking at a 5-day opening of below $100M, and I know some people will say "because it's a good movie", but so many good movies have bombed in the past and so many bad movies have been massive hits before. So what was the one big reason as to why this film was such a hit?</t>
+          <t>Long story short I've watched all the Mission Impossible movies and they were all great. But over time since some are quiet old I have forgotten some bits and pieces and information from the movies. 
+But I remember like characters who is dead, alive who does what etc etc. But I just can't be bothered watching all of them AGAIN before Dead Reckoning Part 1. 
+So what I did was pretty interesting I watched the 3rd one again (the most important one) and then went to watch the NEW Dead Reckoning. Then after I had watched the 7th movie which was btw 10/10. 
+I watched the 4th all the way up to the 6th and it honestly made them so much more FUN!, because I was like "ohh that's why she does this". "This is how that happens..." etc etc. I would honestly recommend it for anyone who can't be bothered rewatching them all because I hate watching movies again because I can vividly remember parts and it makes it boring and INSTEAD try this interesting weird watch order.
+Let me know your opinions in the comments down below 
+(as always keep it spoiler free for people who may have not seen the movies :))</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2923,13 +3519,24 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BOT (M37): "The only films even close to Barbie's [presale growth rate] at [the same point in time] are Avatar 2 and Little Mermaid, and Barbie has basically matched [Avatar 2] in total sales ($17M preview, but with PLF &amp;amp; 3D) and doubled the latter ($10.3M)"</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>Another person who doesn’t know movie theater etiquette</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Went to see Mission Impossible last night. Great movie, but a lot of my experience was made worse just because I sat next to the wrong person. 
+So this girl sits beside me. Is on her phone for all the trailers, and I’m like “that’s ok but she better turn it off for the movie”. Movie starts, she’s on her phone. Almost never puts it away. She was on her phone for (I’m not exaggerating) 90% of the actual movie. 
+During a certain important scene it gets almost silent, and all I hear is tap tap tap because of her nails hitting the screen texting. She didn’t even bother to look up at the screen for the big stunt. 
+At one point I look over to see what’s so important. Snapchat. Granted this is a late 20s early 30s girl on SNAPCHAT. The whole movie. 
+She would get up to leave like 4 different times, not caring about being loud. When she got back after 10+ minutes away doing who knows what, she’d plop her giant purse in the seat for everyone to hear. 
+And you already know she left all her trash on the floor. Yep. Not even in the cup holders or the seat. The freaking floor. 
+And you wanna know the craziest part? She was alone. Why in the world would you pay $20 for a prime-time seat at a prime-time time in the best theater in our city, just to be on Snapchat for 90% of the movie. 
+Frick you.</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -2939,17 +3546,29 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Which is your favorite Mission Impossible movie and why?</t>
+          <t>Oppenheimer has not been banned in Japan</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>A viral tweet this week claimed it was banned. However, it currently doesn't have a release date and it will come down to Toho-Towa, the country’s biggest distributor of Hollywood films to decide if it will be released.
+The IMAX screening schedule in Japan is as follows
+7/14 THE BOY AND THE HERON (Ghibli)
+7/21 MISSION: IMPOSSIBLE: DEAD RECONCILIATION PART ONE
+7/28 THE KINGDOM: FIRE OF FATE
+8/4 Transformers: Rise of the Beasts
+8/18 SAND LAND
+8/25 The Meg 2: The Trench
+9/22 John Wick: Chapter 4 (maybe)
+9/29 The Creator
+10/20 Killers of the Flower Moon
+11/3 Godzilla -1.0 (probably)
+Currently, there are three weeks available in September in Japan, but there is still a possibility that other films will be released. Therefore, Oppenheimer will most likely be after November.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -2959,13 +3578,19 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Solid $7M WED for #TMNT, for $12.5M to date. WoM supporting it well. Should have solid 5-days opening weekend. Box office is buzzing.</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>I saw Oppenheimer in 70mm (non-IMAX) and honestly couldn't really tell the difference [No spoilers]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>I thought I reserved IMAX but turns out it was 70mm in a regular old theater.  I would have liked to have seen 70mm in IMAX, but by the time I found out, IMAX 70mm in my town (Los Angeles) had been sold out for like 3 weeks.
+So watching it projected in 70mm on a regular screen, I honestly didn't see much difference from the current laser projection technology.  It looked REALLY GOOD, and big part of that was that this was the first showing in 70mm at the theater so the reel had next to no scratches.
+But other than some flickering that my eyes adjusted to eventually, I really couldn't tell I was watching something projected on film.  It honestly felt unnecessary and more of a novelty, like getting to see some cigarette burns on the screen again.  But at the same time it didn't cost me any extra, so I'm happy I to experience the novelty.  I just don't think I'll be rushing to see any 70mm projections again anytime soon.</t>
+        </is>
+      </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>tmnt</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -2975,13 +3600,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Did Barbie just deliver the largest 2nd Tuesday of all summer movies? $15.3M vs TLK's $15.2M</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>Top 10 most expensive movies off all time</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>It’s funny how most expensive movies were profitable before, especially top 10. Now Fast X is the first box office bomb inside top 10 and we have two more in top 50 moat expensive movies (Indy 5 and probably MI7) that will bomb. This year is certainly not for enormous amount budget movies.</t>
+        </is>
+      </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -2991,20 +3620,19 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Heard it here first - Oppenheimer will have incredible trend in 3rd/4th weekend</t>
+          <t>Walked in about 8 minutes late to TMNT Mutant Mayhem, what did I miss (if anything)?</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>I have been calling 750M+ WW for Oppenheimer and 320M Domestic since day one. And based on how it did in 2nd weekend, here is my prediction for next two weekends - 
-3rd Weekend = 32M (-32%)  
-4th Weekend = 22M (-30%)
-With extension of IMAX, the trend from now till Aug 17th will be very solid. Domestic still looks 320-330M to me but I am fairly optimistic that Oppenheimer will go past 800M WW as its overseas trending will be even more incredible than domestic. Expect 500M OS now</t>
+          <t>I pretty much walked in at the scene where the turtles were on the roof preparing to go on the corner store heist.
+Now I’ve seen a clip of that scene on YT already so I don’t feel like I missed out on that part just what came before it? Or was that literally the beginning of the movie?
+I felt kinda bad when I walked in and the movie was already playing (didn’t know the sneak previews didn’t show ads) so I ended up 8 minutes late, allegedly. Just wanna know what I missed.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>tmnt</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -3014,13 +3642,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>“Oppenheimer” Is Ultimately a History Channel Movie with Fancy Editing</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>What's with all the people claiming that they think Barbie could do a billion?</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Yes it's a social media meme, Yes there's tons of well known actors in it but I just don't think it'll make that much. Both Barbie and Oppenheimer will do strong numbers and the double feature meme and strong marketing of the two movies is helping both movies for sure but neither will make a billion. Both will probably make around 500M WW</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -3030,13 +3662,18 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>'Oppenheimer' Sacred Text Reading Sex Scene Raises Hackles in India</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>Barbie has outgrossed Spider-Man: Across the Spider-Verse to become the highest grossing film of the summer domestically</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Barbie (current) - $381,724,676  
+Spider-Man: Across the Spider-Verse (current) - $379,256,240</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -3046,13 +3683,23 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Mission: Impossible – Dead Reckoning Part One (2023) Movie Review | Is This The Best Mission YET?</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>With Barbie surpassing Jurassic World Dominion at the box office...</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>... each Hollywood studio has exactly one spot in the "Top 5 highest grossing films of the 2020's"
+1. Avatar: The Way of Water (Fox/Disney)
+2. Spider-Man: No Way Home (Sony)
+3. Top Gun: Maverick (Paramount)
+4. Super Mario Bros Movie (Universal)
+5. Barbie (WB)
+I'd love to put Multiverse of Madness (Disney) as #6 ... but Jurassic World Dominion is in the way.</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -3062,17 +3709,47 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Greta Gerwig becomes the first woman in history to solely direct a film that grossed over $1 billion at the box office Barbie</t>
+          <t>Christopher Nolan vs Quentin Tarantino (Writing)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Who is a better writer when it comes to overall script, dialogue and full circle ending? Example of why you think so. 
+Both Directors have written all the movies they have directed or had a co writer. They both have a taste for action and while Tarantino does not hold back on the violence in the film, Christopher choose to mark his target similarly to Tarantino. They both don’t make movies for everyone, some would argue it is mostly for the men but I think we can compare these similar directors as writers who know how to hold your attention and make you want more!!!
+Ironically they both got into film the same way, early interest and making short films. They both use the same actors, same editors, same crew. It’s amazing that they have not made a movie already but the directing styles are quite different. At this point anything you see below is me just trying to meet the damn word count which holy jeez takes forever. How am I still at 200 words. Anyways here the movies directed and written by these fine gentlemen. Oh my god I’m still not over the count. I need twenty more words so here are twenty more words for you mr bot.
+List of movies for each one below
+Quentin Tarantino: 
+1. Kill Bill Vol. I
+2. Pulp Fiction
+3. Inglourious Basterds 
+4. Jackie Brown 
+5. True Romance 
+6. Django Unchained
+7. Kill Bill Vol. II 
+8. Natural Born Killers 
+9. Once Upon a Time… in Hollywood 
+10. The Hateful Eight 
+11. Death Proof 
+12. Reservoir Dogs 
+13. From Dusk til Dawn
+Christopher Nolan: 
+3. Memento (2000) 
+4. Insomnia (2002) 
+ Batman Begins
+The Prestige (2006) 
+The Dark Knight (2008)
+ Inception (2010) 
+ Dark Knight Rises (2012
+ Man of Steel
+ Interstellar
+ Interstellar (2014) 
+ Dunkirk (2017) 
+Tenet (2020)</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -3082,12 +3759,21 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Barbie is the Buddha</t>
+          <t>Cinemas are equally to blame for poor boxoffice results</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>With the 2023 slate under performing, the majority of talk on this sub has blamed poor quality films and high ticket prices. However after my Barbie experience this Saturday, I think the broader Cinema experience has been degraded to the point it is now actively putting people off. 
+What do you think? My experience below: 
+- partner and I decide to see Barbie opening weekend (this is the first time my partner has gone to a cinema since Covid). We choose the O2 in London, one of the largest cinemas in the capital 
+- booking website is buggy and hard to navigate, constantly asking me to hand over private information 
+- large queues for concessions, that's fine it's a Saturday. Except it is taking 5 minutes per customer (I timed it). 6 people infront of me leave the queue. I send my girlfriend to the seats so she doesn't miss the movie. After 30minutes I also leave the queue, no concessions, and having missed 10 mins of the movie. 
+- everything is sticky, floors, walls, handles, seats. I don't think it had been cleaned in at least a week. 
+- screen is blurry on left side, dark on the right. My 7 year old basic range TV is genuinely better quality. 
+- constant noise and talking throughout the movie. I know this has always been an issue, but my god, I have never seen it this bad. 
+- girlfriend was hit in the back of the head by teenagers whilst I was queuing. They were later kicked out and started a fight in the lobby. 
+With the exception of the teenagers, all of these issues were caused by the cinema presumably in an effort to cut costs. Needless to say my girlfriend now has no interest in ever going to a cinema again, and I will probably wait to rent oppenheimer at home.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3102,12 +3788,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Let's Discuss Christopher Nolan's "Oppenheimer" - Are You Excited?</t>
+          <t>The new Tarantino-Waltz duo of Hollywood ?</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>What are your thoughts on Christopher Nolan's upcoming movie "Oppenheimer"? Personally, I am very excited because the main role is being played by Cillian Murphy, it is based on real-life events, and the fact that it will be shot on 70mm film has got me hyped up for reasons I can't quite explain. So, what are your thoughts on the film, and do you plan on watching it?</t>
+          <t>Kenneth Branagh in Chris Nolan's last three films
+&amp;amp;#x200B;
+British in Dunkirk
+&amp;amp;#x200B;
+Russian in TENET
+&amp;amp;#x200B;
+Danish in Oppenheimer ;
+&amp;amp;#x200B;
+ when I first saw Oppenheimer, My mind did relate between Branagh speaking different European accents in Nolan films to Christoph Waltz mastering different European languages in Tarantino movies.
+&amp;amp;#x200B;
+Did yours? and what accent do you think Branagh would be speaking in the next Nolan film?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3122,13 +3818,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>UPDATE - Barbie opens even stronger than estimated! Domestic opening wknd box office was $162M with SUN doing much more biz than WB expected. Daily breakdown: $70.5M FRI, $47.8M SAT (-32%), $43.7M SUN (-9%), $162M WKND. Incredible!</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>How much does Dead Reckoning Part One need to make to break even?</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>The 2.5x rule suggests $725 million on a reported budget of 290 million, but the franchise is more OS heavy than most. Does that change things?</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -3138,13 +3838,21 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Weekend final numbers: 1. Mission: Impossible — Dead Reckoning Part One - $54.69m $78.49m 2. Sound of Freedom - $27.28m for $85.79m 3. Insidious: The Red Door - $13m for $58.09m</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>The cost of screening rights of older movies</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Firstly, when there is a drought of new releases, why don't cinemas rent out or buy rights for older movies instead of putting filler, mediocre new-releases on their programs. An example, my local cinema is screening only 7 movies the following week, and in an exceptional week where there are big movies considering the rest of the year(Barbie and Oppenheimer, the new MI as well), and the others are some animated movies or other slop.   
+I have observed the crowds for those other mediocre movies, they are not particullary large, 15 people average, in halls as big as 120 seats. So why wouldn't they buy rights and screen a critically acclaimed movie from the past instead of those mediocre new ones.
+I can't imagine a scenario where more people would go to watch the Meg 2 if they had Lord of the Rings in the same week. 
+I also can't imagine rights to such old movies would be more expensive then new-releases.
+My question is, why don't they do it (and I know there are cinemas doing it, im not talking about the exceptions in big cities so dont say oooh new beverly in LA does it, im talking about an average cinema in an average town in an average country), and if someone local would open a small-scale cinema, how would one go about acquiring the right to such movies?</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -3154,13 +3862,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>#Oppenheimer also blew up industry’s projections at US #BoxOffice after BOMBASTIC 80M on its 3-day opening weekend. Biggest for a original film in #ChristopherNolan’s career, beating #Inception’s 62.8M! BIGGEST for any R-rated film Post-Covid, beating #JohnWick4’s 73.8M.</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>Is there any hope for drad reckoning to hit 700 mil</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Noticed a couple of huge groups on Facebook still talking about dead reckoning it gave ne some hope that it might come close to 650-700 mil. I wonder what do you guys think ? Is it a lost cause or is there a chance</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -3170,18 +3882,26 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Oppenheimer X John Wick Chapter 4</t>
+          <t>Has the summer box office changed your thoughts on what films could do well at the end of the year?</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Do you guys think that Oppenheimer will outgross John Wick Chapter 4? Since the projections are being 10M+ in the first Monday for Oppenheimer and JWC4 had grossed $5,632,448 in his first Monday. Do you guys think that Oppenheimer will have better legs?
-And those films prove again that a mid budget film is more likely to get a profit because both had a 100M budget</t>
+          <t>I've been keeping track of what has performed differently to what everyone on the sub predicted. Basically, "What movies was r/boxoffice wrong about?" These are the most obvious ones.  
+So far we've got,
+\- Mario
+\- The Little Mermaid
+\- Across the Spiderverse
+\- The Flash
+\- Indiana Jones and The Dial of Destiny
+\- Mission Impossible
+\- Barbie
+What future movies will perform better or worse in comparison to what most are thinking?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -3191,17 +3911,61 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>If you do not do your research on Oppenheimer you will not enjoy it</t>
+          <t>Now that everything is being pushed back to 2024 are we looking at another flopbuster year</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>I mean just look at the slate that we have for next year for now :
+Bob Marley’s One Love- Jan 12
+Argyle- Feb 2
+Madame Web- Feb 14
+Fall Guy- Mar 1
+Elio- Mar 1
+Quiet Place Day One- Mar 8
+Kung Fu Panda 4- Mar 8
+Godzilla x Kong New Empire- Mar 15
+Snow White- Mar 22
+Ghostbusters Sequel- Mar 29
+Mickey 17- Mar 29
+Untitled M. Night Shyamalan Project- Apr 5
+The Lord of the Rings: The War of the Rohirrim- Apr 12
+Untitled Monster Thriller for Universal Pictures Project- Apr 19
+Challengers- Apr 26
+The Ark and the Aardvark- Apr 30
+Deadpool 3- May 3
+Kingdom of the Planet of the Apes- May 24
+Furiousa- May 24
+Imaginary Friends- May 24
+Ballerina- Jun 7
+The Watchers- Jun 7
+Bad Boys 4- Jun 14
+Inside Out 2- Jun 14
+Mission Impossible Dead Reckoning Part 2- Jun 28
+Despicable Me 4- Jul 3
+Mufasa: The Lion King- Jul 5
+Venom 3- Jul 12 
+Twisters- Jul 19
+Captain America Brave New World- Jul 26
+Trap- Aug 2
+Borderlands- Aug 9
+Alien Romulus- Aug 16
+Kraken The Hunter- Aug 30
+Beetlejuice 2- Sep 6
+Transformers One- Sep 13
+Joker Folie A Deux- Oct 4
+Gladiator 2- Nov 22
+Wicked- Nov 27
+Karate Kid- Dec 13
+Thunderbolts- Dec 20
+Sonic The Hedgehog 3- Dec 20
+Untitled Fourth Film Directed by Jordan Peele- Dec 25
+March, May, June, July, and December are shaping up to be packed months is history going to repeat itself again</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -3211,12 +3975,13 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Barbie💀🫵🛐☕🧖🗿🤓</t>
+          <t>Movio's weekend insights suggest a 60/61% female demo split for Barbie in its second weekend.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>If you just look at intra age splits and assume 50% of audience is male and 50% female (given Barbie and haunted mansion that's probably a little light), they're all pretty much 59% to 61% female.
+    movio.co weekend insights</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3231,13 +3996,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AMC hoping to avoid bankruptcy with smash success of "Barbenheimer"</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>ridley scott is one of the most influential filmmakers.</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>when you look at scott it's plain as day his dry science fiction serious tone with the visuals were clearly huge inspirations for Denis Villeneuve, Christopher Nolan and David Fincher. I often refer to these 3 filmmakers as Ridley babies. because they all riff off of Scott's work with Blade Runner and Alien and its very evident that storytelling and stylistically are very much like Ridley scott.</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -3247,10 +4016,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>‘Oppenheimer’ Star Emily Blunt Says Cast Will Leave London Premiere For Strike If SAG Hits Picket Line</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>Do directors like Nolan have a moral obligation to not be neutral in their story-telling?</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>I can see why Nolan would have wanted to tell this story; clearly Oppenheimer's discovery was monumental in shaping the world and geopolitics today. 
+Can't help but think the movie was designed to depict a well-intentioned troubled genius eliciting a sympathetic response from the audience. In almost all interviews Nolan and the (excellent) cast talk about the emotions, psyche and the tense moments of conflict without ever talking about the consequence in a negative light.
+Most audience reviews talk about the craft (screenplay, audio, script, acting) and not enough about the subject matter is discussed.  One would think acclaimed directors like Nolan have some responsibility towards not maintaining neutrality as much as they did in their depiction of Oppenheimer.
+Thoughts?</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
           <t>oppenheimer</t>
@@ -3263,10 +4039,19 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Worldwide opening weekend estimates for Barbenheimer: • BARBIE — $300M • OPPENHEIMER — $165M Will be one of the biggest weekends in box office history.</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+          <t>Anyone else having a tough time feeling the need or even the want to see anything in the theaters these days?</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Reading about these Barbie/Oppenheimer predictions (no, I'm not calling it Barbenheimer, shut up, internet) and how they're expecting these to be a "return to the theaters" for people. 
+But then I recall how every single blockbuster release, aside from Maverick, has been inaccurately predicting this for the last couple years, and each film has had a satisfactory or lukewarm opening weekend before fizzling out. 
+Then, per usual, the studios seem shocked and find something to blame other than themselves. But could it be that people just don't feel like shelling out a lot of money only to be advertised to for a half an hour before slogging through a good looking but discardable 3 hour film? Especially when it will be streaming in two months anyways. 
+I know this is the case for me. I don't feel compelled to go see movies that have no particular reason for existing except to make rich people richer. Studios and networks just keep churning out movies so forgettable that when you see it, you notice things happening, but almost immediately after it's over, it all just evaporates from your memory, and you never give it much thought about it ever again. This has been about 85% of the dreck that has been released in the last 5 years. 
+I can easily wait to watch these banal and bland films from the comfort of my own home, where I have a giant screen and surround sound, along with my couch, my fridge/pantry, my toilet, and the ability to pause, or stop the movie outright if it is a complete suckfest (I'm looking at you, Ant-Man and the Wasp: Quantumania. I would have felt like a massive idiot spending 20+ bucks to walk out of this.)
+Sure I'm interested in seeing Oppenheimer at some point, but I don't feel like I absolutely HAVE to see it in the theaters. Anyone else feeling like this? I mean, you MUST be based on all these poor box office performances haha</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -3279,17 +4064,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Margot Robbie last 7 movies didn't do too well, but now that Barbie is on her merry way to a billion and beyond, can we know finally call Robbie as Hollywood actress with the biggest box office pull?</t>
+          <t>Can I watch Mission impossible dead reckoning with only have seen the first movie</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Margot Robbie last 7 live action movies: Asteroid City, Babylon, Amsterdam, The Suicide Squad, BoPaTFEo1HQ, Bombshell</t>
+          <t>I wanted to go see mission impossible dead reckoning in the theaters in a few days somebody asked me to go although I have only seen the first film would I be able to understand everything with have only seeing the first one?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3299,17 +4084,18 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>How’s my IMAX seat for Oppenheimer?</t>
+          <t>A possible scenario where Barbie can beat Mario at the Domestic Box Office</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>According to the data I have, Barbie’s opening week so far has been running 13% ahead of Mario’s first full week to date. If we were to allocate Mario’s first two days into a week 0 and start the comparison on opening Friday, if Barbie were to do 13% better than Mario each week, then it will be needing to a total box office gross of $583 million, edging out Mario’s lifetime total by around $10 million.
+This is not intended to be a prediction, but rather a model scenario.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3319,12 +4105,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>July 21-23 will be the highest grossing weekend of the year.</t>
+          <t>Movies aren’t special anymore</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Barbie has the potential to open to 100m, and Oppenheimer could open to 50m. With holdovers like Mission Impossible and Insidious, it could easily be the highest grossing weekend. The current highest grossing weekend is April 7-9, with $205 million. If Barbie and Oppenheimer open on the high end of projections, then that is already 150 million, with MI adding atleast 35 million onto that.</t>
+          <t>I saw a recent post discussing the merits of The Little Mermaid remake (poster was making the argument that TLM remake brought some good ideas but handled them poorly) and I couldn’t get over the feeling of, like, so what? I don’t mean the poster was wrong, I just mean who cares? Who cares about the remake of The Lion King, or the remake of Poltergeist or whatever. They are products designed to trade on name recognition, literally no one involved had any bright ideas on how to improve the material, no one cared about whether they were making a good film or not, they just cared that us poor suckers recognized the brand. The same is true of franchise films- Thor: love and Thunder, Antman: quantumania, Dr Strange: multiverse of fucknows- all feel tired and rote, all feel unnecessary and inessential. Alien: Covenant, exorcist 5, Halloween Ends (lol, jk Halloween: Begins Again coming soon) Scream 7, it just seems to never end. Barbie and Oppenheimer seem to offer some relief, but Hollywood always takes the wrong lessons so I fear the best we can hope for is dramatic biopics on Remington and Glock, while also getting a Bratz and an American Girl movie. It all seems so uninspired and lazy. How much longer before it all comes down round our ears?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3339,17 +4125,18 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Box Office: ‘Haunted Mansion’ Spooked, ‘Barbie’ Scores Record $93M Second Weekend in U.S.</t>
+          <t>Is Nolan The Only Director Capable Of Putting Out Big Budget "Art Films" Nowadays?</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>I truly feel like Christopher Nolan is in a unique position; he has enough clout in the film industry that studios essentially just give him a blank check with full creative control and let him create whatever he wants, with little to no studio interference. how many other directors have garnered that level of trust &amp;amp; goodwill within Hollywood (or any film industry)? Denis Villeneuve is probably the only other director off the top of my head who's actually putting out mega-budget "art films" that feel like an uncompromised vision of an auteur director. Tarantino is another one that came to mind but he doesn't require 100+ million dollar budgets and mostly works on a smaller scale, but a similar uncompromising vision and absolute trust from whatever studio is funding him. What's unusual about this is even veteran, proven directors of some of the most iconic &amp;amp; successful films of all time still struggle to collect the necessary budgets and, on top of that, still have to deal with studio interference despite their near-spotless track record (James Cameron, Steven Spielberg, Francis Ford Coppola, etc.). What do you think makes Director's like Nolan &amp;amp; Tarantino unique in that sense? Is it because they never really "missed" so to speak? Both have built-in audiences that will be interested in whatever they put out so they're pretty much flop-proof from a financial perspective. is that what affords them such freedom in an industry like Hollywood?
+I mean, who else is really putting out big-budget, slow-burn think pieces like Oppenheimer? who else could get away with that (without it flopping badly or dismissed as Oscar bait) other than Christopher Nolan?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3359,17 +4146,20 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Can Sonicbolts become the new Barbenheimer-like sensation?</t>
+          <t>American vs. English directors</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Of course, I'm referring to Sonic the Hedgehog 3 and Thunderbolts going against each other on December 20, 2024. It's something I have been thinking about for a while, and what's most interesting is a superhero movie going up against a video game movie, which are opposite genres. That's how it was with Barbie and Oppenheimer. Sonic 3 and Thunderbolts are both being planned as Christmas releases, so maybe if Sonicbolts does become reality, then it may be considered a holiday season/winter cinematic double feature like how Barbenheimer was a summer cinematic double feature. The only thing, though, is if it does manage to draw social media hype and memes sometime next year.</t>
+          <t>Let's go quality over quantity here and choose the top 5 from each side. Pound for pound.Who will come at the top and why?
+My take will be:
+C. Chaplin          S. SpielbergA.       Hitchkok       Martin Scorsese.     C.Nolan            Francis Ford Coppola.   David Lean       John Ford.  Ridley Scott      Joel Coen
+The English ones won for me based on ... versatility.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -3379,17 +4169,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Barbie is VERY heavy-handed with the feminist message...</t>
+          <t>Will “Oppenheimer” become the highest grossing film….</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>To never become number 1 at the domestic box office. For 14 years, “My Big Fat Greek Wedding” held the top spot for very a very long time at that category. Until “Sing” came out in 2016 and became the highest grossing film to never become number 1 at the domestic box office. “Oppenheimer” will become number 2 on this list by next weekend, but can it surpass Sing?” This has always been one of my favorite all time lists, because it shows that your film doesn’t need to become number 1 at the box office, to be a box office hit.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -3399,17 +4189,18 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Barbie/Oppenheimer for a date?</t>
+          <t>Who is your currently working favourite film composer?</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>After watching Oppenheimer, which was astounding, I could not get the score out of my head. I think Ludwig Göransson is the best working film composer right now. In the last ~ five years he has done The Mandalorian, Black Panther (2x), Tenet and Oppenheimer. All incredible.
+Can anyone match this run in recent years?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -3419,18 +4210,18 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Oppenheimer last scene/ending explained</t>
+          <t>What evidence of Covid are you still seeing on screen?</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>So i just got back from watching oppenheimer.i really love it thoroughly. In my opinion, the best movie released this year and also, this decade. Christopher Nolan really is incredible, it is really nice to see this sort of movie: instead of the basic ones we get nowadays. I think this one might be in his top 5, but i’ll need to research it before deciding.
- But yeah the thing is, i unfortunately didn’t hear the whole the last scene where oppenheimer and einstein are talking while RDJ’s character is coming towards them. My theatre was packed and i was stuck besides this guy and by the time einstein and oppie started talking, all i heard was, the guy next to me, coughing and i didn’t get get all of what they were saying.... i saw the last clip and heard some words but that’s pretty much it. Can someone explain/tell me what they were saying. I’ve read through the discussions and everyone was praising this last scene, so i was wondering… Thanks to anyone who’ll take the time</t>
+          <t>Mission Impossible: Dead Reckoning is (finally) coming out next week, and I know they filmed both before and during covid and were the first to shut and down and even first to start, developing new protocols. I also know Covid is why both MI:7 and The Dial of Destiny have such horrendously inflated budgets.
+Are there any tell-tale signs of Covid-19 that you are still seeing in movies (and even television)?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -3440,10 +4231,19 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>In #China’s #BoxOffice,pre-sales for #MissionImpossibleDeadReckoning improved ahead of THU previews happening tomorrow, $1.8M pre-sales for JUL 13-16 period as of THU 0:01 am local (vs #GoTGVol3’s 1.9M &amp;amp; #NTTD 2.4M at same point) #MI7 has 75k screenings booked for FRI so far!</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
+          <t>Knight &amp;amp; Day: One of the most poorly marketed movies ever</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>For anyone that doesn't know, Knight &amp;amp; Day is a movie wherein Tom Cruise satirizes the exact roles he's spent his life playing ~~- especially~~ (*I don't know what happened there.  I think I had a mini-stroke when I was typing. 
+ No idea what I was originally intending to say.*).  Basically, it's two hours of Tom Cruise making fun of his career.  And shit...he managed to still make a funny and entertaining movie, with a little charm and quirk even?  The movie actually ends up having more interesting personality than any of his last five Mission Impossible movies.  Cameron Diaz is fantastic in this too.  They don't make sense romantically, but the movie doesn't lean into that too much.  Instead, just enjoy their chemistry as two onscreen partners, and enjoy watching Diaz play "Tom Cruise Female Co-star" in a way no one else has.
+They shoulda played the "Tom Cruise mocks Tom Cruise" angle for the movie.  It came out less than two years after his cameo appearance in Tropic Thunder and could have benefitted from that momentum (he only did Valkyrie between Tropic Thunder and Knight &amp;amp; Day).  It's Tom Cruise - but it's new, it's different.
+What's more...it would have made it clear to the audience what this movie actually is about:  it's satirical, while still trying to tell a genuine version of its subject matter.  A subject matter for which Tom Cruise is the literal poster-boy.  The movie is absurd intentionally.  Because these type of movies are fucking absurd.  They're making fun of it.  "Oh look, they stole a car and now they're driving down the highway in a convertible...so cliche.  Neither one is even watching the road while they're talking.  I guess Tom Cruise can magically sense what's ahead of him.  Wait.  Wtf?  They're actually sitting on top of a tractor trailer.  Hah.  That baited me."
+It's absurd shit like that all through the movie.  They bait you - and then sometimes they switch and other times they lean into it.  And even though he's winking at his own career, he's still turning in an earnest, genuine performance.
+This movie for me is up there with True Lies and Mr. and Mrs. Smith.  (I know mentioning those three movies together will get some criticism.)  Funny, entertaining, feel good action movies that I can just re-watch endlessly and enjoy every time.</t>
+        </is>
+      </c>
       <c r="C150" t="inlineStr">
         <is>
           <t>mission_impossible</t>
@@ -3456,12 +4256,16 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>#Barbie ’s THU previews at US #BoxOffice far from plastic… It’s FANTASTIC 22.3M (#24 biggest ever over #HarryPotterandTheHalfBloodPrince’s 22.2M), incl. WED sneaks! 2023 BIGGEST, over #GoTGVol3 17.5M! #5 biggest Post-Covid, over #TheBatman’s 21.6M 140M-170M weekend in the cards!</t>
+          <t>First thoughts after Barbie (no spoilers)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Just got out of the preview here in Germany and wanted to articulate some first thoughts for those who already saw it and feel like discussing.
+First off I was highly entertained and very glad I saw this on the big screen with all the fuzz around it. It was a special screening with Barbie decorations, champagne and ice cream and I felt like this would be the last "event movie" for a long time, considering the latest blockbusters all semi-flopping and the strikes slowing down upcoming productions.
+Trying to summarize the movie I'd say it is a very, very tongue-in-cheek self-aware advertisement for Mattel and Barbie that looks gorgeous, is full of creative, funny ideas and easter eggs and pulls you in with its charming protagonists while they go all in with the meta-jokes and fourth wall breaking. It feels like it's set up to be a modern popcultural feminist manifesto, which is an idea I fully support and applaude, even if the message is anything but subtle and even a bit overbearing at some points. The plot isn't unforeseeable but there are some surprises and the emotional beats are there.
+My gripes with the movie are that it's a bit muddied towards the end where it seems to want to achieve a little too much at once. Also I couldn't entirely shake the feeling of watching a very long, very intricate advertisement for a million dollar company by pandering to progressives who wouldn't normally support that product. I see the merit in using the Barbie brand as a Troyan horse by teaching open mindness, gender and race equality and tolerance to the masses, I just wish it wouldn't feel as much of a marketing campaign and more like a genuine story. 
+Production and set design is top notch, the soundtrack is banging and I was laughing much more than I thought I would. Overall a sweet cinematic experience with a slightly bitter taste of hypercapitalism on the side.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3476,13 +4280,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>AI Recreated Tom Cruise's Insane MI-7 Motorcycle Stunt. Epic. And AI Analysis and Docu Feature.</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
+          <t>Oppenheimer : 35mm or IMAX</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Got the option to watch both in my city. Did he use two different cameras for the two versions or is one of them converted from the other one? If it is the former I may want to watch both, but any thoughts are welcome. This is one of the movies that I look forward to most this year, and I want to get the best experience.</t>
+        </is>
+      </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -3492,17 +4300,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>From a production standpoint, was it a coincidence that both Fast X and Mission Impossible: Dead Reckoning, two action movies that came out this year, had a destructive automotive chase scene through Rome?</t>
+          <t>Oppenheimer gets pg 13 ( UA ) rating in India</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>In other countries it is rated R because of nudity and sex , in india it was rated A for a few weeks ( A is the equivalent R in india ) but a day beforr release the central board changed it to UA ( pg 13 ) , the runtime has not been shortened meaning no scenes have been reduced , the audience might expect censored cuss and zoomed screen during scenes showing nudity or sex .</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -3512,12 +4320,16 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>'Oppenheimer' cast exits London premiere after SAG-AFTRA strike is called</t>
+          <t>The Exorcist: Believer Predictions</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Caught the trailer for The Exorcist: Believer last night on IMAX in front of Oppenheimer. Packed audience seemed to find it very entertaining, with a lot chatter and bemused laughter as it ended. 
+Honestly, it looks pretty dumb, but should still be a fun movie for spooky season with a ton of callbacks for horror nerds.  With a prime mid-October (Friday the 13th) release date, there's no way this isn't going to be a hit with how well horror has been doing lately. David Gordon Green also knows how to deliver a solid scary movie, even if the last two Halloweens sucked.
+OW: 55-60 mill
+Total Gross: 120-130 Mill
+Outside shot at Halloween (2018) numbers if the movie is actually well done.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3532,17 +4344,31 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Mission: Impossible - Dead Reckoning Part One Review</t>
+          <t>Has this been the most entertaining year ever to track the box office?</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Started off with a meme horror movie blowing up in January.
+Ant Man flopped to kick things off and show Marvel's mortality. 
+March had a string of strong hits, and also Shazam putting up the most pitiful comic book movie performance ever. Showing that even with Marvel weaker DC is still ten steps behind. 
+Mario blew tf up and proved all the naysayers wrong and grossed more than even the most optimistic people projected and seemed to have a clear lock on the 2023 crown.
+Guardians paid for the sins of Quantumania but in a hilarious twist the movie was able to turn things around after a mediocre opening due to it being so good. 
+Fast X and The Little Mermaid flopped to this sub's horror, little did they know June would make them look impressive. 
+Spiderverse blew up and doubled its predecessor. 
+Flash bombed in catastrophic fashiom and did worse than anyone could ever have imagined, yet somehow still managed to be topped for worse flop of the year when Indy did even worse for its expectations.
+With Indy flopping, the Mission Impossible vs Indiana Jones debate for the next Top Gun Maverick seemed over, but then Mission Impossible also fell flat on its face. 
+Meanwhile while all of this is happening you had Elemental which when it opened was looking like the biggest bomb of the year and a death knell to Pixar, but instead it just kept going and going week after week and now it might actually breakeven.
+None of this was helped by Sound of Freedom which came out of nowhere and was a clear win for conservatives. However, that too was short lived as it had only two weeks before being overshadowed by the "wokest" movie of the year.
+Speaking of you then had Barbenheimer completely destroying everything in its path and doing better than anyone ever anticipated. A true never before seen phenomenon. Mario looked 100% secure at #1 but Barbie just came out of nowhere and pulled the rug from under Mario. Nothing new for Universal. This happened in 2015 with Jurassic World and Force Awakens. However this is a way closer and more entertaining race and Mario looked way more secure for number one before being displaced than Jurassic World did in 2015. It's not just about Barbie either. Guardians looked pretty secure for a top 3 spot by year's end but Oppenheimer is coming very close to ending that.
+Just when everyone thought DC was already 6 feet under a small pulse seems to be felt, now that we potentially have Blue Beetle possibly being the least embarrassing DC performance of the year despite being abandoned by Warner Bros.
+I'm sure November will bring plenty of surprises as well
+Tldr: 2023 has been the most entertaining box office year by far. So many twists and turns and when a consensus is reached on something, you know it's about to be wrong lol.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -3552,17 +4378,31 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Structure of Oppenheimer</t>
+          <t>Is it me or are movies way longer than normal right now?</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>In the passed 3 years or so there have been a ton of high profile block buster movies that have been pushing the run times to their limit. Ever since Endgame studios have really been letting loose with length of these things. Here's just a few examples I could think of:
+-The Batman clocked in at 3 hours nearly on the dot
+-the new Top Gun was 2 and a half hours
+-theres the new Avatar obviously which topped it's predescers run time by an episode and a half of It's Always Sunny
+-Across the Spiderverse set a record for the longest American Animated film ever made at 2 and a half hours. And this may be premature, but imma venture to say the next one is gonna be about that long too if not maybe longer.
+-the new Guardians movie was 2 and a half hours
+-Inidiana Jones and the dial of destiny was 2 and a half hours, easily longer than any previous Indie movie
+-Black Panther Wakanda Forever was 2 hours and 43 minutes, which I think seats it right behind Endgame for the longest Marvel movie
+-The new John Wick was creeping up on 3 hours
+-part one of the new Dune saga was 2 and a half hours
+-this is kind of a cheat since it was only released on streaming, but there's the 4 hour cut of Justice League. Ditto for RRR. 
+-that Elvis movie was also sneaking up and 3 hours
+-Marty Scorrcesse is coming out with a new movie that's gonna make the Irishman look lean. Not looking forward to seeing that fucker in theaters unless there's an intermission
+-and the new Mission Impossible movie is gonna be 2 hours and 43 minutes, and that's only part one of a much greater story continued in the next movie
+I'm not even saying this is a bad thing or these movies need to be shorter. In fact, with most of these movies I'd say their run times are incredibly justified, but it is noticeable, right?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -3572,14 +4412,14 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Can anything besides Barbie outgross GOTG3 and become third highest grossing of the year?</t>
+          <t>After all the "Top Gun: Maverick of 2023" talk that happened with Indiana Jones and Mission Impossible, it's a little funny that Barbie will be this year's Maverick.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>With how the opening weekend for Barbie seems to be going, it will likely outgross Guardians of the Galaxy 3 worldwide to become the second highest grossing movie of 2023 behind Super Mario Bros.
-GOTG3 will fall to #3, but is there anything that could potentially beat it for third place?
-I think the biggest candidates are The Marvels, Dune 2, and Aquaman 2, though I have trouble imagining any of them actually accomplishing it.</t>
+          <t>Despite being the polar opposite in content and form, Barbie is the movie that's going to have the 120+ opening weekend. 
+Not just that but it'll also have a pretty good awards run like Top Gun had last year. Both films that aren't your typical Oscar fare, getting in because of how popular it was.
+It's pretty funny looking back now.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3594,12 +4434,13 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Is anyone else confused about the Barbie movie?</t>
+          <t>Will the Barbenheimer double feature hurt the legs of both movies?</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Obviously will aid in the OW for both but will people run back to the theater when they will have just spent money for 2 movies? It’s been trending like an event so hopefully it ends up not being a one-time watch for the GA. 
+Maybe I’m overthinking this though lol</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3614,12 +4455,21 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Barbie 100% gratuit</t>
+          <t>Region by region comparison. Mario vs Barbie</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>With Barbie's absolutely explosive debut it's very hard to see it missing 1b at this point, however passing Mario doesn't look to be in the cards. Looking at it from a major region perspective vs Mario here is how I see it shaking out 
+Domestic: Mario (575m), Barbie (500m)
+LATAM: Mario (200m), Barbie (200m)
+Europe: Mario (325m), Barbie (275m)
+Asia: Mario (175m), Barbie (100m)
+Oceania: Mario (40m), Barbie (50m)
+Rest of the world: Mario (40m), Barbie (20m)
+OVERALL: Mario (1.35b) and Barbie (1.15b)
+The biggest issue for Barbie matching Mario is Asia and that's largely because a Japanese breakout does not seem to be in the cards where Mario basically made 100m. The rest of the world territories are the other smaller thing holding it back against matching Mario as it won't release in all middle east territories and doesn't seem particulary popular there or in Africa.
+With all this said, this shouldn't be taken a slight against Barbie as it will be the 5th phenomenon run post pandemic, joining the likes of No Way Home, Top Gun Maverick, Avatar Way of Water, and The Super Mario Bros Movie. A pre pandemic Barbie likely would have made 1.4b competing with the likes of Frozen II for biggest female led movie.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3634,10 +4484,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>International Box Office’s July Mega Month Propelled by ‘Barbie,’ ‘Oppenheimer’ and Chinese Blockbusters</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
+          <t>Wife and I went to "Barbie". Her complaint: why everyone so old? Where did all young actors go?</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>My wife and I went to see Barbie yesterday, and her informed complaint this morning was that everyone was way older than she thought they would be. The complaint, in order of appearance, applied to:
+- Gosling (She saw him in particular as someone over 40 who goes to lengths to look younger)
+- His main Ken counterpart
+- All other Kens
+- Barbies (well, perhaps not the titular one, she actually was OK)
+Her reasoning was that when she played Barbies, she imagined them from late teens to mid-20es, as, as a kid, people after 30 felt ancient. I didn't quite know what to say; true, I used an argument that Gosling is an established actor and the producers didn't want to take risks, but other Kens?
+ Is Hollywood so badly out of young actors that they couldn't find enough beach bum type actors to fill a beach?</t>
+        </is>
+      </c>
       <c r="C160" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -3650,13 +4510,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BoxOfficeReport.com on Twitter - Paramount's Teenage Mutant Ninja Turtles: Mutant Mayhem grossed $28.01M this weekend (from 3,858 locations). Total domestic gross stands at $43.08M.</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
+          <t>Excellent booking for Mission: Impossible – Dead Reckoning in south India</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>will be the biggest Hollywood opener this year in india</t>
+        </is>
+      </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>tmnt</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -3666,13 +4530,23 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Oppenheimer formats and aspect ratio infographic</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr"/>
+          <t>Why do emotional moments in modern films always need to be undercut with a bad joke?</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>I saw the *Barbie* movie yesterday and was really enjoying it. At the climax, America Ferrera gets this incredible speech about the conflicting rules that is part of being a woman. After everything that had happened with her character and Generic Barbie, it was a real moment of catharsis.
+And then about two seconds later they had this out of nowhere joke about the Snyder cut.
+In *Thor Ragnarok*, the lead's home is destroyed and it's played for comedy even though in the next two films with the character, they try to act like we should be sad about it even though they pulled a cheap punchline about "foundations." 
+My question is, why does this happen?
+Are audiences jaded by sincere emotion in films? Are studio executives forcing writers to put more comedy in certain places? Has art just changed in a way that Westerns were once popular and now they are not?
+I feel like if *The Lord of the Rings* films came out today, they would be shredded as there's never a wink at the audience during all their emotional moments.
+What are your thoughts?</t>
+        </is>
+      </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -3682,21 +4556,35 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Overused fonts on posters</t>
+          <t>Rescheduling Paramount's 2023 Slate</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>So I've seen some movie posters which commonly use a certain font. Sometimes it's so common that it becomes a trope for a certain movie genre.
-Take for example Helvetica. I've seen them on at least 20 different movie posters, and they sometimes use different variants (especially the condensed ones).
-Agency FB is another example, which is used in the Mission Impossible film series.
-Streaming service film posters, on the other hand, use minimalist typefaces like Montserrat or Momentum Sans.
-What other fonts are overused in movie posters?</t>
+          <t>Paramount had such an amazing lineup last year with the likes of Scream, Jackass Forever, The Lost City, Smile, Sonic the Hedgehog 2, and Top Gun: Maverick. The 2023 lineup could’ve been similar. However, the biggest problem with Paramount’s 2023 lineup is the release dates. Just like 2018, Paramount decided to choose some awful release dates for some of their films, so I decided to shift some release dates. Not all these films have released yet, so they could do well on their current release date. However, keep in mind that there is the SAG strike, which prevents actors from promoting their films. Now, if a Paramount executive foresaw what happened in 2023, I’m sure they’d make changes. Here’s the release dates I think would work better.
+**80 for Brady** \- (Initial Release: February 3) **January 27**
+This film was released on the Super Bowl weekend, which is appropriate because the film is about four old women going to the Super Bowl in person. However, the problem is that it only gave the film one (EDIT: two) weekend to capitalize on that. Moving the film up by a week earlier could've given the film two (EDIT: three) weeks to capitalize on the Super Bowl, and the film could've had a shot at $50M worldwide. While still not at the breakeven point, Paramount would be able to minimize losses.
+EDIT: I don’t know why I thought the Super Bowl was the first Sunday of February.
+**Dungeons &amp;amp; Dragons: Honor Among Thieves** \- (Initial Release: March 31) **February 3**
+Being squished between John Wick and Mario was a mistake. At this time, the only film people would bother to go to the movie theaters to see would be to watch Avatar: The Way of Water. Dungeons &amp;amp; Dragons: Honor Among Thieves could've beaten Ant-Man and the Wasp: Quantumania to be the first blockbuster of 2023. It could've had a good two weeks with no competition instead of being squished by John Wick: Chapter 4 and The Super Mario Bros. Movie. An early February release date could've led to the film possibly grossing as much as $400M worldwide, being a moderate success for Paramount.
+**Scream VI** \- **March 10**
+Scream VI should keep its spot. Congrats for being a hit for Paramount.
+**Transformers: Rise of the Beasts** \- (Initial Release: June 9) **April 21**
+Now you may argue that it wouldn't make sense for Paramount to release a Transformers film in April, and that's a fair point. However, Transformers One is releasing in September (2024), which is worse. The Super Mario Bros. Movie went unopposed for the entire month of April. Transformers: Rise of the Beasts could've taken the April spot and have less competition. Instead of being squished by Spider-Man: Across the Spider-Verse and The Flash, Transformers: Rise of the Beasts would have dealt with the third weekend of The Super Mario Bros. Movie and Guardians of the Galaxy Volume 3 just two weeks away. Transformers: Rise of the Beasts could've had a shot at making as much as $600M worldwide.
+**Killers of the Flower Moon** \- (Initial Release: October 6) **May 26**
+The biggest reason I have for moving up Killers of the Flower Moon is so that it can be before the SAG strike. I wanted to have one Paramount film a month before the strike and that left me with a May release but still after its debut at Cannes. I don’t think Apple and Paramount expect the film to make a ton of money, but I think a wide release immediately after a Cannes debut would've helped, unlike the two Disney films that got hurt from Cannes.
+**Mission: Impossible - Dead Reckoning Part One** \- (Initial Release: July 12) **June 21**
+This would've required a Paramount executive to have some foresight and see that The Flash and Indiana Jones and the Dial of Destiny would be massive flops. Had they done that though, Mission: Impossible - Dead Reckoning Part One could've done better than how it's currently doing. The biggest reason why it's better to go against Indiana Jones and the Dial of Destiny instead of Oppenheimer, is the fact that Mission: Impossible could've easily shared the IMAX screens with Dial of Destiny compared to Oppenheimer, which markets viewing the film on IMAX as a necessity. Instead of eight days of IMAX screenings for Mission: Impossible, it could have almost a month's worth of IMAX screenings that it will have to share with Dial of Destiny.
+**Teenage Mutant Ninja Turtles: Mutant Mayhem** \- (Initial Release: August 2) **July 5**
+I know Ruby Gillman, Teenage Kraken released five days earlier, but no one cares about that movie. I'd move this film up, so that its promotion wouldn't be affected by the SAG strike. It would've worked better as the family film to watch, while the adults watch Sound of Freedom or Barbie or Oppenheimer. This would also give the film two and a half weekends to dominate the box office instead of one.
+**PAW Patrol: The Mighty Movie** \- (Initial Release: September 29) **October 20**
+Even though I pushed every Paramount film (except Scream VI) forward, PAW Patrol: The Mighty Movie is a film that should be pushed back. The SAG strike shouldn't affect the film as much because five years don't go on social media or watch red carpet events. Even though the September releases are targeted toward adults, October 20 would be better for the film because October has less films than September. I think Paramount should end the year on a profitable note instead of a money loser like Killers of the Flower Moon. November and December are too packed for a film like this to succeed. October 20 could also give PAW Patrol: The Mighty Movie a shot at topping the box office.
+I'm not saying these dates are perfect, but Paramount's had a few missed opportunities here and there.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -3706,10 +4594,16 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sound of Freedom has outpaced Mission Impossible. That is insane. Despite what you think of the movie - it’s grassroots growth is commendable.</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
+          <t>Could I watch Dead Reckoning Part 1 without having seen Mission: Impossible 2-6?</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>I’ve seen the 1st Mission Impossible, but the rest of the movies were taken off of Netflix in my country. I wanted to watch the rest and I was planning on watching them but I didn’t have time to watch the rest of them. 
+My question is whether or not I’ll be able to understand Dead Reckoning if I haven’t seen Mission Impossible 2-6. I know it would probably be better if I’ve seen all 6 of them before I watch the seventh but I was unable to.
+Will I be able to understand Dead Reckoning? How confused will I be?</t>
+        </is>
+      </c>
       <c r="C164" t="inlineStr">
         <is>
           <t>mission_impossible</t>
@@ -3722,17 +4616,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Tom Cruise can speak in Hindi</t>
+          <t>Were there any moments where studios learned the *right* lesson from a film’s success?</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>This is coming off the news of how Mattel wants to make their own cinematic universe after the success of Barbie. Obviously the lesson we want all studios to take from this is to give acclaimed creatives the opportunity to bring artistic vision to big IPs, but that doesn’t seem to be happen. Everyone was pessimistic after the release knowing they would take the wrong lesson (and it’s looking like they did), but I wanna ask, were there any moments where studios took the right lesson?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -3742,13 +4636,18 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>What is the reason a movie like Venom 2 and Ant Man 3 get weak reviews but still cross 200 million but a highly praised movie like Dead Reckoning will struggle to reach that mark? Are people just automatically more interested in superhero movies?</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
+          <t>How come in America if a movie has people of color, women or LGBTQ people. It is criticized for being "woke" , "political" or , "promoting an agenda." Even if such people are in a scene for 5 seconds.</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>How come in America if a movie has people of color, women or LGBTQ people. It is criticized for being "woke" , "political" or , "promoting an agenda." Even if such people are in a scene for 5 seconds. 
+Can someone explain this too me. Apparently there is a transgender doctor in the barbie movie. Has a brief scene and people are already angry.</t>
+        </is>
+      </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -3758,13 +4657,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Will Joker or Oppenheimer Gross more?</t>
+          <t>Will Oppenheimer cross Spiderverse?</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>I don’t see Oppenheimer making $1B
-[View Poll](https://www.reddit.com/poll/15nggjw)</t>
+          <t>It looks like it might cross $700M WW which spiderverse might not able to reach</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3779,13 +4677,20 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Oppenheimer is FANTASTIC but FLAWED - IMAX 70mm Movie Review</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr"/>
+          <t>I hate how social media has turned movies into a competition</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>I saw a tweet today saying, "Margot Robbie could do Oppenheimer but Cillian Murphy couldn't do Barbie"
+When did movies become sports? Why does your fandom of Margot or any other actor mean you have to put down another performer? Or people who are MCU fanboys so they take joy in the failure of a DC film? I already know there are going to be people celebrating Barbie beating Oppenheimer at the box office like "hahahahaha suck it Christopher Nolan" completely ignoring the fact that it's good for movies that there are two films with such high levels of interest opening at the same time.
+It's art, not sports. It's not supposed to be a competition. Its supposed to be a celebration of auteurs successfully fulfilling their visions.
+Rant over.</t>
+        </is>
+      </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -3795,17 +4700,19 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Christopher Nolan Says ‘Oppenheimer’ and ‘Barbie’ Opening Together Is ‘Terrific’ Because a ‘Crowded’ Marketplace Is a ‘Healthy’ One: “We’ve Been Waiting For This”</t>
+          <t>What’s up with movies never using the correct foreign language?</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>As a bit of context, just saw Oppenheimer in Belgium. In one of the scenes Oppenheimer explains his paper on atoms at the University of Leiden (the Netherlands) in Dutch. However, the actor actually spoke German. 
+As I saw the movie in the Dutch speaking part of Belgium, everybody in the cinema laughed. This is an occurrence that is even memed by Netflix as this mixup between German and Dutch happens so often. 
+So what gives? You would expect from a Christopher Nolan movie more research before filming.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -3815,17 +4722,20 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>[Brazil] Oppenheimer grosses ~$480k USD on opening day in Brazil. Tracking for the biggest non-Batman Nolan opening despite debuting against Barbie (projected to be at least the 3rd biggest opening ever in Brazil).</t>
+          <t>Hypothesis: Playing "Iron Man" marvel-ized Robert Downey Jr.'s acting. Discuss!</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>[deleted]</t>
+          <t>Two things:
+1. I love the guy
+2. I think in recent years his acting lacks a certain subtlety and nuance. It feels like his bonvivant-image seeps into his roles. In some he is typecast and it doesn't matter so much (e.g. "The Judge"), but when he is not typecast (like in "Oppenheimer") he seems a bit over-the-top and comic-booky. I get, that he shall be the adversary to the tranquil portrayal of Oppenheimer. But he could have played that with much less goofiness in his expressions etc.
+I'm not sure, maybe I am being unfair. It's just that I liked his acting pre-Iron Man way more and am interested in your opinions. Cheers!</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -3835,17 +4745,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Going to see Oppenheimer tonight</t>
+          <t>Mission Impossible Dead Reckoning Part One Which Format to Best Experience?</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Going to see Oppenheimer tonight, looking forward to it</t>
+          <t>I live in Turkey and wanna watch the new Mission Impossible movie in best experience. I heard that movie was shot on IMAX cameras but the ratio is same with a normal movie. Is it true? I think i am going to enjoy 4dx/d-box but people say its for just fun and you cant focus to the movie. But i heard them saying movies like Top Gun:Maverick are so good in 4dx. Also i heard them saying 4dx is following the movie but D-BOX is experiencing the movie. I love to try all formats for specific movies. What would you recommend me to watch that movie? Also there is a huge IMAX screen near me. Even movie does not expand and keeps same ratio all, it can be good experience. So which format i should go? Thanks...</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -3855,17 +4765,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Indiana Jones and the Dial of Destiny gets nuked by Mission Impossible Dead Reckoning Part 1 in South Korea. Drops 87.2% in its 3rd weekend down to $146k. The likely final total (&amp;lt;$7M) will end at about 1/4th of Kingdom of the Crystal Skull's total ($26.5M).</t>
+          <t>Can Barbenheimer overtake Star Wars: The Force Awakens? (Domestic)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>A disastrous performance by any metric.   WoM is not very good but the release date combined with fierce competition sealed Indy's fate.  We might see another big drop off (albeit less extreme) in Japan due to the big opening of How Do You Live? combined with MI DR Part 1 opening on July 21.</t>
+          <t>I think it will, or at least it seems so at the moment.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -3875,18 +4785,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Barbie is currently sitting on a 2.95x multiplier from its opening weekend; Oppenheimer's is currently 2.89x. Which one ends their run with the higher multiplier?</t>
+          <t>Mission Impossible Premature Doomsaying?</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>I think this will continue to be close since while Barbie will lose the school holiday weekdays which have been so strong for it up to now, Oppy will also lose its IMAX showings at around the same time which have been key in its run.
-[View Poll](https://www.reddit.com/poll/15muo68)</t>
+          <t>I find it very depressing to see people already writing off this movie as yet another failure when there is already word on how the film will rely on strong word of mouth to continue.  It should.  Sure, it’s budgeted high, but I still feel sure it will leg out.  No reason to get bent out of shape for one Monday.  The real test is it’s staying power.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -3896,18 +4805,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Do you think BARBIE can pass $300M DOM while The Little Mermaid couldn’t?</t>
+          <t>Where will MI: Dead Reckoning Part 2 move to?</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>[deleted]
-[View Poll](https://www.reddit.com/poll/14uhzfn)</t>
+          <t>Since it's most likely not making its current date (June 28, 2024). Where will it move to? Can it stay in 2024? I think they try for something like December 20,2024 first and if it can't make that it's off to Summer 2025.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -3917,13 +4825,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Barbie it's going to have like a 15% drop on Sunday, so around $93m is likely.</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+          <t>Mission impossible worldwide</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Could dead reckoning be the first mission impossible movie not to finish top 10 worldwide end of the yr?</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -3933,13 +4845,21 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ALL-TIME biggest 2nd wknd #boxoffice: $149.2M #StarWars TFA $147.4M #AvengersEndgame $114.8M #AvengersInfinityWar $111.7M #BlackPanther $106.6M #JurassicWorld $103.1M #Avengers $93M #BARBIE $92.3M #SuperMarioBros $90.4M #BeautyAndTheBeast $90M #TopGunMaverick</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr"/>
+          <t>Opinions on multi-part movies?</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Recently I saw both 'Mission Impossible Dead Reckoning' and 'Across the Spider verse' and a thought came to mind. The movies do not have good endings. 
+Don't get me wrong, sequels are great but those movies have satisfying conclusions meanwhile multi-parters like mission impossible have such a weird ending. I would not mind if they extended the run time by 1 hour to include the final act.
+Overall, I think these films need to either extend their runtime or finish with a more satisfying conclusion.
+I feel like the movies are suffering quality wise due to their conclusions and are worse off as a result.
+What do you guys think about these 2/3 part movies? Do you have suggestions for how to improve the problems or are the films fine?</t>
+        </is>
+      </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -3949,13 +4869,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>OPPENHEIMER 70MM IMAX film print assembly at Science Museum, London.</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr"/>
+          <t>Barbie Trailer Different in theater vs online</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>I’ve seen the Barbie trailer a couple of times in the theater and noticed the trailer is cut differently. There’s a part where one of the Barbies yells flat feet and makes a throw up noise, but they don’t show it in theaters. Anyone else notice this? Thought it was weird. I think it’s important to note that the Barbie that yells this is a transgender woman.</t>
+        </is>
+      </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -3965,13 +4889,63 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Robert Downey Jr. Calls Oppenheimer 'The Best Film I've Ever Been In'</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr"/>
+          <t>Barbie X Oppenheimer-courtesy of ChatGPT</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Title: Oppenheimer's Quest for Knowledge in Barbie's World
+INT. BARBIE'S DREAM HOUSE - DAY
+Dr. ROBERT OPPENHEIMER, dressed in a suit, enters BARBIE'S glamorous Dream House. He looks around, marveling at the vibrant colors and luxurious decor.
+OPPENHEIMER
+(amazed)
+Barbie, your Dream House is truly a testament to creativity and style. It's a delight to be here.
+BARBIE, dressed in a fashionable outfit, greets Oppenheimer with a warm smile.
+BARBIE
+(thrilled)
+Thank you, Oppenheimer! I'm so excited to show you around and share my world with you.
+OPPENHEIMER
+(curiously)
+Barbie, as a renowned physicist, I have been studying nuclear energy and its implications. I must admit, I'm quite curious about how it relates to your world.
+BARBIE
+(enthusiastically)
+Oh, Oppenheimer, I'm happy to enlighten you! Nuclear energy has a significant impact on our lives, just like fashion and design. Let's explore together!
+Barbie leads Oppenheimer through the various rooms of the Dream House, showcasing its splendor and discussing their shared interests.
+BARBIE
+(pointing)
+This is the Glam Room, where I get ready for fabulous events. And here is the Fashion Studio, where I design my own clothing collections.
+OPPENHEIMER
+(fascinated)
+Your passion for fashion is evident, Barbie. But how does it connect to nuclear energy?
+BARBIE
+(smiling)
+Oppenheimer, just like fashion trends evolve, so does technology. We can find innovative ways to incorporate sustainable materials and energy-efficient practices into the fashion industry.
+OPPENHEIMER
+(nods)
+Ah, I see the connection. It's about embracing advancements and ensuring responsible practices, both in energy and design.
+As they continue exploring, they arrive at Barbie's futuristic, energy-efficient Dream House Control Room.
+BARBIE
+(excitedly)
+And here we have the Control Room, Oppenheimer! It's where I monitor and optimize the energy consumption of the Dream House.
+OPPENHEIMER
+(impressed)
+Remarkable, Barbie! You've implemented energy management systems to reduce your ecological footprint. It aligns with my research on harnessing nuclear energy for sustainable power.
+BARBIE
+(enthusiastically)
+Exactly, Oppenheimer! By embracing clean energy solutions, we can create a better world for future generations. It's all about using knowledge and technology for positive change.
+OPPENHEIMER
+(smiling)
+Indeed, Barbie. Knowledge is our greatest asset, and when applied responsibly, it can transform lives. We must ensure that nuclear energy is harnessed safely and for peaceful purposes.
+BARBIE
+(nods)
+Absolutely, Oppenheimer. It's about striking a balance between progress and responsibility, just like in fashion, where we strive for innovation while respecting ethical practices.
+They continue their journey through the Dream House, discussing the intersections of fashion, responsible energy consumption, and the importance of education.
+FADE OUT.</t>
+        </is>
+      </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -3981,17 +4955,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Steven Soderbergh on Helping Christopher Nolan Early in His Career by Getting Him His 1st Studio Meeting: “Chris Wanted to Do ‘Insomnia’ but WB Wouldn’t Take the Meeting. The Executive Didn’t Like ‘Memento”</t>
+          <t>Who is Darkness's Father in Legend (1985)?</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>[deleted]</t>
+          <t>One of my favorite fantasy movies is the 1985 movie, Legend, starring Tim Curry and Tom Cruise. So, I know that the Lord of Darkness, played by Tim Curry, is the manifestation of evil, but in the movie, we hear a bigger force speak to Darkness. This voice seems to be evil, given that it sounds like the Horned King from Black Cauldron. This evil voice seems to be Darkness's father, as Darkness calls him so. He seems to be taking orders from this evil, unseen force. Who is he? He is evil and of a greater power than Darkness but Darkness is the literal manifestation of evil, or is he? If Darkness is not the embodiment of evil, then who is he? And who is his unseen father?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -4001,17 +4975,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Was having 'Oppenheimer' come out the same day as 'Barbie' unintentionally the best marketing strategy for a movie ever?</t>
+          <t>Let's Discuss Christopher Nolan's "Oppenheimer" - Are You Excited?</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>What are your thoughts on Christopher Nolan's upcoming movie "Oppenheimer"? Personally, I am very excited because the main role is being played by Cillian Murphy, it is based on real-life events, and the fact that it will be shot on 70mm film has got me hyped up for reasons I can't quite explain. So, what are your thoughts on the film, and do you plan on watching it?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4021,12 +4995,15 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>What are your thoughts about Oppenheimer?</t>
+          <t>Would it be better to see Oppenheimer in Cinemark 70mm (non-IMAX) or 35mm XD</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Would it be better to see Oppenheimer in 70mm (non-IMAX) or 35mm XD
+I don’t really understand the differences between the 2, but I’ve been looking forward to this movie for years and I want the best experience. 
+The 70mm theater is about an hour away, while the 35mm XD is down the road. 
+If someone could ELi5 why the perforations of film matter, like 5 perf 70mm vs 15 perf 70mm that would be awesome.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4041,14 +5018,21 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Format vs comfortable seating for a popular movie in theaters</t>
+          <t>Christopher Nolan’s “Memento” does not stand up well today compared to his later work</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>I just reserved tickets to see Oppenheimer in 70mm, and my seats are front row  and to the left.   There are all sorts of theaters in the area with normal screens and better seating.
-I also wanted to see Avatar 2 in 48fps last year and made a similar compromise.
-How would other moviegoers approach the issue of format vs seating?</t>
+          <t>I’m not sure I’m in the minority here, but I just saw Nolan’s 2000 film Memento after seeing it at the top of many Nolan lists on Reddit and I was pretty disappointed. I don’t think it’s a terrible film, and I believe it does a lot of things right, but I found it to be more frustrating to watch than not compared to his other films.
+*SPOILERS AHEAD*
+What I LIKE: 
+1. I was constantly trying to figure out who Teddy really was. That was neat.
+2. Definitely made me think “what would I do to try and live in this condition” fun kind of thought experiment
+What I DONT like:
+Memento begins with being introduced to the character at the end of the story and goes backwards. After the second time we jump back all I could think was “oh no, tell me this isn’t the entire movie” and it was. I respect how the film’s structure puts you in the main character’s position, but man is it a drag to watch. And by going backwards the whole time, it takes away from the sense of any real story progression. The whole film is “but how do you think about what you know given THIS context” which works well in a lot of Nolan’s other movies paired with an ongoing plot to anchor the film, but in Memento, it’s just that exact same trope all the way down. So now I’m also just immediately thinking how each scene is gonna be a twist, making the ending incredibly obvious and by the time we get there there’s no pay off. Like yeah, I got the idea of how you chose this like 10 flashbacks ago. 
+Do you a share a similar experience? Do you think the film holds up today? I feel like seeing this in 2000 it might have been more mind blowing compared to watching it today after being exposed to so much of Nolan’s work which uses this trope more effectively. What do you think?
+Edit 1: okay so I’m definitely in the minority haha. That’s fine! But y’all also made me realize the other reason I don’t like this film as much: every flashback is separated by a black and white timeline which is mostly the main character just talking on the phone either giving exposition or telling a long story about Sammy, which isn’t as engaging broken up and IMO kills the suspense of other scenes.
+Edit 2: first off I like the discussion and appreciate it! Second, I acknowledge the cuts in the film and structure are all intentional. The hairpin story structure IS creative, and tbf I don’t know another movie that does this. I still think it’s a decent movie. I just think that no matter how you do it, the storyline structure is just not as fun to watch. We know the ending, so we’re only ever getting more context instead of driving the plot forward, and the forward storyline is shorter and much slower, and by necessity cuts the tension of scenes. And the twist from the end is predictable so the payoff doesn’t work. “A man with short term memory loss hunts down his wife’s murderer” oh no there’s no way he killed her and forgot! The setup is obvious from the Sammy story too. Everything done here to grip the audience, such as characters, twists, timeline fuckery, suspense, and mystery are all done better in his other films, which is WHY I think this film looks worse in comparison</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4063,13 +5047,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Tom Cruise Wants To Continue Making ‘Mission: Impossible’ Movies Into His 80s Like Harrison Ford With ‘Indiana Jones’</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr"/>
+          <t>Fandango showing times for a movie a day before it's supposed to be in theaters?</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>I want to go see Oppenheimer in theaters when it comes out. I looked up the release date and Google said Friday, July 21st but in the Fandango app, it said there were screenings of the movie on Thursday, July 20th ( a day before it was supposed to release). Does anyone know why this is?</t>
+        </is>
+      </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -4079,13 +5067,26 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Oppenheimer (2023) Movie Review</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr"/>
+          <t>Do you think the Barbie film will pass the reverse bechdel test?</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>This topic came up in discussion with some friends and I was curious if others thought if it would.
+For the ones who forgot or don't know, a movie only passes the Bechdel Test if it meets the following requirements:
+* The movie has at least two women in it
+* who talk to each other
+* about something other than a man
+The reverse bechdel test replaces woman for men in the criteria. So, Barbie would NOT pass a reverse Bechdel Test if it:
+* DOES NOT have at least two men in it
+* who do NOT talk to each other
+* about something other than women
+Thank you to everyone in advance :)</t>
+        </is>
+      </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -4095,13 +5096,30 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>‘Barbenheimer’ creates a world record in UK</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
+          <t>Barbie and Oppenheimer are likely to both break into the Top-10 live-action movies of all-time that weren‘t part of an already existing Hollywood-franchise</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Here is the list of the Top-10 highest grossing live-action (= non-animated) movies who were not part of an already existing Hollywood-franchise at the time of their release (so they were no sequels, prequels, spinoffs, remakes, cinematic universes, etc).
+For Barbie I estimated a 1.5bn outcome, so Barbie will end up 3rd in this ranking.
+1)Avatar (2.92bn) / 2009
+2)Titanic (2.26bn) / 1997
+3)Barbie (1.5bn) / 2023
+4)Jurassic Park (1.11bn) / 1993
+5)Harry Potter and the Sorcerers Stone (1.02bn) / 2001
+6)Bohemian Rapsody (910M) / 2018
+7)LotR: The Fellowship of the Ring (898M) / 2001
+8)Inception (870M) / 2010
+9)Spider-Man (825M) / 2002
+10)Independence Day (817M) / 1996
+Oppenheimer has a great chance to reach the Top-10, it even has a shot for #6 (Bohemian Rapsody, 910M) or even to break into the Top-5 if it’s going completely crazy in China and Korea. But Top-10 (817M) is almost a sure thing already.
+I just think it’s very interesting and remarkable that two movies who were released on the SAME DAY likely will both be in this Top-10 Hollywood list OF ALL TIME.</t>
+        </is>
+      </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4111,18 +5129,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Barbie &amp;amp; Margot Robbie Haters Rant Post</t>
+          <t>Physical film flickering (35mm)</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>I thought that it would be good to create a post where all the Barbie haters can rant that the plastic creature stomped on them and their Oppeinheimer with ease. Also for all the Margot Robbie haters who seem to be very active on this sub. 
-Come and post your rants below. How awful does it feel? What coping mechanism will you use to go through this tough period of time?</t>
+          <t>I decided to see the new Oppenheimer movie in 35mm film. It was the first time I saw a movie that was projected physically, it was a nice movie but there was this flickering that broke the immersion a bit. The flickering was only noticable on the bright parts of the screen (ex: if there was a landscape with a bright sky on screen then you would notice that the sky was flickering). Is this a normal part of the experience (35mm)? Or was that an issue with the projector?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -4132,20 +5149,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Box Office Mojo vs The-Numbers</t>
+          <t>Forgetting plot points</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>I know this has been discussed in the past but not that recently. I always am curious which box office tracker do you find more accurate? I am using 2023 Worldwide charts as a comparison. As you can see both of these charts have very similar numbers for most of the films. Glaring differences: Barbie gross significantly higher on BOM, and few films higher slightly on each (Oppenheimer and Fast X for the-numbers, transformers and indy for BOM). The biggest glaring difference seems to be the lack of Chinese films on the BOM top 20. Did BOM miscalculate those grosses or forget to include the Chinese market entirely? I personally prefer using the-numbers but wanted to know if you find that BOM is actually still much more accurate.
-[The Numbers](https://preview.redd.it/9msmlufem0fb1.png?width=915&amp;amp;format=png&amp;amp;auto=webp&amp;amp;s=4eee3dd0a2648d550777a64b97dc6256c95324e9)
-[Box Office Mojo](https://preview.redd.it/6bgerwvnl0fb1.png?width=993&amp;amp;format=png&amp;amp;auto=webp&amp;amp;s=59bed770040ae97193d78e83234fd365cdd53475)
-&amp;amp;#x200B;</t>
+          <t>I saw Oppenheimer on Saturday and Im already forgetting some details of the movies like if Einstein wrote a letter to the president telling him to make an atomic bomb or not make an atomic bomb and the entire situation regarding the soviets making a bomb. Is this normal or is there something wrong with my mind?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -4155,59 +5169,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Barbie surpasses Doctor Strange 2 &amp;amp; Jurassic World 3 &amp;amp; Fantastic Beasts 3, Oppenheimer beats Interstellar &amp;amp; Tenet, Elemental passes Cars 3 &amp;amp; Coco, The Meg: The Trench feasts opening +78.7% bigger than The Meg, Teenage Mutant Ninja Turtles: Mutant Mayhem disappoints - Germany Box Office</t>
+          <t>Does Barbie 2 work without Greta Gerwig box office wise?</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://preview.redd.it/es7fi2zye4hb1.jpg?width=1365&amp;amp;format=pjpg&amp;amp;auto=webp&amp;amp;s=5b13c3690857ad99f1e777ebb2c1e1ee21ba7870
-&amp;amp;#x200B;
-|Nr.|Film|Weekend Ticket Sales|Drop|Total Ticket Sales|Weekend|Theaters|Average|Final Total (Prediction)|
-|:-|:-|:-|:-|:-|:-|:-|:-|:-|
-|1|Barbie|702,316|\-15%|3,263,560|3|816|861|5M|
-|2|Oppenheimer|522,527|\-13%|2,243,428|3|677|772|3.25M|
-|3|The Meg - The Trench|275,637|\-|305,779|New|418|659|800K|
-|4|Elemental|146,555|\-2%|1,405,898|7|602|243|1.75M|
-|5|Mission: Impossible - Dead Reckoning Part One|107,892|\-32%|986,350|4|566|191|1.2M|
-|6|Lassie - A New Adventure|98,343|\-0%|308,428|2|597|165|550K|
-|7|Ladybug &amp;amp; Cat Noir - The Movie|94,982|\-20%|955,110|5|638|149|1.15M|
-|8|Teenage Mutant Ninja Turtles - Mutant Mayhem|93,821|\-|106,606|New|458|205|350K|
-|9|Indiana Jones and the Dial of Destiny|69,455|\-27%|1,241,911|6|460|151|1.35M|
-|10|Haunted Mansion (2023)|33,427|\-50%|136,405|2|358|93|200K|
-|11|Insidious - The Red Door|29,570|\-39%|412,891|5|294|101|475K|
-|12|Talk to Me|21,616|\-24%|75,472|2|200|108|125K|
-|13|The Young Lovers|16,367|\-|17,698|New|87|188|75K|
-|14|The Super Mario Bros. Movie|14,942|\-3%|5,218,926|18|244|61|5.25M|
-|15|The Little Mermaid (2023)|12,314|\-26%|1,244,902|11|219|56|1.275M|
-|16|Ruby Gillman, Teenage Kraken|11,972|\-28%|192,966|6|273|44|220K|
-|17|No Hard Feelings|11,639|\-43%|466,751|7|196|59|500K|
-|18|L'immensità|7,257|\-20%|23,421|2|85|85|50K|
-|19|Asteroid City|6,891|\-17%|224,798|8|139|50|240K|
-|20|Rumba Therapy|6,473|\-8%|129,392|7|89|73|150K|
-&amp;amp;#x200B;
-|Nr.|Film|Weekend Box Office|Drop|Total Box Office|Weekend|Theaters|Average|Final Total (Prediction)|
-|:-|:-|:-|:-|:-|:-|:-|:-|:-|
-|1|Barbie|€6,802,647|\-14.4%|€30,584,677|3|816|€8,337|€47.5M|
-|2|Oppenheimer|€6,179,578|\-12.7%|€25,979,611|3|677|€9,128|€37.5M|
-|3|The Meg - The Trench|€2,940,566|\-|€3,271,214|New|418|€7,035|€8.5M|
-|4|Mission: Impossible - Dead Reckoning Part One|€1,206,725|\-31.8%|€11,126,122|4|566|€2,132|€13.5M|
-|5|Elemental|€1,156,465|\-3.1%|€11,424,099|7|602|€1,921|€14M|
-|6|Teenage Mutant Ninja Turtles - Mutant Mayhem|€802,159|\-|€910,647|New|458|€1,751|€3.2M|
-|7|Indiana Jones and the Dial of Destiny|€750,929|\-24.9%|€13,541,250|6|460|€1,632|€14.75M|
-|8|Lassie - A New Adventure|€741,162|\-2.1%|€2,305,698|2|597|€1,241|€4M|
-|9|Ladybug &amp;amp; Cat Noir - The Movie|€718,331|\-21.9%|€7,471,412|5|638|€1,126|€9M|
-|10|Haunted Mansion (2023)|€312,275|\-51.3%|€1,261,943|2|358|€872|€1.85M|
-|11|Insidious - The Red Door|€300,749|\-38%|€4,086,258|5|294|€1,023|€4.7M|
-|12|Talk to Me|€214,634|\-24.2%|€691,089|2|200|€1,073|€1.1M|
-|13|The Young Lovers|€150,279|\-|€159,304|New|87|€1,727|€650K|
-|14|The Super Mario Bros. Movie|€121,126|\-1.8%|€51,073,453|18|244|€496|€51.35M|
-|15|No Hard Feelings|€114,304|\-43.3%|€4,389,024|7|196|€583|€4.65M|
-|16|The Little Mermaid (2023)|€110,139|\-27%|€12,405,304|11|219|€503|€12.65M|
-|17|Ruby Gillman, Teenage Kraken|€88,087|\-26.5%|€1,444,662|6|273|€323|€1.6M|
-|18|L'immensità|€67,450|\-19.5%|€210,377|2|85|€794|€450K|
-|19|Asteroid City|€62,802|\-16.5%|€2,056,863|8|139|€452|€2.2M|
-|20|Rumba Therapy|€55,981|\-12.7%|€1,116,596|7|89|€629|€1.3M|
-&amp;amp;#x200B;</t>
+          <t>Greta Gerwig has stated she has zero plans to do a sequel but we know Zaslav and WB will move forward to reap more cash..I dont think Zazlav realizes that Barbie vision was Greta complete utter vision. If they move on with another director it's a huge risk and gamble and if it's a flop box office they will regret it. Does Barbie work without Gerwig?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4222,12 +5189,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Barbie vs Mario - Weekend 2 Int’I Markets Comparison</t>
+          <t>Does the success of Barbie affect The Fall Guy?</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Sources: twitter.com/BORReport, twitter.com/TaiwanBoxOffice</t>
+          <t>Even though not much information has been revealed about 2024’s The Fall Guy, will Ryan Gosling’s presence in Barbie benefit this production by establishing him as a “butts in seats” star?</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4242,18 +5209,29 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Oppenheimer movie - If you saw it, what do you think?</t>
+          <t>Question about movie villains. [Minor MI Dead Reckoning P1 Spoilers]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Anyone see the Oppenheimer movie?  If you did, what did you think of it?  Was it supposed to be historically accurate?  Or Hollywood’s version of what happened?  Did they talk about Oppenheimer attempt to poison his teacher with an apple?  Vetasium on YouTube has a wonderful video about Oppenheimer’s life and his failures. 
-The stars of the movies walked out of the premiere in London because of the writers strike.</t>
+          <t>.
+.
+.
+So usually there are villains in movies who aren't really fleshed out, and despite doing cool stuff or being intimidating, end up not being considered interesting characters by the viewers.
+One example is Gabriel, from Dead Reckoning 1. He was cool, amazing at combat and pretty intimidating too, given that every time he was on screen, the viewers feared for the lives of the IMF team.
+However as of now, before part 2's release, we don't know much about him as a human, his motivation for helping the entity and other objectives etc. (Although it's most likely the Entity bullying him into doing this but this wasn't explained in the film).
+And due to this, quite a few people online have been somewhat critical of that character, calling him an uninteresting villain.
+There are several other examples of this too, I remember the blue bad guy (Ronin i think his name was) from Guardians of the galaxy.
+However then there are instances when the same happens, but people for some reason love that villain. 
+Darth Vader from A New Hope is an example of that. (Not considering Vader from the 2 sequels or the prequel trilogy).
+He was scary, intimidating, but we knew nothing about him as a character, except a few bits like him being ObiWan's friend etc.
+But then why was he universally loved?
+P.s: I'm also a vader fan, just trying to analyse these characters further.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -4263,13 +5241,18 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Barbenheimer is ridiculous</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr"/>
+          <t>How necessary is it to watch Oppenheimer in IMAX?</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>For people who saw the film in IMAX, in hindsight, do you think it's essential for movie-goers to watch it in IMAX, or could they watch it on a standard screen and still enjoy the film to the full extent? Is it like Avatar 2 level important or is it like Indy 5 where it's not as crucial?
+ I'm just asking this because the  70mm IMAX theatre is 1 and a half hours drive away, and I wonder if it's worth the drive instead of going to the small AMC theatre 5 minutes away from my house.</t>
+        </is>
+      </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -4279,13 +5262,13 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>to what extent have the memes influenced the hype for Barbie and Oppenheimer, and could similar online viral content drive the success of other films</t>
+          <t>Will Barbie be a bomb in Japan?</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>I think the first memes surrounding Barbie and Oppenheimer competing was at least a year ago, and has influenced enough that even people outside of normal film internet have joked about doing Barbie Oppenheimer double features, I have seen theaters encourage it online, and both films are expected to do well opening weekend
-Have those memes actually impacted the hype for these films? and if so, what can other studios take away from that</t>
+          <t>Full disclaimer: I am actually really rooting for Barbie and want it to become number one for the year, so I'm not concern trolling.
+Anyways,I'm worried that Barbie might be doa in Japan mainly because of its association with Oppenheimer. Reject Barbenheimer has been trending all weekend in Japan, and I think this might be the one market where these two films being entwined together might be a big negative as Barbie could be rejected by association.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4300,17 +5283,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Cillian Murphy’s Introvert Personality Led RDJ into Thinking He Was ‘Icing’ Him: “I Was Regularly Skipping Cast Dinner Parties”, Says He Wasn’t Much Fun to Hang Out With on ‘Oppenheimer’ Set</t>
+          <t>Is there a possibility that Barbie does NOT outrank Mario Bros movie as the #1 worldwide Box office for 2023? And if so, what would have to happen?</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Like for example if Nintendo decides to re-release the Mario Movie in theatres at a later date (like Morbius did unsuccesfully), could it wedge up the numbers?</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -4320,17 +5303,20 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Looking forward to Oppenheimer release</t>
+          <t>What’s your prediction for the new TMNT movie?</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>While not much hype is forming around this movie, relatively speaking, with it getting caught up in the barbenheimer storm, I personally think it has quite a bit going for it. TMNT has a relatively loyal fanbase and considering it’s the first non-Michael-Bay-esque TMNT media in a long time, I personally think it will gather a lot of steam in comic and TMNT fan circles, especially if the RT reviews are an indication of its quality.
+Not only that, but its heavily stylized spiderverse-inspired animation demonstrates that (in a way) it’s not entirely aiming to be mainstream (which is almost mainstream in of itself) and willing to go into a more faithful and comic book-y direction. Also, the trailers have kind of demonstrated that the movie is likely willing to go into a more niche direction and explore aspects of the franchise which aren’t expanded upon very often (such as the teenager-ness if the TEENAGE MNT), which I think will go over well with returning TMNT fans. Add that to the franchise still being a (relative) hit with kids whose parents will most likely get dragged along to see the movie, and I’m personally predicting a 20-25m opening weekend.
+I would predict 30 but animated movies are traditionally less front-loaded and make more over time, and I don’t think I’m ready to be that optimistic, especially with middling mainstream appeal. But maybe Seth Rogan still has some pull, and he has been a big part of the marketing for this movie, so who knows?
+This movie also has an estimated 70-80m budget, so do you think it’ll make a profit within its lifespan?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -4340,13 +5326,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>They have done the impossible. Early estimates have SOUND OF FREEDOM as the #1 film in the nation, topping MISSION IMPOSSIBLE yesterday—$4.8M to $4.6M. That’s some serious trafficking.</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr"/>
+          <t>Most hyped week ever seen on this thread since I joined in</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>I have been following this thread since 2020 and this is probably the most exciting week I have ever seen. I'm Italian and sadly here There's no Oppenheimer - Barbie week cause Oppenheimer in Italy will be released only in late August. But I will watch Barbie this week and I'm looking forward for the review embargo lifting for both movies. Hype hype hype! Hype for these movies and for the box office, without forgetting the 2nd week of MI7. Personally I hope the tom cruise last epic movie will find the break even point but in general this is going to be a week to be remembered! I"m sure to be not the only one to feel in this way here 😋</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>mission_impossible</t>
+          <t>barbie</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -4356,19 +5346,14 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Oppenheimer true resolution format guide</t>
+          <t>My Imax theatre has 2 options for Oppenheimer. The Imax digital version and the 70mm version. But idk what the better experience is for this specific theatre?</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>&amp;amp;#x200B;
-![img](94z8ptnuazcb1 " It seems like a lot of people assume digital IMAX is a higher resolution than 70mm, and that's not the case. For those wondering about the different ways to see Oppenheimer, here's an official diagram they released to explain the specifics.
-")
-The absolute best way to see the film is in 70mm IMAX (top left in the image here). There are only 30 theaters worldwide showing it that way, but if you can, definitely watch it that way. The resolution is the equivalent of 18k, which may well be the highest resolution you've ever seen a movie in in your life.  
-Regular (non-IMAX) 70mm (center left) is the second best option if you want a high resolution. It's the equivalent of 12k-13k.  
-Regular (digital) IMAX (top right and center right) screen resolution is 2k or 4k, which is lower resolution than 32mm celluloid (bottom left, 6k) and the aforementioned 70mm options (18k and 12-13k). (And I don't know the numbers, but I'm guessing there are a lot more theaters equipped with the 2k xenon IMAX than the 4k laser IMAX capabilities.) Regular IMAX will be a taller aspect ratio than the non-IMAX 70mm, so you'll see more screen area, but you won't see as much detail in the image in regular IMAX as you will in 70mm. Seeing the film in one of the 70mm options will be your only chance to see it at as high a resolution as possible - at least three times as much detail as regular IMAX. (Buying the eventual 4k disc will allow you to see it at just as high a resolution as the regular IMAX, though presumably on a smaller screen. 📷 )  
-DCP (Digital Cinema Package, bottom right) is the way most movies are shown in most theaters ever since digital projection from a portable hard drive has almost completely replaced celluloid. 35mm film used to be the standard way for a movie to be shown on the big screen, but not for a number of years now. DCP options will vary from 2k to 4k, as with the non-70mm IMAX options.  
-I'm going to see it on 70mm, since the closest theater showing the 70mm IMAX is a two hour drive away. If I want to see it a second time, I'll consider trying the digital IMAX. But I want to see it in the higher resolution first.</t>
+          <t>The Imax version is of course the Imax version. Large screen, large seating, loud sound, good quality, etc. For $20.
+But what I'm stuck on is the 70mm version. Because at my theatre this version is playing on a much smaller screen, with much smaller seating. It doesn't indicate if it's using good sound or not. And the prices are $12. 
+Nolan says that the 70mm is the true experience but I feel like that's not the case at my theatre? Or am I wrong?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4383,17 +5368,21 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>‘BARBIE’ is Certified Fresh on Rotten Tomatoes at 89%</t>
+          <t>Do you think it is better to see Oppenheimer in IMAX or 70mm ?</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Where I live I have the option of one of the other and not both.
+There's only 1 real IMAX in my entire country. I expected they'd be showing the 70mm print of Oppenheimer. It's a few hours drive away so we booked a hotel overnight months ago to see it in a few weeks time. I found out yesterday the screening won't be 70mm so I am now on the fence on cancelling the trip.
+The 70mm option are on regular smaller cinema screens but there are 2-3 options in far more local theaters.
+I'm trying to decide whether to make the trip or just catch it nearby.
+What would you do? Let's purely consider it based on the viewing experience of the film as opposed to caveats of the distance traveled and hotel.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -4403,10 +5392,19 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Will Barbie outgross Across the Spiderverse?</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr"/>
+          <t>Barbie and the PG-13 comedy</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Came back from Barbie and was very surprised at how good it was. Not just good, but incredibly funny. 
+It brought back a type of comedy we don't see anymore, the PG-13 comedy. 
+I was thinking about what comedy movie felt the most similar to Barbie and I kept coming to "Wayne's World". There's an absurdity to both movies, but also a very real self conscious look at itself. With a lot of jokes around that aspect of the film. 
+With Wayne's World also being a PG-13 movie, you had a similar humor. Less raunchy. More double entendres. More physical comedy. 
+Thought Barbie was great, funny, and a throwback to the old PG-13 comedies that no longer exist
+Note: This post is not me putting down Joy Ride or No Hard Feelings. Think those are funny movies too. We just have not seen a successful PG-13 comedy in a LOOONNNGGGG time.</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>barbie</t>
@@ -4419,17 +5417,19 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>#Barbie scored the biggest pre-show #boxoffice debut of ANY film since Black Panther: Wakanda Forever last NOV. Just look at what she beat: $22.3M/ #BarbieTheMovie $17.5M/ #GuardiansOfTheGalaxyVol3 $17.5M/ #AntMan3 $17.4M/ #SpiderManAcrossTheSpiderVerse $17M/ #AvatarTheWayOfWater</t>
+          <t>Nolan’s film rankings (top 10)</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>[removed]</t>
+          <t>Oppenheimer was an absolutely incredible and visceral experience. Another perfected piece of cinema by the living legend Christopher Nolan. Those who have seen Oppenheimer already, in what order would you now rank Nolan’s movies? 
+My list: 
+1. The Dark Knight (of course) 2.Interstellar 3. Inception 4. Oppenheimer 5. The Prestige 6. The Dark Knight Rises 7. Batman Begins 8. Momento 9. Dunkirk 10. Tenet</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -4439,18 +5439,20 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FILM _ Oppenheimer - What are Perforations?</t>
+          <t>Just Saw Mission Impossible: Dead Reckoning Part 1</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Oppenheimer is the first film to be shot with 15 perforations and a 70mm film, and to my understanding, IMAX encapsulates 70mm - 5 and above perforations. What is so special about nolans film being shot in 15? He's done it in 5 before(Dark Knight, Dunkirk). \\
-P.S - If anyone has any links for me to research about films(quality, resolution, digital vs analog, etc, please tell me where to get started, im interested!)</t>
+          <t>I thought it was pretty good but the script was a little stilted.
+It definitely improved as it went along.
+I give it 8/10.
+How do you think it compared to 4, 5 and 6?</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>oppenheimer</t>
+          <t>mission_impossible</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -4460,18 +5462,19 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Per Deadline, Disney’s The Haunted Mansion will take all of Barbie‘s PLFs</t>
+          <t>Oppenheimer Metacritic Review Predictions</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>[Deadline](https://deadline.com/2023/07/barbie-oppenheimer-warner-bros-tuesday-box-office-record-1235448678/):
-&amp;gt; As we told you both movies are looking at excellent second weekend holds around (-55%) with Barbie eyeing $70M-$72M, and Oppeneheimer around $35M. **Disney’s The Haunted Mansion takes all of Barbie‘s PLFs. If Haunted Mansion is lucky, it will to north of $30M, which is where presales have it.**</t>
+          <t>With the review embargo for Oppenheimer dropping within a day, thought it would be a bit of fun (for those who care) to share Metascore predictions based on what we’ve heard so far.
+I’m honestly thinking it could score as one of Nolan’s best (around 89-91). The 94 score of Dunkirk could be tough to beat though. But this might just have everything critics have been searching for in a historical movie since something like Schindlers list. But of course, early social reactions can’t always be trusted. 
+What are your predictions?</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>barbie</t>
+          <t>oppenheimer</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
